--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BC1EFCE-BE84-4374-90F7-906903E930CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D49A40B9-5CA7-4DA1-BB00-E68EA1AAA7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2047,18 +2047,150 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_won-NZL_0009</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_9</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0002</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_2</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0001</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_1</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0029</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_29</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0039</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_39</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0053</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_53</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0065</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_65</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0066</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_66</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0082</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_82</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0052</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_52</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0086</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_86</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0005</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_5</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0040</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_40</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0042</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_42</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0054</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_54</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0059</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_59</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0112</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_112</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0098</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_98</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0043</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_43</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0020</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_20</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0051</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_51</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0100</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_100</t>
+  </si>
+  <si>
     <t>distr_solelc_won-NZL_0044</t>
   </si>
   <si>
     <t>connecting solar and wind to buses in grid cell NZL_44</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_won-NZL_0030</t>
   </si>
   <si>
@@ -2107,52 +2239,82 @@
     <t>connecting solar and wind to buses in grid cell NZL_93</t>
   </si>
   <si>
-    <t>distr_solelc_won-NZL_0052</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_52</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0086</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_86</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0005</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_5</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0040</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_40</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0042</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_42</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0054</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_54</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0059</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_59</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0112</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_112</t>
+    <t>distr_solelc_won-NZL_0073</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_73</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0026</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_26</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0094</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_94</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0070</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_70</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0104</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_104</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0111</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_111</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0032</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_32</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0013</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_13</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0022</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_22</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0061</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_61</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0062</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_62</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0076</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_76</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0109</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_109</t>
   </si>
   <si>
     <t>distr_solelc_won-NZL_0096</t>
@@ -2221,6 +2383,210 @@
     <t>connecting solar and wind to buses in grid cell NZL_89</t>
   </si>
   <si>
+    <t>distr_solelc_won-NZL_0068</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_68</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0083</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_83</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0045</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_45</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0077</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_77</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0099</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_99</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0017</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_17</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0102</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_102</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0057</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_57</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0064</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_64</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0078</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_78</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0018</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_18</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0025</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_25</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0016</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_16</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0034</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_34</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0063</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_63</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0067</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_67</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0079</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_79</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0091</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_91</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0036</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_36</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0110</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_110</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0027</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_27</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0103</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_103</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0008</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_8</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0021</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_21</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0101</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_101</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0108</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_108</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0114</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_114</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0087</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_87</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0056</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_56</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0047</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_47</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0048</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_48</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0071</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_71</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0084</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_84</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0088</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_88</t>
+  </si>
+  <si>
     <t>distr_solelc_won-NZL_0081</t>
   </si>
   <si>
@@ -2263,40 +2629,46 @@
     <t>connecting solar and wind to buses in grid cell NZL_107</t>
   </si>
   <si>
-    <t>distr_solelc_won-NZL_0073</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_73</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0026</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_26</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0094</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_94</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0070</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_70</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0104</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_104</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0111</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_111</t>
+    <t>distr_solelc_won-NZL_0055</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_55</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0072</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_72</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0004</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_4</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0006</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_6</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0046</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_46</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0050</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_50</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-NZL_0090</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell NZL_90</t>
   </si>
   <si>
     <t>distr_solelc_won-NZL_0095</t>
@@ -2353,381 +2725,129 @@
     <t>connecting solar and wind to buses in grid cell NZL_58</t>
   </si>
   <si>
-    <t>distr_solelc_won-NZL_0068</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_68</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0083</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_83</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0045</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_45</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0077</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_77</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0099</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_99</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0027</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_27</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0103</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_103</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0008</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_8</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0021</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_21</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0101</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_101</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0108</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_108</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0114</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_114</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0087</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_87</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0056</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_56</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0047</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_47</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0048</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_48</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0071</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_71</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0084</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_84</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0088</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_88</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0009</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_9</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0002</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_2</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0001</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_1</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0029</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_29</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0039</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_39</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0053</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_53</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0065</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_65</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0066</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_66</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0082</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_82</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0036</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_36</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0110</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_110</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0078</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_78</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0018</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_18</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0025</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_25</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0016</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_16</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0034</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_34</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0063</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_63</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0067</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_67</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0079</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_79</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0091</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_91</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0055</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_55</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0072</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_72</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0004</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_4</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0006</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_6</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0046</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_46</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0050</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_50</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0090</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_90</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0017</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_17</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0102</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_102</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0057</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_57</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0064</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_64</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0032</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_32</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0013</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_13</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0022</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_22</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0061</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_61</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0062</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_62</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0076</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_76</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0109</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_109</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0098</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_98</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0043</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_43</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0020</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_20</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0051</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_51</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-NZL_0100</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell NZL_100</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
+    <t>elc_won-NZL_0009,elc_spv-NZL_0009</t>
+  </si>
+  <si>
+    <t>e_w272195826-220,e_w412588974-220,e_NZ43-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0002,elc_spv-NZL_0002</t>
+  </si>
+  <si>
+    <t>e_w412589726-220,e_NZ41-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0001,elc_spv-NZL_0001</t>
+  </si>
+  <si>
+    <t>e_NZ41-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0029,elc_spv-NZL_0029</t>
+  </si>
+  <si>
+    <t>e_NZ30-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0039,elc_spv-NZL_0039</t>
+  </si>
+  <si>
+    <t>e_w268826084-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0053,elc_spv-NZL_0053</t>
+  </si>
+  <si>
+    <t>e_w95046918-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0065,elc_spv-NZL_0065</t>
+  </si>
+  <si>
+    <t>e_w232382576-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0066,elc_spv-NZL_0066</t>
+  </si>
+  <si>
+    <t>e_w89943957-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0082,elc_spv-NZL_0082</t>
+  </si>
+  <si>
+    <t>e_w191346761-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0052,elc_spv-NZL_0052</t>
+  </si>
+  <si>
+    <t>e_w93827784-220,e_w95046918-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0086,elc_spv-NZL_0086</t>
+  </si>
+  <si>
+    <t>e_w167177413-220,e_w167293888-220,e_w187858674-220,e_NZ10-220,e_NZ7-220,e_NZ9-220,e_NZ5-220,e_NZ6-220,e_NZ8-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0005,elc_spv-NZL_0005</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0040,elc_spv-NZL_0040</t>
+  </si>
+  <si>
+    <t>e_w1099619174-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0042,elc_spv-NZL_0042</t>
+  </si>
+  <si>
+    <t>e_w95048289-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0054,elc_spv-NZL_0054</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0059,elc_spv-NZL_0059</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0112,elc_spv-NZL_0112</t>
+  </si>
+  <si>
+    <t>e_w167283894-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0098,elc_spv-NZL_0098</t>
+  </si>
+  <si>
+    <t>e_w119877500-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0043,elc_spv-NZL_0043</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0020,elc_spv-NZL_0020</t>
+  </si>
+  <si>
+    <t>e_w180519027-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0051,elc_spv-NZL_0051</t>
+  </si>
+  <si>
+    <t>e_w100957314-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0100,elc_spv-NZL_0100</t>
+  </si>
+  <si>
+    <t>e_NZ3-220</t>
+  </si>
+  <si>
     <t>elc_won-NZL_0044,elc_spv-NZL_0044</t>
   </si>
   <si>
@@ -2749,9 +2869,6 @@
     <t>elc_won-NZL_0012,elc_spv-NZL_0012</t>
   </si>
   <si>
-    <t>e_w180519027-220</t>
-  </si>
-  <si>
     <t>elc_won-NZL_0014,elc_spv-NZL_0014</t>
   </si>
   <si>
@@ -2764,64 +2881,79 @@
     <t>elc_won-NZL_0028,elc_spv-NZL_0028</t>
   </si>
   <si>
-    <t>e_NZ30-220</t>
-  </si>
-  <si>
     <t>elc_won-NZL_0038,elc_spv-NZL_0038</t>
   </si>
   <si>
-    <t>e_w268826084-220</t>
-  </si>
-  <si>
     <t>elc_won-NZL_0093,elc_spv-NZL_0093</t>
   </si>
   <si>
     <t>e_NZ23-220</t>
   </si>
   <si>
-    <t>elc_won-NZL_0052,elc_spv-NZL_0052</t>
-  </si>
-  <si>
-    <t>e_w93827784-220,e_w95046918-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0086,elc_spv-NZL_0086</t>
-  </si>
-  <si>
-    <t>e_w167177413-220,e_w167293888-220,e_w187858674-220,e_NZ10-220,e_NZ7-220,e_NZ9-220,e_NZ5-220,e_NZ6-220,e_NZ8-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0005,elc_spv-NZL_0005</t>
-  </si>
-  <si>
-    <t>e_NZ41-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0040,elc_spv-NZL_0040</t>
-  </si>
-  <si>
-    <t>e_w1099619174-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0042,elc_spv-NZL_0042</t>
-  </si>
-  <si>
-    <t>e_w95048289-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0054,elc_spv-NZL_0054</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0059,elc_spv-NZL_0059</t>
-  </si>
-  <si>
-    <t>e_w89943957-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0112,elc_spv-NZL_0112</t>
-  </si>
-  <si>
-    <t>e_w167283894-220</t>
+    <t>elc_won-NZL_0073,elc_spv-NZL_0073</t>
+  </si>
+  <si>
+    <t>e_w26671244-220,e_w61853727-220,e_w82881422-220,e_w161270797-220,e_w907631032-220,e_w1363994055-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0026,elc_spv-NZL_0026</t>
+  </si>
+  <si>
+    <t>e_w89664063-220,e_NZ38-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0094,elc_spv-NZL_0094</t>
+  </si>
+  <si>
+    <t>e_w191346761-220,e_NZ20-220,e_NZ21-220,e_NZ22-220,e_NZ23-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0070,elc_spv-NZL_0070</t>
+  </si>
+  <si>
+    <t>e_r17609399-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0104,elc_spv-NZL_0104</t>
+  </si>
+  <si>
+    <t>e_w270556206-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0111,elc_spv-NZL_0111</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0032,elc_spv-NZL_0032</t>
+  </si>
+  <si>
+    <t>e_w89637173-220,e_w89637174-220,e_w94840399-220,e_NZ39-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0013,elc_spv-NZL_0013</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0022,elc_spv-NZL_0022</t>
+  </si>
+  <si>
+    <t>e_w89636510-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0061,elc_spv-NZL_0061</t>
+  </si>
+  <si>
+    <t>e_NZ27-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0062,elc_spv-NZL_0062</t>
+  </si>
+  <si>
+    <t>e_w167705537-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0076,elc_spv-NZL_0076</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0109,elc_spv-NZL_0109</t>
   </si>
   <si>
     <t>elc_won-NZL_0096,elc_spv-NZL_0096</t>
@@ -2851,9 +2983,6 @@
     <t>elc_won-NZL_0105,elc_spv-NZL_0105</t>
   </si>
   <si>
-    <t>e_w270556206-220</t>
-  </si>
-  <si>
     <t>elc_won-NZL_0033,elc_spv-NZL_0033</t>
   </si>
   <si>
@@ -2875,15 +3004,168 @@
     <t>elc_won-NZL_0069,elc_spv-NZL_0069</t>
   </si>
   <si>
-    <t>e_r17609399-220</t>
-  </si>
-  <si>
     <t>elc_won-NZL_0089,elc_spv-NZL_0089</t>
   </si>
   <si>
     <t>e_w82881422-220</t>
   </si>
   <si>
+    <t>elc_won-NZL_0068,elc_spv-NZL_0068</t>
+  </si>
+  <si>
+    <t>e_w95343089-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0083,elc_spv-NZL_0083</t>
+  </si>
+  <si>
+    <t>e_w167427251-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0045,elc_spv-NZL_0045</t>
+  </si>
+  <si>
+    <t>e_w93827784-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0077,elc_spv-NZL_0077</t>
+  </si>
+  <si>
+    <t>e_w93713118-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0099,elc_spv-NZL_0099</t>
+  </si>
+  <si>
+    <t>e_NZ5-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0017,elc_spv-NZL_0017</t>
+  </si>
+  <si>
+    <t>e_w90092620-220,e_NZ42-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0102,elc_spv-NZL_0102</t>
+  </si>
+  <si>
+    <t>e_w93419960-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0057,elc_spv-NZL_0057</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0064,elc_spv-NZL_0064</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0078,elc_spv-NZL_0078</t>
+  </si>
+  <si>
+    <t>e_w93713118-220,e_w627162826-220,e_NZ26-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0018,elc_spv-NZL_0018</t>
+  </si>
+  <si>
+    <t>e_w180514007-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0025,elc_spv-NZL_0025</t>
+  </si>
+  <si>
+    <t>e_w414953388-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0016,elc_spv-NZL_0016</t>
+  </si>
+  <si>
+    <t>e_NZ42-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0034,elc_spv-NZL_0034</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0063,elc_spv-NZL_0063</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0067,elc_spv-NZL_0067</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0079,elc_spv-NZL_0079</t>
+  </si>
+  <si>
+    <t>e_NZ26-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0091,elc_spv-NZL_0091</t>
+  </si>
+  <si>
+    <t>e_w1026587442-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0036,elc_spv-NZL_0036</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0110,elc_spv-NZL_0110</t>
+  </si>
+  <si>
+    <t>e_NZ13-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0027,elc_spv-NZL_0027</t>
+  </si>
+  <si>
+    <t>e_w89635947-220,e_w89636266-220,e_w89636510-220,e_w170300247-220,e_w270012796-220,e_NZ37-220,e_NZ36-220,e_NZ34-220,e_NZ30-220,e_NZ31-220,e_NZ35-220,e_NZ33-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0103,elc_spv-NZL_0103</t>
+  </si>
+  <si>
+    <t>e_w95512216-220,e_w409049317-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0008,elc_spv-NZL_0008</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0021,elc_spv-NZL_0021</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0101,elc_spv-NZL_0101</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0108,elc_spv-NZL_0108</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0114,elc_spv-NZL_0114</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0087,elc_spv-NZL_0087</t>
+  </si>
+  <si>
+    <t>e_w61455399-220,e_w75609279-220,e_w87897292-220,e_w90098853-220,e_w156094589-220,e_w235066414-220,e_w341099346-220,e_w359449581-220,e_w849110529-220,e_w1018655038-220,e_NZ4-220,e_NZ2-220,e_NZ3-220,e_NZ1-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0056,elc_spv-NZL_0056</t>
+  </si>
+  <si>
+    <t>e_w167705537-220,e_NZ27-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0047,elc_spv-NZL_0047</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0048,elc_spv-NZL_0048</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0071,elc_spv-NZL_0071</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0084,elc_spv-NZL_0084</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0088,elc_spv-NZL_0088</t>
+  </si>
+  <si>
     <t>elc_won-NZL_0081,elc_spv-NZL_0081</t>
   </si>
   <si>
@@ -2902,15 +3184,9 @@
     <t>elc_won-NZL_0060,elc_spv-NZL_0060</t>
   </si>
   <si>
-    <t>e_w95046918-220</t>
-  </si>
-  <si>
     <t>elc_won-NZL_0074,elc_spv-NZL_0074</t>
   </si>
   <si>
-    <t>e_w232382576-220</t>
-  </si>
-  <si>
     <t>elc_won-NZL_0080,elc_spv-NZL_0080</t>
   </si>
   <si>
@@ -2920,31 +3196,31 @@
     <t>e_w95512216-220</t>
   </si>
   <si>
-    <t>elc_won-NZL_0073,elc_spv-NZL_0073</t>
-  </si>
-  <si>
-    <t>e_w26671244-220,e_w61853727-220,e_w82881422-220,e_w161270797-220,e_w907631032-220,e_w1363994055-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0026,elc_spv-NZL_0026</t>
-  </si>
-  <si>
-    <t>e_w89664063-220,e_NZ38-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0094,elc_spv-NZL_0094</t>
-  </si>
-  <si>
-    <t>e_w191346761-220,e_NZ20-220,e_NZ21-220,e_NZ22-220,e_NZ23-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0070,elc_spv-NZL_0070</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0104,elc_spv-NZL_0104</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0111,elc_spv-NZL_0111</t>
+    <t>elc_won-NZL_0055,elc_spv-NZL_0055</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0072,elc_spv-NZL_0072</t>
+  </si>
+  <si>
+    <t>e_w188180344-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0004,elc_spv-NZL_0004</t>
+  </si>
+  <si>
+    <t>e_w412588974-220</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0006,elc_spv-NZL_0006</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0046,elc_spv-NZL_0046</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0050,elc_spv-NZL_0050</t>
+  </si>
+  <si>
+    <t>elc_won-NZL_0090,elc_spv-NZL_0090</t>
   </si>
   <si>
     <t>elc_won-NZL_0095,elc_spv-NZL_0095</t>
@@ -2990,282 +3266,6 @@
   </si>
   <si>
     <t>elc_won-NZL_0058,elc_spv-NZL_0058</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0068,elc_spv-NZL_0068</t>
-  </si>
-  <si>
-    <t>e_w95343089-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0083,elc_spv-NZL_0083</t>
-  </si>
-  <si>
-    <t>e_w167427251-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0045,elc_spv-NZL_0045</t>
-  </si>
-  <si>
-    <t>e_w93827784-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0077,elc_spv-NZL_0077</t>
-  </si>
-  <si>
-    <t>e_w93713118-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0099,elc_spv-NZL_0099</t>
-  </si>
-  <si>
-    <t>e_NZ5-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0027,elc_spv-NZL_0027</t>
-  </si>
-  <si>
-    <t>e_w89635947-220,e_w89636266-220,e_w89636510-220,e_w170300247-220,e_w270012796-220,e_NZ37-220,e_NZ36-220,e_NZ34-220,e_NZ30-220,e_NZ31-220,e_NZ35-220,e_NZ33-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0103,elc_spv-NZL_0103</t>
-  </si>
-  <si>
-    <t>e_w95512216-220,e_w409049317-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0008,elc_spv-NZL_0008</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0021,elc_spv-NZL_0021</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0101,elc_spv-NZL_0101</t>
-  </si>
-  <si>
-    <t>e_w93419960-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0108,elc_spv-NZL_0108</t>
-  </si>
-  <si>
-    <t>e_NZ13-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0114,elc_spv-NZL_0114</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0087,elc_spv-NZL_0087</t>
-  </si>
-  <si>
-    <t>e_w61455399-220,e_w75609279-220,e_w87897292-220,e_w90098853-220,e_w156094589-220,e_w235066414-220,e_w341099346-220,e_w359449581-220,e_w849110529-220,e_w1018655038-220,e_NZ4-220,e_NZ2-220,e_NZ3-220,e_NZ1-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0056,elc_spv-NZL_0056</t>
-  </si>
-  <si>
-    <t>e_w167705537-220,e_NZ27-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0047,elc_spv-NZL_0047</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0048,elc_spv-NZL_0048</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0071,elc_spv-NZL_0071</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0084,elc_spv-NZL_0084</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0088,elc_spv-NZL_0088</t>
-  </si>
-  <si>
-    <t>e_NZ3-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0009,elc_spv-NZL_0009</t>
-  </si>
-  <si>
-    <t>e_w272195826-220,e_w412588974-220,e_NZ43-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0002,elc_spv-NZL_0002</t>
-  </si>
-  <si>
-    <t>e_w412589726-220,e_NZ41-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0001,elc_spv-NZL_0001</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0029,elc_spv-NZL_0029</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0039,elc_spv-NZL_0039</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0053,elc_spv-NZL_0053</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0065,elc_spv-NZL_0065</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0066,elc_spv-NZL_0066</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0082,elc_spv-NZL_0082</t>
-  </si>
-  <si>
-    <t>e_w191346761-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0036,elc_spv-NZL_0036</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0110,elc_spv-NZL_0110</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0078,elc_spv-NZL_0078</t>
-  </si>
-  <si>
-    <t>e_w93713118-220,e_w627162826-220,e_NZ26-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0018,elc_spv-NZL_0018</t>
-  </si>
-  <si>
-    <t>e_w180514007-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0025,elc_spv-NZL_0025</t>
-  </si>
-  <si>
-    <t>e_w414953388-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0016,elc_spv-NZL_0016</t>
-  </si>
-  <si>
-    <t>e_NZ42-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0034,elc_spv-NZL_0034</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0063,elc_spv-NZL_0063</t>
-  </si>
-  <si>
-    <t>e_w167705537-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0067,elc_spv-NZL_0067</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0079,elc_spv-NZL_0079</t>
-  </si>
-  <si>
-    <t>e_NZ26-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0091,elc_spv-NZL_0091</t>
-  </si>
-  <si>
-    <t>e_w1026587442-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0055,elc_spv-NZL_0055</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0072,elc_spv-NZL_0072</t>
-  </si>
-  <si>
-    <t>e_w188180344-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0004,elc_spv-NZL_0004</t>
-  </si>
-  <si>
-    <t>e_w412588974-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0006,elc_spv-NZL_0006</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0046,elc_spv-NZL_0046</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0050,elc_spv-NZL_0050</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0090,elc_spv-NZL_0090</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0017,elc_spv-NZL_0017</t>
-  </si>
-  <si>
-    <t>e_w90092620-220,e_NZ42-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0102,elc_spv-NZL_0102</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0057,elc_spv-NZL_0057</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0064,elc_spv-NZL_0064</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0032,elc_spv-NZL_0032</t>
-  </si>
-  <si>
-    <t>e_w89637173-220,e_w89637174-220,e_w94840399-220,e_NZ39-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0013,elc_spv-NZL_0013</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0022,elc_spv-NZL_0022</t>
-  </si>
-  <si>
-    <t>e_w89636510-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0061,elc_spv-NZL_0061</t>
-  </si>
-  <si>
-    <t>e_NZ27-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0062,elc_spv-NZL_0062</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0076,elc_spv-NZL_0076</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0109,elc_spv-NZL_0109</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0098,elc_spv-NZL_0098</t>
-  </si>
-  <si>
-    <t>e_w119877500-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0043,elc_spv-NZL_0043</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0020,elc_spv-NZL_0020</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0051,elc_spv-NZL_0051</t>
-  </si>
-  <si>
-    <t>e_w100957314-220</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0100,elc_spv-NZL_0100</t>
   </si>
   <si>
     <t>e_won-NZL_0000</t>
@@ -9212,7 +9212,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4821CDF-1D6A-4BC8-A7BB-EAF6C7FA052C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{815FF28B-74D4-417C-8671-20624F1307D3}">
   <dimension ref="B9:AR122"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9387,7 +9387,7 @@
         <v>2.7760129659643439E-2</v>
       </c>
       <c r="N11">
-        <v>0.113</v>
+        <v>0.13557988630474541</v>
       </c>
       <c r="P11" t="s">
         <v>638</v>
@@ -9426,7 +9426,7 @@
         <v>1</v>
       </c>
       <c r="AC11" t="s">
-        <v>497</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" spans="2:44">
@@ -9464,7 +9464,7 @@
         <v>3.1717002455087483E-3</v>
       </c>
       <c r="N12">
-        <v>0.106</v>
+        <v>0.1393182814834493</v>
       </c>
       <c r="P12" t="s">
         <v>638</v>
@@ -9503,7 +9503,7 @@
         <v>1</v>
       </c>
       <c r="AC12" t="s">
-        <v>469</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="2:44">
@@ -9541,7 +9541,7 @@
         <v>7.3151430741959993E-4</v>
       </c>
       <c r="N13">
-        <v>9.8000000000000004E-2</v>
+        <v>0.1468540135131588</v>
       </c>
       <c r="P13" t="s">
         <v>638</v>
@@ -9580,7 +9580,7 @@
         <v>1</v>
       </c>
       <c r="AC13" t="s">
-        <v>579</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="2:44">
@@ -9618,7 +9618,7 @@
         <v>0.31828022341745965</v>
       </c>
       <c r="N14">
-        <v>0.105</v>
+        <v>0.14561710477607931</v>
       </c>
       <c r="P14" t="s">
         <v>638</v>
@@ -9657,7 +9657,7 @@
         <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>435</v>
+        <v>467</v>
       </c>
     </row>
     <row r="15" spans="2:44">
@@ -9695,7 +9695,7 @@
         <v>1.47796163929902</v>
       </c>
       <c r="N15">
-        <v>0.13500000000000001</v>
+        <v>0.14317429989714001</v>
       </c>
       <c r="P15" t="s">
         <v>638</v>
@@ -9728,13 +9728,13 @@
         <v>874</v>
       </c>
       <c r="AA15" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="AB15">
         <v>1</v>
       </c>
       <c r="AC15" t="s">
-        <v>439</v>
+        <v>487</v>
       </c>
     </row>
     <row r="16" spans="2:44">
@@ -9772,7 +9772,7 @@
         <v>0.98465738400648506</v>
       </c>
       <c r="N16">
-        <v>0.14299999999999999</v>
+        <v>0.1435206851838097</v>
       </c>
       <c r="P16" t="s">
         <v>638</v>
@@ -9802,16 +9802,16 @@
         <v>651</v>
       </c>
       <c r="Z16" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AA16" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AB16">
         <v>1</v>
       </c>
       <c r="AC16" t="s">
-        <v>455</v>
+        <v>515</v>
       </c>
     </row>
     <row r="17" spans="2:29">
@@ -9849,7 +9849,7 @@
         <v>0.19618446110676666</v>
       </c>
       <c r="N17">
-        <v>0.14099999999999999</v>
+        <v>0.14743548397672079</v>
       </c>
       <c r="P17" t="s">
         <v>638</v>
@@ -9879,16 +9879,16 @@
         <v>653</v>
       </c>
       <c r="Z17" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="AA17" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AB17">
         <v>1</v>
       </c>
       <c r="AC17" t="s">
-        <v>465</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" spans="2:29">
@@ -9926,7 +9926,7 @@
         <v>3.818866976510489E-3</v>
       </c>
       <c r="N18">
-        <v>0.108</v>
+        <v>0.151279468166237</v>
       </c>
       <c r="P18" t="s">
         <v>638</v>
@@ -9956,16 +9956,16 @@
         <v>655</v>
       </c>
       <c r="Z18" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="AA18" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="AB18">
         <v>1</v>
       </c>
       <c r="AC18" t="s">
-        <v>485</v>
+        <v>541</v>
       </c>
     </row>
     <row r="19" spans="2:29">
@@ -10003,7 +10003,7 @@
         <v>1.3553813802146566</v>
       </c>
       <c r="N19">
-        <v>0.13100000000000001</v>
+        <v>0.1492204982544815</v>
       </c>
       <c r="P19" t="s">
         <v>638</v>
@@ -10033,16 +10033,16 @@
         <v>657</v>
       </c>
       <c r="Z19" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AA19" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AB19">
         <v>1</v>
       </c>
       <c r="AC19" t="s">
-        <v>595</v>
+        <v>573</v>
       </c>
     </row>
     <row r="20" spans="2:29">
@@ -10080,7 +10080,7 @@
         <v>3.1693862667113906</v>
       </c>
       <c r="N20">
-        <v>0.13500000000000001</v>
+        <v>0.1497782526243627</v>
       </c>
       <c r="P20" t="s">
         <v>638</v>
@@ -10110,10 +10110,10 @@
         <v>659</v>
       </c>
       <c r="Z20" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AA20" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="AB20">
         <v>1</v>
@@ -10157,7 +10157,7 @@
         <v>1.9907164377072475</v>
       </c>
       <c r="N21">
-        <v>0.14099999999999999</v>
+        <v>0.15273468455452049</v>
       </c>
       <c r="P21" t="s">
         <v>638</v>
@@ -10187,10 +10187,10 @@
         <v>661</v>
       </c>
       <c r="Z21" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="AA21" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AB21">
         <v>1</v>
@@ -10234,7 +10234,7 @@
         <v>0.20100641431023578</v>
       </c>
       <c r="N22">
-        <v>0.14099999999999999</v>
+        <v>0.1552216675586752</v>
       </c>
       <c r="P22" t="s">
         <v>638</v>
@@ -10264,10 +10264,10 @@
         <v>663</v>
       </c>
       <c r="Z22" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AA22" t="s">
-        <v>888</v>
+        <v>871</v>
       </c>
       <c r="AB22">
         <v>1</v>
@@ -10311,7 +10311,7 @@
         <v>6.5500000000000003E-2</v>
       </c>
       <c r="N23">
-        <v>0.14599999999999999</v>
+        <v>0.16043898876011289</v>
       </c>
       <c r="P23" t="s">
         <v>638</v>
@@ -10388,7 +10388,7 @@
         <v>4.241541434091884E-2</v>
       </c>
       <c r="N24">
-        <v>0.126</v>
+        <v>0.163221371913883</v>
       </c>
       <c r="P24" t="s">
         <v>638</v>
@@ -10465,7 +10465,7 @@
         <v>0.94576627356300502</v>
       </c>
       <c r="N25">
-        <v>0.125</v>
+        <v>0.15128760338989061</v>
       </c>
       <c r="P25" t="s">
         <v>638</v>
@@ -10542,7 +10542,7 @@
         <v>3.1518072809247446</v>
       </c>
       <c r="N26">
-        <v>0.13700000000000001</v>
+        <v>0.15116140941395709</v>
       </c>
       <c r="P26" t="s">
         <v>638</v>
@@ -10575,7 +10575,7 @@
         <v>894</v>
       </c>
       <c r="AA26" t="s">
-        <v>895</v>
+        <v>881</v>
       </c>
       <c r="AB26">
         <v>1</v>
@@ -10619,7 +10619,7 @@
         <v>1.9156900853578462</v>
       </c>
       <c r="N27">
-        <v>0.14099999999999999</v>
+        <v>0.1595691250240463</v>
       </c>
       <c r="P27" t="s">
         <v>638</v>
@@ -10649,10 +10649,10 @@
         <v>673</v>
       </c>
       <c r="Z27" t="s">
+        <v>895</v>
+      </c>
+      <c r="AA27" t="s">
         <v>896</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>897</v>
       </c>
       <c r="AB27">
         <v>1</v>
@@ -10696,7 +10696,7 @@
         <v>1.3524374018558174</v>
       </c>
       <c r="N28">
-        <v>0.156</v>
+        <v>0.16480881671278511</v>
       </c>
       <c r="P28" t="s">
         <v>638</v>
@@ -10726,16 +10726,16 @@
         <v>675</v>
       </c>
       <c r="Z28" t="s">
+        <v>897</v>
+      </c>
+      <c r="AA28" t="s">
         <v>898</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>899</v>
       </c>
       <c r="AB28">
         <v>1</v>
       </c>
       <c r="AC28" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="29" spans="2:29">
@@ -10773,7 +10773,7 @@
         <v>0.62352228472522708</v>
       </c>
       <c r="N29">
-        <v>0.16400000000000001</v>
+        <v>0.16508225281289149</v>
       </c>
       <c r="P29" t="s">
         <v>638</v>
@@ -10803,16 +10803,16 @@
         <v>677</v>
       </c>
       <c r="Z29" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AA29" t="s">
-        <v>901</v>
+        <v>875</v>
       </c>
       <c r="AB29">
         <v>1</v>
       </c>
       <c r="AC29" t="s">
-        <v>559</v>
+        <v>495</v>
       </c>
     </row>
     <row r="30" spans="2:29">
@@ -10850,7 +10850,7 @@
         <v>2.9338414355030665E-2</v>
       </c>
       <c r="N30">
-        <v>0.14199999999999999</v>
+        <v>0.16182224107328269</v>
       </c>
       <c r="P30" t="s">
         <v>638</v>
@@ -10880,16 +10880,16 @@
         <v>679</v>
       </c>
       <c r="Z30" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="AA30" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="AB30">
         <v>1</v>
       </c>
       <c r="AC30" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
     </row>
     <row r="31" spans="2:29">
@@ -10927,7 +10927,7 @@
         <v>0.12938073943440198</v>
       </c>
       <c r="N31">
-        <v>0.13300000000000001</v>
+        <v>0.15949237479539341</v>
       </c>
       <c r="P31" t="s">
         <v>638</v>
@@ -10957,16 +10957,16 @@
         <v>681</v>
       </c>
       <c r="Z31" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="AA31" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="AB31">
         <v>1</v>
       </c>
       <c r="AC31" t="s">
-        <v>603</v>
+        <v>511</v>
       </c>
     </row>
     <row r="32" spans="2:29">
@@ -11004,7 +11004,7 @@
         <v>2.0952328703703706</v>
       </c>
       <c r="N32">
-        <v>0.13500000000000001</v>
+        <v>0.15241190151015499</v>
       </c>
       <c r="P32" t="s">
         <v>638</v>
@@ -11034,16 +11034,16 @@
         <v>683</v>
       </c>
       <c r="Z32" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="AA32" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="AB32">
         <v>1</v>
       </c>
       <c r="AC32" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
     </row>
     <row r="33" spans="2:29">
@@ -11081,7 +11081,7 @@
         <v>3.2008495652173914</v>
       </c>
       <c r="N33">
-        <v>0.14499999999999999</v>
+        <v>0.1605032460891449</v>
       </c>
       <c r="P33" t="s">
         <v>638</v>
@@ -11111,16 +11111,16 @@
         <v>685</v>
       </c>
       <c r="Z33" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="AA33" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="AB33">
         <v>1</v>
       </c>
       <c r="AC33" t="s">
-        <v>475</v>
+        <v>497</v>
       </c>
     </row>
     <row r="34" spans="2:29">
@@ -11158,7 +11158,7 @@
         <v>3.8243688086262821</v>
       </c>
       <c r="N34">
-        <v>0.156</v>
+        <v>0.16717321787465711</v>
       </c>
       <c r="P34" t="s">
         <v>638</v>
@@ -11188,16 +11188,16 @@
         <v>687</v>
       </c>
       <c r="Z34" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="AA34" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="AB34">
         <v>1</v>
       </c>
       <c r="AC34" t="s">
-        <v>417</v>
+        <v>469</v>
       </c>
     </row>
     <row r="35" spans="2:29">
@@ -11235,7 +11235,7 @@
         <v>1.0633011376828418</v>
       </c>
       <c r="N35">
-        <v>0.155</v>
+        <v>0.16929421541986761</v>
       </c>
       <c r="P35" t="s">
         <v>638</v>
@@ -11265,7 +11265,7 @@
         <v>689</v>
       </c>
       <c r="Z35" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AA35" t="s">
         <v>911</v>
@@ -11274,7 +11274,7 @@
         <v>1</v>
       </c>
       <c r="AC35" t="s">
-        <v>425</v>
+        <v>579</v>
       </c>
     </row>
     <row r="36" spans="2:29">
@@ -11312,7 +11312,7 @@
         <v>0.85034701007838753</v>
       </c>
       <c r="N36">
-        <v>0.161</v>
+        <v>0.16955342258047409</v>
       </c>
       <c r="P36" t="s">
         <v>638</v>
@@ -11342,16 +11342,16 @@
         <v>691</v>
       </c>
       <c r="Z36" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="AA36" t="s">
-        <v>890</v>
+        <v>901</v>
       </c>
       <c r="AB36">
         <v>1</v>
       </c>
       <c r="AC36" t="s">
-        <v>491</v>
+        <v>435</v>
       </c>
     </row>
     <row r="37" spans="2:29">
@@ -11389,7 +11389,7 @@
         <v>0.31342795497185744</v>
       </c>
       <c r="N37">
-        <v>0.156</v>
+        <v>0.1694192058728341</v>
       </c>
       <c r="P37" t="s">
         <v>638</v>
@@ -11419,16 +11419,16 @@
         <v>693</v>
       </c>
       <c r="Z37" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="AA37" t="s">
-        <v>915</v>
+        <v>901</v>
       </c>
       <c r="AB37">
         <v>1</v>
       </c>
       <c r="AC37" t="s">
-        <v>547</v>
+        <v>439</v>
       </c>
     </row>
     <row r="38" spans="2:29">
@@ -11466,7 +11466,7 @@
         <v>0.26166653094462544</v>
       </c>
       <c r="N38">
-        <v>0.13200000000000001</v>
+        <v>0.16779314162019829</v>
       </c>
       <c r="P38" t="s">
         <v>638</v>
@@ -11496,16 +11496,16 @@
         <v>695</v>
       </c>
       <c r="Z38" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="AA38" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB38">
         <v>1</v>
       </c>
       <c r="AC38" t="s">
-        <v>587</v>
+        <v>455</v>
       </c>
     </row>
     <row r="39" spans="2:29">
@@ -11543,7 +11543,7 @@
         <v>1.0196417764536101</v>
       </c>
       <c r="N39">
-        <v>0.13900000000000001</v>
+        <v>0.1603490339856832</v>
       </c>
       <c r="P39" t="s">
         <v>638</v>
@@ -11573,16 +11573,16 @@
         <v>697</v>
       </c>
       <c r="Z39" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="AA39" t="s">
-        <v>919</v>
+        <v>873</v>
       </c>
       <c r="AB39">
         <v>1</v>
       </c>
       <c r="AC39" t="s">
-        <v>571</v>
+        <v>465</v>
       </c>
     </row>
     <row r="40" spans="2:29">
@@ -11620,7 +11620,7 @@
         <v>1.8270330330330331</v>
       </c>
       <c r="N40">
-        <v>0.14299999999999999</v>
+        <v>0.16393038969252829</v>
       </c>
       <c r="P40" t="s">
         <v>638</v>
@@ -11650,16 +11650,16 @@
         <v>699</v>
       </c>
       <c r="Z40" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="AA40" t="s">
-        <v>921</v>
+        <v>875</v>
       </c>
       <c r="AB40">
         <v>1</v>
       </c>
       <c r="AC40" t="s">
-        <v>447</v>
+        <v>485</v>
       </c>
     </row>
     <row r="41" spans="2:29">
@@ -11697,7 +11697,7 @@
         <v>2.0741027795155955</v>
       </c>
       <c r="N41">
-        <v>0.14799999999999999</v>
+        <v>0.1684721490885713</v>
       </c>
       <c r="P41" t="s">
         <v>638</v>
@@ -11727,16 +11727,16 @@
         <v>701</v>
       </c>
       <c r="Z41" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="AA41" t="s">
-        <v>903</v>
+        <v>919</v>
       </c>
       <c r="AB41">
         <v>1</v>
       </c>
       <c r="AC41" t="s">
-        <v>433</v>
+        <v>595</v>
       </c>
     </row>
     <row r="42" spans="2:29">
@@ -11774,7 +11774,7 @@
         <v>1.9771316877431904</v>
       </c>
       <c r="N42">
-        <v>0.14899999999999999</v>
+        <v>0.1718119222789779</v>
       </c>
       <c r="P42" t="s">
         <v>638</v>
@@ -11804,16 +11804,16 @@
         <v>703</v>
       </c>
       <c r="Z42" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AA42" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="AB42">
         <v>1</v>
       </c>
       <c r="AC42" t="s">
-        <v>529</v>
+        <v>555</v>
       </c>
     </row>
     <row r="43" spans="2:29">
@@ -11851,7 +11851,7 @@
         <v>1.0605408504144842</v>
       </c>
       <c r="N43">
-        <v>0.158</v>
+        <v>0.1737005919215289</v>
       </c>
       <c r="P43" t="s">
         <v>638</v>
@@ -11881,16 +11881,16 @@
         <v>705</v>
       </c>
       <c r="Z43" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="AA43" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="AB43">
         <v>1</v>
       </c>
       <c r="AC43" t="s">
-        <v>557</v>
+        <v>461</v>
       </c>
     </row>
     <row r="44" spans="2:29">
@@ -11928,7 +11928,7 @@
         <v>0.27037889918843028</v>
       </c>
       <c r="N44">
-        <v>0.14299999999999999</v>
+        <v>0.17180692048267859</v>
       </c>
       <c r="P44" t="s">
         <v>638</v>
@@ -11958,16 +11958,16 @@
         <v>707</v>
       </c>
       <c r="Z44" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="AA44" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="AB44">
         <v>1</v>
       </c>
       <c r="AC44" t="s">
-        <v>569</v>
+        <v>597</v>
       </c>
     </row>
     <row r="45" spans="2:29">
@@ -12005,7 +12005,7 @@
         <v>0.48462225032208811</v>
       </c>
       <c r="N45">
-        <v>0.13300000000000001</v>
+        <v>0.15552609305904019</v>
       </c>
       <c r="P45" t="s">
         <v>638</v>
@@ -12035,16 +12035,16 @@
         <v>709</v>
       </c>
       <c r="Z45" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="AA45" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="AB45">
         <v>1</v>
       </c>
       <c r="AC45" t="s">
-        <v>623</v>
+        <v>549</v>
       </c>
     </row>
     <row r="46" spans="2:29">
@@ -12082,7 +12082,7 @@
         <v>2.1389505235602098</v>
       </c>
       <c r="N46">
-        <v>0.14499999999999999</v>
+        <v>0.17375475778179231</v>
       </c>
       <c r="P46" t="s">
         <v>638</v>
@@ -12112,16 +12112,16 @@
         <v>711</v>
       </c>
       <c r="Z46" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="AA46" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="AB46">
         <v>1</v>
       </c>
       <c r="AC46" t="s">
-        <v>555</v>
+        <v>617</v>
       </c>
     </row>
     <row r="47" spans="2:29">
@@ -12159,7 +12159,7 @@
         <v>3.0587470406587749</v>
       </c>
       <c r="N47">
-        <v>0.14899999999999999</v>
+        <v>0.1727899663635333</v>
       </c>
       <c r="P47" t="s">
         <v>638</v>
@@ -12189,16 +12189,16 @@
         <v>713</v>
       </c>
       <c r="Z47" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="AA47" t="s">
-        <v>933</v>
+        <v>896</v>
       </c>
       <c r="AB47">
         <v>1</v>
       </c>
       <c r="AC47" t="s">
-        <v>461</v>
+        <v>631</v>
       </c>
     </row>
     <row r="48" spans="2:29">
@@ -12236,7 +12236,7 @@
         <v>0.78380198019801972</v>
       </c>
       <c r="N48">
-        <v>0.155</v>
+        <v>0.16891748105637991</v>
       </c>
       <c r="P48" t="s">
         <v>638</v>
@@ -12266,16 +12266,16 @@
         <v>715</v>
       </c>
       <c r="Z48" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="AA48" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="AB48">
         <v>1</v>
       </c>
       <c r="AC48" t="s">
-        <v>597</v>
+        <v>473</v>
       </c>
     </row>
     <row r="49" spans="2:29">
@@ -12313,7 +12313,7 @@
         <v>0.1556984704071272</v>
       </c>
       <c r="N49">
-        <v>0.13400000000000001</v>
+        <v>0.16025043860458191</v>
       </c>
       <c r="P49" t="s">
         <v>638</v>
@@ -12343,16 +12343,16 @@
         <v>717</v>
       </c>
       <c r="Z49" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="AA49" t="s">
-        <v>915</v>
+        <v>901</v>
       </c>
       <c r="AB49">
         <v>1</v>
       </c>
       <c r="AC49" t="s">
-        <v>549</v>
+        <v>437</v>
       </c>
     </row>
     <row r="50" spans="2:29">
@@ -12390,7 +12390,7 @@
         <v>0.70323982983249145</v>
       </c>
       <c r="N50">
-        <v>0.13100000000000001</v>
+        <v>0.15279580787310049</v>
       </c>
       <c r="P50" t="s">
         <v>638</v>
@@ -12420,16 +12420,16 @@
         <v>719</v>
       </c>
       <c r="Z50" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="AA50" t="s">
-        <v>907</v>
+        <v>935</v>
       </c>
       <c r="AB50">
         <v>1</v>
       </c>
       <c r="AC50" t="s">
-        <v>617</v>
+        <v>453</v>
       </c>
     </row>
     <row r="51" spans="2:29">
@@ -12467,7 +12467,7 @@
         <v>0.20051555311824024</v>
       </c>
       <c r="N51">
-        <v>0.13</v>
+        <v>0.1592123986586641</v>
       </c>
       <c r="P51" t="s">
         <v>638</v>
@@ -12497,16 +12497,16 @@
         <v>721</v>
       </c>
       <c r="Z51" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="AA51" t="s">
-        <v>897</v>
+        <v>937</v>
       </c>
       <c r="AB51">
         <v>1</v>
       </c>
       <c r="AC51" t="s">
-        <v>631</v>
+        <v>531</v>
       </c>
     </row>
     <row r="52" spans="2:29">
@@ -12544,7 +12544,7 @@
         <v>1.691024481552633</v>
       </c>
       <c r="N52">
-        <v>0.151</v>
+        <v>0.17614378027548699</v>
       </c>
       <c r="P52" t="s">
         <v>638</v>
@@ -12574,16 +12574,16 @@
         <v>723</v>
       </c>
       <c r="Z52" t="s">
+        <v>938</v>
+      </c>
+      <c r="AA52" t="s">
         <v>939</v>
-      </c>
-      <c r="AA52" t="s">
-        <v>940</v>
       </c>
       <c r="AB52">
         <v>1</v>
       </c>
       <c r="AC52" t="s">
-        <v>599</v>
+        <v>533</v>
       </c>
     </row>
     <row r="53" spans="2:29">
@@ -12621,7 +12621,7 @@
         <v>2.6365491189844636</v>
       </c>
       <c r="N53">
-        <v>0.15</v>
+        <v>0.1767456226726275</v>
       </c>
       <c r="P53" t="s">
         <v>638</v>
@@ -12651,16 +12651,16 @@
         <v>725</v>
       </c>
       <c r="Z53" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AA53" t="s">
-        <v>942</v>
+        <v>881</v>
       </c>
       <c r="AB53">
         <v>1</v>
       </c>
       <c r="AC53" t="s">
-        <v>621</v>
+        <v>561</v>
       </c>
     </row>
     <row r="54" spans="2:29">
@@ -12698,7 +12698,7 @@
         <v>0.41650673776054287</v>
       </c>
       <c r="N54">
-        <v>0.151</v>
+        <v>0.1736483329975243</v>
       </c>
       <c r="P54" t="s">
         <v>638</v>
@@ -12728,16 +12728,16 @@
         <v>727</v>
       </c>
       <c r="Z54" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="AA54" t="s">
-        <v>944</v>
+        <v>896</v>
       </c>
       <c r="AB54">
         <v>1</v>
       </c>
       <c r="AC54" t="s">
-        <v>593</v>
+        <v>627</v>
       </c>
     </row>
     <row r="55" spans="2:29">
@@ -12775,7 +12775,7 @@
         <v>5.0883040488922844E-2</v>
       </c>
       <c r="N55">
-        <v>0.127</v>
+        <v>0.15903352561533199</v>
       </c>
       <c r="P55" t="s">
         <v>638</v>
@@ -12805,16 +12805,16 @@
         <v>729</v>
       </c>
       <c r="Z55" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="AA55" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="AB55">
         <v>1</v>
       </c>
       <c r="AC55" t="s">
-        <v>483</v>
+        <v>601</v>
       </c>
     </row>
     <row r="56" spans="2:29">
@@ -12852,7 +12852,7 @@
         <v>0.19590972908047513</v>
       </c>
       <c r="N56">
-        <v>0.13300000000000001</v>
+        <v>0.1553957060744825</v>
       </c>
       <c r="P56" t="s">
         <v>638</v>
@@ -12882,16 +12882,16 @@
         <v>731</v>
       </c>
       <c r="Z56" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="AA56" t="s">
-        <v>876</v>
+        <v>945</v>
       </c>
       <c r="AB56">
         <v>1</v>
       </c>
       <c r="AC56" t="s">
-        <v>457</v>
+        <v>559</v>
       </c>
     </row>
     <row r="57" spans="2:29">
@@ -12929,7 +12929,7 @@
         <v>0.11947548286878279</v>
       </c>
       <c r="N57">
-        <v>0.13200000000000001</v>
+        <v>0.1577494444815174</v>
       </c>
       <c r="P57" t="s">
         <v>638</v>
@@ -12959,16 +12959,16 @@
         <v>733</v>
       </c>
       <c r="Z57" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="AA57" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="AB57">
         <v>1</v>
       </c>
       <c r="AC57" t="s">
-        <v>471</v>
+        <v>431</v>
       </c>
     </row>
     <row r="58" spans="2:29">
@@ -13006,7 +13006,7 @@
         <v>4.6317173753665682E-2</v>
       </c>
       <c r="N58">
-        <v>0.13700000000000001</v>
+        <v>0.16629632168082439</v>
       </c>
       <c r="P58" t="s">
         <v>638</v>
@@ -13036,16 +13036,16 @@
         <v>735</v>
       </c>
       <c r="Z58" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="AA58" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="AB58">
         <v>1</v>
       </c>
       <c r="AC58" t="s">
-        <v>479</v>
+        <v>603</v>
       </c>
     </row>
     <row r="59" spans="2:29">
@@ -13083,7 +13083,7 @@
         <v>3.9594516355816553E-2</v>
       </c>
       <c r="N59">
-        <v>0.14000000000000001</v>
+        <v>0.17846830537104069</v>
       </c>
       <c r="P59" t="s">
         <v>638</v>
@@ -13113,16 +13113,16 @@
         <v>737</v>
       </c>
       <c r="Z59" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="AA59" t="s">
-        <v>892</v>
+        <v>929</v>
       </c>
       <c r="AB59">
         <v>1</v>
       </c>
       <c r="AC59" t="s">
-        <v>507</v>
+        <v>619</v>
       </c>
     </row>
     <row r="60" spans="2:29">
@@ -13160,7 +13160,7 @@
         <v>0.14290794439401905</v>
       </c>
       <c r="N60">
-        <v>0.14699999999999999</v>
+        <v>0.18349581246367919</v>
       </c>
       <c r="P60" t="s">
         <v>638</v>
@@ -13190,16 +13190,16 @@
         <v>739</v>
       </c>
       <c r="Z60" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="AA60" t="s">
-        <v>895</v>
+        <v>952</v>
       </c>
       <c r="AB60">
         <v>1</v>
       </c>
       <c r="AC60" t="s">
-        <v>525</v>
+        <v>475</v>
       </c>
     </row>
     <row r="61" spans="2:29">
@@ -13237,7 +13237,7 @@
         <v>1.6883044643284366</v>
       </c>
       <c r="N61">
-        <v>0.153</v>
+        <v>0.1810434506623336</v>
       </c>
       <c r="P61" t="s">
         <v>638</v>
@@ -13267,16 +13267,16 @@
         <v>741</v>
       </c>
       <c r="Z61" t="s">
+        <v>953</v>
+      </c>
+      <c r="AA61" t="s">
         <v>954</v>
-      </c>
-      <c r="AA61" t="s">
-        <v>955</v>
       </c>
       <c r="AB61">
         <v>1</v>
       </c>
       <c r="AC61" t="s">
-        <v>545</v>
+        <v>417</v>
       </c>
     </row>
     <row r="62" spans="2:29">
@@ -13314,7 +13314,7 @@
         <v>0.73172300884955754</v>
       </c>
       <c r="N62">
-        <v>0.153</v>
+        <v>0.17801864377056181</v>
       </c>
       <c r="P62" t="s">
         <v>638</v>
@@ -13344,16 +13344,16 @@
         <v>743</v>
       </c>
       <c r="Z62" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="AA62" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="AB62">
         <v>1</v>
       </c>
       <c r="AC62" t="s">
-        <v>575</v>
+        <v>425</v>
       </c>
     </row>
     <row r="63" spans="2:29">
@@ -13391,7 +13391,7 @@
         <v>0.20511575842560806</v>
       </c>
       <c r="N63">
-        <v>0.158</v>
+        <v>0.17626727477474519</v>
       </c>
       <c r="P63" t="s">
         <v>638</v>
@@ -13421,16 +13421,16 @@
         <v>745</v>
       </c>
       <c r="Z63" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="AA63" t="s">
-        <v>959</v>
+        <v>890</v>
       </c>
       <c r="AB63">
         <v>1</v>
       </c>
       <c r="AC63" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
     </row>
     <row r="64" spans="2:29">
@@ -13468,7 +13468,7 @@
         <v>0.37186106307796413</v>
       </c>
       <c r="N64">
-        <v>0.154</v>
+        <v>0.1715058512290232</v>
       </c>
       <c r="P64" t="s">
         <v>638</v>
@@ -13498,16 +13498,16 @@
         <v>747</v>
       </c>
       <c r="Z64" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="AA64" t="s">
-        <v>961</v>
+        <v>927</v>
       </c>
       <c r="AB64">
         <v>1</v>
       </c>
       <c r="AC64" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
     </row>
     <row r="65" spans="2:29">
@@ -13545,7 +13545,7 @@
         <v>0.30803918175210271</v>
       </c>
       <c r="N65">
-        <v>0.159</v>
+        <v>0.1772104891094336</v>
       </c>
       <c r="P65" t="s">
         <v>638</v>
@@ -13575,16 +13575,16 @@
         <v>749</v>
       </c>
       <c r="Z65" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="AA65" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="AB65">
         <v>1</v>
       </c>
       <c r="AC65" t="s">
-        <v>607</v>
+        <v>587</v>
       </c>
     </row>
     <row r="66" spans="2:29">
@@ -13622,7 +13622,7 @@
         <v>0.29988733353510894</v>
       </c>
       <c r="N66">
-        <v>0.153</v>
+        <v>0.18804932960830359</v>
       </c>
       <c r="P66" t="s">
         <v>638</v>
@@ -13652,16 +13652,16 @@
         <v>751</v>
       </c>
       <c r="Z66" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="AA66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="AB66">
         <v>1</v>
       </c>
       <c r="AC66" t="s">
-        <v>463</v>
+        <v>545</v>
       </c>
     </row>
     <row r="67" spans="2:29">
@@ -13699,7 +13699,7 @@
         <v>0.28561500232955422</v>
       </c>
       <c r="N67">
-        <v>0.157</v>
+        <v>0.20333316960890149</v>
       </c>
       <c r="P67" t="s">
         <v>638</v>
@@ -13729,16 +13729,16 @@
         <v>753</v>
       </c>
       <c r="Z67" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="AA67" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="AB67">
         <v>1</v>
       </c>
       <c r="AC67" t="s">
-        <v>615</v>
+        <v>575</v>
       </c>
     </row>
     <row r="68" spans="2:29">
@@ -13776,7 +13776,7 @@
         <v>0.30068824497531293</v>
       </c>
       <c r="N68">
-        <v>0.152</v>
+        <v>0.20673244809741531</v>
       </c>
       <c r="P68" t="s">
         <v>638</v>
@@ -13806,16 +13806,16 @@
         <v>755</v>
       </c>
       <c r="Z68" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="AA68" t="s">
-        <v>911</v>
+        <v>965</v>
       </c>
       <c r="AB68">
         <v>1</v>
       </c>
       <c r="AC68" t="s">
-        <v>427</v>
+        <v>499</v>
       </c>
     </row>
     <row r="69" spans="2:29">
@@ -13853,7 +13853,7 @@
         <v>0.29701666312433583</v>
       </c>
       <c r="N69">
-        <v>0.14499999999999999</v>
+        <v>0.1866545188962094</v>
       </c>
       <c r="P69" t="s">
         <v>638</v>
@@ -13883,16 +13883,16 @@
         <v>757</v>
       </c>
       <c r="Z69" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="AA69" t="s">
-        <v>873</v>
+        <v>967</v>
       </c>
       <c r="AB69">
         <v>1</v>
       </c>
       <c r="AC69" t="s">
-        <v>451</v>
+        <v>563</v>
       </c>
     </row>
     <row r="70" spans="2:29">
@@ -13930,7 +13930,7 @@
         <v>0.31344650893374326</v>
       </c>
       <c r="N70">
-        <v>0.154</v>
+        <v>0.18754634838315079</v>
       </c>
       <c r="P70" t="s">
         <v>638</v>
@@ -13960,16 +13960,16 @@
         <v>759</v>
       </c>
       <c r="Z70" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="AA70" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="AB70">
         <v>1</v>
       </c>
       <c r="AC70" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
     </row>
     <row r="71" spans="2:29">
@@ -14007,7 +14007,7 @@
         <v>0.41278866461702979</v>
       </c>
       <c r="N71">
-        <v>0.159</v>
+        <v>0.18888135654523</v>
       </c>
       <c r="P71" t="s">
         <v>638</v>
@@ -14037,16 +14037,16 @@
         <v>761</v>
       </c>
       <c r="Z71" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="AA71" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="AB71">
         <v>1</v>
       </c>
       <c r="AC71" t="s">
-        <v>625</v>
+        <v>443</v>
       </c>
     </row>
     <row r="72" spans="2:29">
@@ -14084,7 +14084,7 @@
         <v>9.7877027980249234E-2</v>
       </c>
       <c r="N72">
-        <v>0.14699999999999999</v>
+        <v>0.19477300865565519</v>
       </c>
       <c r="P72" t="s">
         <v>638</v>
@@ -14114,16 +14114,16 @@
         <v>763</v>
       </c>
       <c r="Z72" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="AA72" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="AB72">
         <v>1</v>
       </c>
       <c r="AC72" t="s">
-        <v>635</v>
+        <v>613</v>
       </c>
     </row>
     <row r="73" spans="2:29">
@@ -14161,7 +14161,7 @@
         <v>0.94772990732113938</v>
       </c>
       <c r="N73">
-        <v>0.14399999999999999</v>
+        <v>0.19504090243261779</v>
       </c>
       <c r="P73" t="s">
         <v>638</v>
@@ -14191,16 +14191,16 @@
         <v>765</v>
       </c>
       <c r="Z73" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="AA73" t="s">
-        <v>976</v>
+        <v>939</v>
       </c>
       <c r="AB73">
         <v>1</v>
       </c>
       <c r="AC73" t="s">
-        <v>583</v>
+        <v>523</v>
       </c>
     </row>
     <row r="74" spans="2:29">
@@ -14238,7 +14238,7 @@
         <v>1.0879229879205814</v>
       </c>
       <c r="N74">
-        <v>0.13900000000000001</v>
+        <v>0.1847931993454644</v>
       </c>
       <c r="P74" t="s">
         <v>638</v>
@@ -14268,16 +14268,16 @@
         <v>767</v>
       </c>
       <c r="Z74" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="AA74" t="s">
-        <v>978</v>
+        <v>927</v>
       </c>
       <c r="AB74">
         <v>1</v>
       </c>
       <c r="AC74" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
     </row>
     <row r="75" spans="2:29">
@@ -14315,7 +14315,7 @@
         <v>1.3966906092660167</v>
       </c>
       <c r="N75">
-        <v>0.14000000000000001</v>
+        <v>0.1882783914412737</v>
       </c>
       <c r="P75" t="s">
         <v>638</v>
@@ -14345,16 +14345,16 @@
         <v>769</v>
       </c>
       <c r="Z75" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="AA75" t="s">
-        <v>892</v>
+        <v>977</v>
       </c>
       <c r="AB75">
         <v>1</v>
       </c>
       <c r="AC75" t="s">
-        <v>503</v>
+        <v>565</v>
       </c>
     </row>
     <row r="76" spans="2:29">
@@ -14392,7 +14392,7 @@
         <v>0.3516447630426125</v>
       </c>
       <c r="N76">
-        <v>0.14899999999999999</v>
+        <v>0.19928300422587439</v>
       </c>
       <c r="P76" t="s">
         <v>638</v>
@@ -14422,16 +14422,16 @@
         <v>771</v>
       </c>
       <c r="Z76" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="AA76" t="s">
-        <v>892</v>
+        <v>979</v>
       </c>
       <c r="AB76">
         <v>1</v>
       </c>
       <c r="AC76" t="s">
-        <v>505</v>
+        <v>445</v>
       </c>
     </row>
     <row r="77" spans="2:29">
@@ -14469,7 +14469,7 @@
         <v>3.8896792550439728E-2</v>
       </c>
       <c r="N77">
-        <v>0.14399999999999999</v>
+        <v>0.19490171491190181</v>
       </c>
       <c r="P77" t="s">
         <v>638</v>
@@ -14499,16 +14499,16 @@
         <v>773</v>
       </c>
       <c r="Z77" t="s">
+        <v>980</v>
+      </c>
+      <c r="AA77" t="s">
         <v>981</v>
-      </c>
-      <c r="AA77" t="s">
-        <v>915</v>
       </c>
       <c r="AB77">
         <v>1</v>
       </c>
       <c r="AC77" t="s">
-        <v>551</v>
+        <v>459</v>
       </c>
     </row>
     <row r="78" spans="2:29">
@@ -14546,7 +14546,7 @@
         <v>0.68572700622938809</v>
       </c>
       <c r="N78">
-        <v>0.14599999999999999</v>
+        <v>0.1918406123485808</v>
       </c>
       <c r="P78" t="s">
         <v>638</v>
@@ -14579,13 +14579,13 @@
         <v>982</v>
       </c>
       <c r="AA78" t="s">
-        <v>957</v>
+        <v>983</v>
       </c>
       <c r="AB78">
         <v>1</v>
       </c>
       <c r="AC78" t="s">
-        <v>577</v>
+        <v>441</v>
       </c>
     </row>
     <row r="79" spans="2:29">
@@ -14623,7 +14623,7 @@
         <v>2.4847081967213112</v>
       </c>
       <c r="N79">
-        <v>0.14099999999999999</v>
+        <v>0.18817034082125389</v>
       </c>
       <c r="P79" t="s">
         <v>638</v>
@@ -14653,16 +14653,16 @@
         <v>777</v>
       </c>
       <c r="Z79" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="AA79" t="s">
-        <v>984</v>
+        <v>952</v>
       </c>
       <c r="AB79">
         <v>1</v>
       </c>
       <c r="AC79" t="s">
-        <v>585</v>
+        <v>477</v>
       </c>
     </row>
     <row r="80" spans="2:29">
@@ -14700,7 +14700,7 @@
         <v>0.70525998874507589</v>
       </c>
       <c r="N80">
-        <v>0.14399999999999999</v>
+        <v>0.1881784132319477</v>
       </c>
       <c r="P80" t="s">
         <v>638</v>
@@ -14733,13 +14733,13 @@
         <v>985</v>
       </c>
       <c r="AA80" t="s">
-        <v>986</v>
+        <v>939</v>
       </c>
       <c r="AB80">
         <v>1</v>
       </c>
       <c r="AC80" t="s">
-        <v>429</v>
+        <v>535</v>
       </c>
     </row>
     <row r="81" spans="2:29">
@@ -14777,7 +14777,7 @@
         <v>0.50615648399866453</v>
       </c>
       <c r="N81">
-        <v>0.14599999999999999</v>
+        <v>0.1923189742630973</v>
       </c>
       <c r="P81" t="s">
         <v>638</v>
@@ -14807,16 +14807,16 @@
         <v>781</v>
       </c>
       <c r="Z81" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AA81" t="s">
-        <v>988</v>
+        <v>881</v>
       </c>
       <c r="AB81">
         <v>1</v>
       </c>
       <c r="AC81" t="s">
-        <v>415</v>
+        <v>543</v>
       </c>
     </row>
     <row r="82" spans="2:29">
@@ -14854,7 +14854,7 @@
         <v>1.0371829595552999</v>
       </c>
       <c r="N82">
-        <v>0.14299999999999999</v>
+        <v>0.190719214279644</v>
       </c>
       <c r="P82" t="s">
         <v>638</v>
@@ -14884,16 +14884,16 @@
         <v>783</v>
       </c>
       <c r="Z82" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="AA82" t="s">
-        <v>888</v>
+        <v>988</v>
       </c>
       <c r="AB82">
         <v>1</v>
       </c>
       <c r="AC82" t="s">
-        <v>413</v>
+        <v>567</v>
       </c>
     </row>
     <row r="83" spans="2:29">
@@ -14931,7 +14931,7 @@
         <v>1.8082457454050376</v>
       </c>
       <c r="N83">
-        <v>0.14099999999999999</v>
+        <v>0.1874326386506274</v>
       </c>
       <c r="P83" t="s">
         <v>638</v>
@@ -14961,16 +14961,16 @@
         <v>785</v>
       </c>
       <c r="Z83" t="s">
+        <v>989</v>
+      </c>
+      <c r="AA83" t="s">
         <v>990</v>
-      </c>
-      <c r="AA83" t="s">
-        <v>878</v>
       </c>
       <c r="AB83">
         <v>1</v>
       </c>
       <c r="AC83" t="s">
-        <v>467</v>
+        <v>591</v>
       </c>
     </row>
     <row r="84" spans="2:29">
@@ -15008,7 +15008,7 @@
         <v>1.4964056980056981</v>
       </c>
       <c r="N84">
-        <v>0.13900000000000001</v>
+        <v>0.18752576846680499</v>
       </c>
       <c r="P84" t="s">
         <v>638</v>
@@ -15041,13 +15041,13 @@
         <v>991</v>
       </c>
       <c r="AA84" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="AB84">
         <v>1</v>
       </c>
       <c r="AC84" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="85" spans="2:29">
@@ -15085,7 +15085,7 @@
         <v>0.29758299938711047</v>
       </c>
       <c r="N85">
-        <v>0.14199999999999999</v>
+        <v>0.1934945871321376</v>
       </c>
       <c r="P85" t="s">
         <v>638</v>
@@ -15118,13 +15118,13 @@
         <v>992</v>
       </c>
       <c r="AA85" t="s">
-        <v>924</v>
+        <v>993</v>
       </c>
       <c r="AB85">
         <v>1</v>
       </c>
       <c r="AC85" t="s">
-        <v>515</v>
+        <v>629</v>
       </c>
     </row>
     <row r="86" spans="2:29">
@@ -15162,7 +15162,7 @@
         <v>0.13649542759521657</v>
       </c>
       <c r="N86">
-        <v>0.14000000000000001</v>
+        <v>0.19345578389302029</v>
       </c>
       <c r="P86" t="s">
         <v>638</v>
@@ -15192,16 +15192,16 @@
         <v>791</v>
       </c>
       <c r="Z86" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="AA86" t="s">
-        <v>926</v>
+        <v>995</v>
       </c>
       <c r="AB86">
         <v>1</v>
       </c>
       <c r="AC86" t="s">
-        <v>539</v>
+        <v>463</v>
       </c>
     </row>
     <row r="87" spans="2:29">
@@ -15239,7 +15239,7 @@
         <v>1.1263374349266444</v>
       </c>
       <c r="N87">
-        <v>0.14299999999999999</v>
+        <v>0.18629736837172881</v>
       </c>
       <c r="P87" t="s">
         <v>638</v>
@@ -15269,16 +15269,16 @@
         <v>793</v>
       </c>
       <c r="Z87" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="AA87" t="s">
-        <v>895</v>
+        <v>997</v>
       </c>
       <c r="AB87">
         <v>1</v>
       </c>
       <c r="AC87" t="s">
-        <v>541</v>
+        <v>615</v>
       </c>
     </row>
     <row r="88" spans="2:29">
@@ -15316,7 +15316,7 @@
         <v>0.87306069000251829</v>
       </c>
       <c r="N88">
-        <v>0.14199999999999999</v>
+        <v>0.18642682541457509</v>
       </c>
       <c r="P88" t="s">
         <v>638</v>
@@ -15346,16 +15346,16 @@
         <v>795</v>
       </c>
       <c r="Z88" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="AA88" t="s">
-        <v>996</v>
+        <v>954</v>
       </c>
       <c r="AB88">
         <v>1</v>
       </c>
       <c r="AC88" t="s">
-        <v>573</v>
+        <v>427</v>
       </c>
     </row>
     <row r="89" spans="2:29">
@@ -15393,7 +15393,7 @@
         <v>1.4924229506514826</v>
       </c>
       <c r="N89">
-        <v>0.15</v>
+        <v>0.18554162964315521</v>
       </c>
       <c r="P89" t="s">
         <v>638</v>
@@ -15423,16 +15423,16 @@
         <v>797</v>
       </c>
       <c r="Z89" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="AA89" t="s">
-        <v>878</v>
+        <v>901</v>
       </c>
       <c r="AB89">
         <v>1</v>
       </c>
       <c r="AC89" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
     </row>
     <row r="90" spans="2:29">
@@ -15470,7 +15470,7 @@
         <v>1.6595090666157664</v>
       </c>
       <c r="N90">
-        <v>0.14199999999999999</v>
+        <v>0.1798877801063401</v>
       </c>
       <c r="P90" t="s">
         <v>638</v>
@@ -15500,7 +15500,7 @@
         <v>799</v>
       </c>
       <c r="Z90" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="AA90" t="s">
         <v>973</v>
@@ -15509,7 +15509,7 @@
         <v>1</v>
       </c>
       <c r="AC90" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
     </row>
     <row r="91" spans="2:29">
@@ -15547,7 +15547,7 @@
         <v>0.91353583678560302</v>
       </c>
       <c r="N91">
-        <v>0.13800000000000001</v>
+        <v>0.17401419334752691</v>
       </c>
       <c r="P91" t="s">
         <v>638</v>
@@ -15577,16 +15577,16 @@
         <v>801</v>
       </c>
       <c r="Z91" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="AA91" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="AB91">
         <v>1</v>
       </c>
       <c r="AC91" t="s">
-        <v>565</v>
+        <v>625</v>
       </c>
     </row>
     <row r="92" spans="2:29">
@@ -15624,7 +15624,7 @@
         <v>1.9218525438809348</v>
       </c>
       <c r="N92">
-        <v>0.13600000000000001</v>
+        <v>0.17272205362473819</v>
       </c>
       <c r="P92" t="s">
         <v>638</v>
@@ -15654,16 +15654,16 @@
         <v>803</v>
       </c>
       <c r="Z92" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="AA92" t="s">
-        <v>1002</v>
+        <v>973</v>
       </c>
       <c r="AB92">
         <v>1</v>
       </c>
       <c r="AC92" t="s">
-        <v>445</v>
+        <v>635</v>
       </c>
     </row>
     <row r="93" spans="2:29">
@@ -15701,7 +15701,7 @@
         <v>2.6664638115074197</v>
       </c>
       <c r="N93">
-        <v>0.13800000000000001</v>
+        <v>0.1746226826189459</v>
       </c>
       <c r="P93" t="s">
         <v>638</v>
@@ -15740,7 +15740,7 @@
         <v>1</v>
       </c>
       <c r="AC93" t="s">
-        <v>459</v>
+        <v>583</v>
       </c>
     </row>
     <row r="94" spans="2:29">
@@ -15778,7 +15778,7 @@
         <v>3.2425434108178592</v>
       </c>
       <c r="N94">
-        <v>0.14299999999999999</v>
+        <v>0.17737054888906281</v>
       </c>
       <c r="P94" t="s">
         <v>638</v>
@@ -15817,7 +15817,7 @@
         <v>1</v>
       </c>
       <c r="AC94" t="s">
-        <v>441</v>
+        <v>521</v>
       </c>
     </row>
     <row r="95" spans="2:29">
@@ -15855,7 +15855,7 @@
         <v>3.4158610392663999</v>
       </c>
       <c r="N95">
-        <v>0.14299999999999999</v>
+        <v>0.18193387342271519</v>
       </c>
       <c r="P95" t="s">
         <v>638</v>
@@ -15888,13 +15888,13 @@
         <v>1007</v>
       </c>
       <c r="AA95" t="s">
-        <v>909</v>
+        <v>892</v>
       </c>
       <c r="AB95">
         <v>1</v>
       </c>
       <c r="AC95" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
     </row>
     <row r="96" spans="2:29">
@@ -15932,7 +15932,7 @@
         <v>1.9731233650822586</v>
       </c>
       <c r="N96">
-        <v>0.14099999999999999</v>
+        <v>0.18606412330448721</v>
       </c>
       <c r="P96" t="s">
         <v>638</v>
@@ -15965,13 +15965,13 @@
         <v>1008</v>
       </c>
       <c r="AA96" t="s">
-        <v>1009</v>
+        <v>892</v>
       </c>
       <c r="AB96">
         <v>1</v>
       </c>
       <c r="AC96" t="s">
-        <v>535</v>
+        <v>505</v>
       </c>
     </row>
     <row r="97" spans="2:29">
@@ -16009,7 +16009,7 @@
         <v>0.12604571651851129</v>
       </c>
       <c r="N97">
-        <v>0.14599999999999999</v>
+        <v>0.1928107369460893</v>
       </c>
       <c r="P97" t="s">
         <v>638</v>
@@ -16039,16 +16039,16 @@
         <v>813</v>
       </c>
       <c r="Z97" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AA97" t="s">
-        <v>895</v>
+        <v>927</v>
       </c>
       <c r="AB97">
         <v>1</v>
       </c>
       <c r="AC97" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
     </row>
     <row r="98" spans="2:29">
@@ -16086,7 +16086,7 @@
         <v>9.2643811394891959E-2</v>
       </c>
       <c r="N98">
-        <v>0.14699999999999999</v>
+        <v>0.1988430077084001</v>
       </c>
       <c r="P98" t="s">
         <v>638</v>
@@ -16116,16 +16116,16 @@
         <v>815</v>
       </c>
       <c r="Z98" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="AA98" t="s">
-        <v>1012</v>
+        <v>963</v>
       </c>
       <c r="AB98">
         <v>1</v>
       </c>
       <c r="AC98" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
     </row>
     <row r="99" spans="2:29">
@@ -16163,7 +16163,7 @@
         <v>1.5717994938680162</v>
       </c>
       <c r="N99">
-        <v>0.14599999999999999</v>
+        <v>0.1875341362232876</v>
       </c>
       <c r="P99" t="s">
         <v>638</v>
@@ -16193,16 +16193,16 @@
         <v>817</v>
       </c>
       <c r="Z99" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="AA99" t="s">
-        <v>1014</v>
+        <v>905</v>
       </c>
       <c r="AB99">
         <v>1</v>
       </c>
       <c r="AC99" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
     </row>
     <row r="100" spans="2:29">
@@ -16240,7 +16240,7 @@
         <v>2.2859931055155878</v>
       </c>
       <c r="N100">
-        <v>0.13700000000000001</v>
+        <v>0.1817955766772078</v>
       </c>
       <c r="P100" t="s">
         <v>638</v>
@@ -16270,16 +16270,16 @@
         <v>819</v>
       </c>
       <c r="Z100" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="AA100" t="s">
-        <v>892</v>
+        <v>1013</v>
       </c>
       <c r="AB100">
         <v>1</v>
       </c>
       <c r="AC100" t="s">
-        <v>519</v>
+        <v>571</v>
       </c>
     </row>
     <row r="101" spans="2:29">
@@ -16317,7 +16317,7 @@
         <v>2.8468676499412</v>
       </c>
       <c r="N101">
-        <v>0.13600000000000001</v>
+        <v>0.17887065851836809</v>
       </c>
       <c r="P101" t="s">
         <v>638</v>
@@ -16347,16 +16347,16 @@
         <v>821</v>
       </c>
       <c r="Z101" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="AA101" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="AB101">
         <v>1</v>
       </c>
       <c r="AC101" t="s">
-        <v>553</v>
+        <v>447</v>
       </c>
     </row>
     <row r="102" spans="2:29">
@@ -16394,7 +16394,7 @@
         <v>2.5368718693284942</v>
       </c>
       <c r="N102">
-        <v>0.13900000000000001</v>
+        <v>0.1785609472675386</v>
       </c>
       <c r="P102" t="s">
         <v>638</v>
@@ -16424,16 +16424,16 @@
         <v>823</v>
       </c>
       <c r="Z102" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="AA102" t="s">
-        <v>1019</v>
+        <v>947</v>
       </c>
       <c r="AB102">
         <v>1</v>
       </c>
       <c r="AC102" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
     </row>
     <row r="103" spans="2:29">
@@ -16471,7 +16471,7 @@
         <v>1.1499075064463757</v>
       </c>
       <c r="N103">
-        <v>0.14399999999999999</v>
+        <v>0.1778047148773034</v>
       </c>
       <c r="P103" t="s">
         <v>638</v>
@@ -16501,16 +16501,16 @@
         <v>825</v>
       </c>
       <c r="Z103" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="AA103" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="AB103">
         <v>1</v>
       </c>
       <c r="AC103" t="s">
-        <v>423</v>
+        <v>529</v>
       </c>
     </row>
     <row r="104" spans="2:29">
@@ -16548,7 +16548,7 @@
         <v>0.84996737244012499</v>
       </c>
       <c r="N104">
-        <v>0.14499999999999999</v>
+        <v>0.1743718002763128</v>
       </c>
       <c r="P104" t="s">
         <v>638</v>
@@ -16578,16 +16578,16 @@
         <v>827</v>
       </c>
       <c r="Z104" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="AA104" t="s">
-        <v>924</v>
+        <v>879</v>
       </c>
       <c r="AB104">
         <v>1</v>
       </c>
       <c r="AC104" t="s">
-        <v>501</v>
+        <v>557</v>
       </c>
     </row>
     <row r="105" spans="2:29">
@@ -16625,7 +16625,7 @@
         <v>2.2978835646329756</v>
       </c>
       <c r="N105">
-        <v>0.14199999999999999</v>
+        <v>0.17510488722751641</v>
       </c>
       <c r="P105" t="s">
         <v>638</v>
@@ -16655,16 +16655,16 @@
         <v>829</v>
       </c>
       <c r="Z105" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="AA105" t="s">
-        <v>892</v>
+        <v>1013</v>
       </c>
       <c r="AB105">
         <v>1</v>
       </c>
       <c r="AC105" t="s">
-        <v>509</v>
+        <v>569</v>
       </c>
     </row>
     <row r="106" spans="2:29">
@@ -16702,7 +16702,7 @@
         <v>2.6083367937447544</v>
       </c>
       <c r="N106">
-        <v>0.14099999999999999</v>
+        <v>0.1810377185650367</v>
       </c>
       <c r="P106" t="s">
         <v>638</v>
@@ -16732,16 +16732,16 @@
         <v>831</v>
       </c>
       <c r="Z106" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="AA106" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="AB106">
         <v>1</v>
       </c>
       <c r="AC106" t="s">
-        <v>589</v>
+        <v>623</v>
       </c>
     </row>
     <row r="107" spans="2:29">
@@ -16779,7 +16779,7 @@
         <v>1.9197678295087768</v>
       </c>
       <c r="N107">
-        <v>0.14199999999999999</v>
+        <v>0.18796302969675899</v>
       </c>
       <c r="P107" t="s">
         <v>638</v>
@@ -16809,16 +16809,16 @@
         <v>833</v>
       </c>
       <c r="Z107" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="AA107" t="s">
-        <v>1025</v>
+        <v>892</v>
       </c>
       <c r="AB107">
         <v>1</v>
       </c>
       <c r="AC107" t="s">
-        <v>443</v>
+        <v>519</v>
       </c>
     </row>
     <row r="108" spans="2:29">
@@ -16856,7 +16856,7 @@
         <v>0.42314333158538719</v>
       </c>
       <c r="N108">
-        <v>0.14099999999999999</v>
+        <v>0.19460235000797091</v>
       </c>
       <c r="P108" t="s">
         <v>638</v>
@@ -16886,16 +16886,16 @@
         <v>835</v>
       </c>
       <c r="Z108" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="AA108" t="s">
-        <v>971</v>
+        <v>1024</v>
       </c>
       <c r="AB108">
         <v>1</v>
       </c>
       <c r="AC108" t="s">
-        <v>613</v>
+        <v>553</v>
       </c>
     </row>
     <row r="109" spans="2:29">
@@ -16933,7 +16933,7 @@
         <v>7.2256648997464853E-2</v>
       </c>
       <c r="N109">
-        <v>0.14499999999999999</v>
+        <v>0.19996746694328421</v>
       </c>
       <c r="P109" t="s">
         <v>638</v>
@@ -16963,16 +16963,16 @@
         <v>837</v>
       </c>
       <c r="Z109" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="AA109" t="s">
-        <v>1009</v>
+        <v>1026</v>
       </c>
       <c r="AB109">
         <v>1</v>
       </c>
       <c r="AC109" t="s">
-        <v>523</v>
+        <v>419</v>
       </c>
     </row>
     <row r="110" spans="2:29">
@@ -17010,7 +17010,7 @@
         <v>2.1082473283960437</v>
       </c>
       <c r="N110">
-        <v>0.14599999999999999</v>
+        <v>0.18949475630306259</v>
       </c>
       <c r="P110" t="s">
         <v>638</v>
@@ -17040,16 +17040,16 @@
         <v>839</v>
       </c>
       <c r="Z110" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AA110" t="s">
-        <v>915</v>
+        <v>871</v>
       </c>
       <c r="AB110">
         <v>1</v>
       </c>
       <c r="AC110" t="s">
-        <v>537</v>
+        <v>423</v>
       </c>
     </row>
     <row r="111" spans="2:29">
@@ -17087,7 +17087,7 @@
         <v>3.1372171043831094</v>
       </c>
       <c r="N111">
-        <v>0.14899999999999999</v>
+        <v>0.18701929618415999</v>
       </c>
       <c r="P111" t="s">
         <v>638</v>
@@ -17117,16 +17117,16 @@
         <v>841</v>
       </c>
       <c r="Z111" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AA111" t="s">
-        <v>1030</v>
+        <v>877</v>
       </c>
       <c r="AB111">
         <v>1</v>
       </c>
       <c r="AC111" t="s">
-        <v>473</v>
+        <v>501</v>
       </c>
     </row>
     <row r="112" spans="2:29">
@@ -17164,7 +17164,7 @@
         <v>1.4572588588588591</v>
       </c>
       <c r="N112">
-        <v>0.14899999999999999</v>
+        <v>0.18122662352562571</v>
       </c>
       <c r="P112" t="s">
         <v>638</v>
@@ -17194,16 +17194,16 @@
         <v>843</v>
       </c>
       <c r="Z112" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="AA112" t="s">
-        <v>873</v>
+        <v>892</v>
       </c>
       <c r="AB112">
         <v>1</v>
       </c>
       <c r="AC112" t="s">
-        <v>437</v>
+        <v>509</v>
       </c>
     </row>
     <row r="113" spans="2:29">
@@ -17241,7 +17241,7 @@
         <v>0.63977956915789957</v>
       </c>
       <c r="N113">
-        <v>0.14299999999999999</v>
+        <v>0.17615242521582869</v>
       </c>
       <c r="P113" t="s">
         <v>638</v>
@@ -17271,16 +17271,16 @@
         <v>845</v>
       </c>
       <c r="Z113" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="AA113" t="s">
-        <v>1033</v>
+        <v>990</v>
       </c>
       <c r="AB113">
         <v>1</v>
       </c>
       <c r="AC113" t="s">
-        <v>453</v>
+        <v>589</v>
       </c>
     </row>
     <row r="114" spans="2:29">
@@ -17318,7 +17318,7 @@
         <v>1.5388714007112541</v>
       </c>
       <c r="N114">
-        <v>0.14199999999999999</v>
+        <v>0.17633075864071929</v>
       </c>
       <c r="P114" t="s">
         <v>638</v>
@@ -17348,16 +17348,16 @@
         <v>847</v>
       </c>
       <c r="Z114" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="AA114" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="AB114">
         <v>1</v>
       </c>
       <c r="AC114" t="s">
-        <v>531</v>
+        <v>599</v>
       </c>
     </row>
     <row r="115" spans="2:29">
@@ -17395,7 +17395,7 @@
         <v>1.7137119163653516</v>
       </c>
       <c r="N115">
-        <v>0.14899999999999999</v>
+        <v>0.1868255198840435</v>
       </c>
       <c r="P115" t="s">
         <v>638</v>
@@ -17425,16 +17425,16 @@
         <v>849</v>
       </c>
       <c r="Z115" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="AA115" t="s">
-        <v>1009</v>
+        <v>1034</v>
       </c>
       <c r="AB115">
         <v>1</v>
       </c>
       <c r="AC115" t="s">
-        <v>533</v>
+        <v>621</v>
       </c>
     </row>
     <row r="116" spans="2:29">
@@ -17472,7 +17472,7 @@
         <v>1.2400799329234209</v>
       </c>
       <c r="N116">
-        <v>0.14599999999999999</v>
+        <v>0.17976064651049189</v>
       </c>
       <c r="P116" t="s">
         <v>638</v>
@@ -17502,16 +17502,16 @@
         <v>851</v>
       </c>
       <c r="Z116" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="AA116" t="s">
-        <v>895</v>
+        <v>1036</v>
       </c>
       <c r="AB116">
         <v>1</v>
       </c>
       <c r="AC116" t="s">
-        <v>561</v>
+        <v>593</v>
       </c>
     </row>
     <row r="117" spans="2:29">
@@ -17549,7 +17549,7 @@
         <v>0.78886030623122383</v>
       </c>
       <c r="N117">
-        <v>0.14199999999999999</v>
+        <v>0.17757040204047719</v>
       </c>
       <c r="P117" t="s">
         <v>638</v>
@@ -17579,16 +17579,16 @@
         <v>853</v>
       </c>
       <c r="Z117" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AA117" t="s">
         <v>1038</v>
-      </c>
-      <c r="AA117" t="s">
-        <v>897</v>
       </c>
       <c r="AB117">
         <v>1</v>
       </c>
       <c r="AC117" t="s">
-        <v>627</v>
+        <v>483</v>
       </c>
     </row>
     <row r="118" spans="2:29">
@@ -17626,7 +17626,7 @@
         <v>0.42002997002997006</v>
       </c>
       <c r="N118">
-        <v>0.14799999999999999</v>
+        <v>0.18640358727154679</v>
       </c>
       <c r="P118" t="s">
         <v>638</v>
@@ -17659,13 +17659,13 @@
         <v>1039</v>
       </c>
       <c r="AA118" t="s">
-        <v>1040</v>
+        <v>915</v>
       </c>
       <c r="AB118">
         <v>1</v>
       </c>
       <c r="AC118" t="s">
-        <v>605</v>
+        <v>457</v>
       </c>
     </row>
     <row r="119" spans="2:29">
@@ -17703,7 +17703,7 @@
         <v>1.1156741926264646</v>
       </c>
       <c r="N119">
-        <v>0.14699999999999999</v>
+        <v>0.18218348485866609</v>
       </c>
       <c r="P119" t="s">
         <v>638</v>
@@ -17733,16 +17733,16 @@
         <v>857</v>
       </c>
       <c r="Z119" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AA119" t="s">
         <v>1041</v>
-      </c>
-      <c r="AA119" t="s">
-        <v>880</v>
       </c>
       <c r="AB119">
         <v>1</v>
       </c>
       <c r="AC119" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
     </row>
     <row r="120" spans="2:29">
@@ -17780,7 +17780,7 @@
         <v>0.35205544710912801</v>
       </c>
       <c r="N120">
-        <v>0.14499999999999999</v>
+        <v>0.1892175571183716</v>
       </c>
       <c r="P120" t="s">
         <v>638</v>
@@ -17813,13 +17813,13 @@
         <v>1042</v>
       </c>
       <c r="AA120" t="s">
-        <v>873</v>
+        <v>1043</v>
       </c>
       <c r="AB120">
         <v>1</v>
       </c>
       <c r="AC120" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
     </row>
     <row r="121" spans="2:29">
@@ -17857,7 +17857,7 @@
         <v>0.19172951780081116</v>
       </c>
       <c r="N121">
-        <v>0.14399999999999999</v>
+        <v>0.20317368116064699</v>
       </c>
       <c r="P121" t="s">
         <v>638</v>
@@ -17887,16 +17887,16 @@
         <v>861</v>
       </c>
       <c r="Z121" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="AA121" t="s">
-        <v>1044</v>
+        <v>892</v>
       </c>
       <c r="AB121">
         <v>1</v>
       </c>
       <c r="AC121" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="122" spans="2:29">
@@ -17934,7 +17934,7 @@
         <v>0.25543345461509004</v>
       </c>
       <c r="N122">
-        <v>0.13100000000000001</v>
+        <v>0</v>
       </c>
       <c r="P122" t="s">
         <v>638</v>
@@ -17967,13 +17967,13 @@
         <v>1045</v>
       </c>
       <c r="AA122" t="s">
-        <v>984</v>
+        <v>881</v>
       </c>
       <c r="AB122">
         <v>1</v>
       </c>
       <c r="AC122" t="s">
-        <v>609</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -17982,7 +17982,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12950C22-246D-49EE-A883-6BB6FB18CC50}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{950BAC83-497F-44DB-B630-1E2643EC1D18}">
   <dimension ref="B9:AB123"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18147,7 +18147,7 @@
         <v>0.29315311993517018</v>
       </c>
       <c r="N12">
-        <v>0.44</v>
+        <v>0.46139408924877429</v>
       </c>
     </row>
     <row r="13" spans="2:28">
@@ -18185,7 +18185,7 @@
         <v>0.17653996336853592</v>
       </c>
       <c r="N13">
-        <v>0.41399999999999998</v>
+        <v>0.32754239945258851</v>
       </c>
     </row>
     <row r="14" spans="2:28">
@@ -18223,7 +18223,7 @@
         <v>5.0536971385160799E-2</v>
       </c>
       <c r="N14">
-        <v>0.317</v>
+        <v>0.42436113531403008</v>
       </c>
     </row>
     <row r="15" spans="2:28">
@@ -18261,7 +18261,7 @@
         <v>1.5227814726304616</v>
       </c>
       <c r="N15">
-        <v>0.48199999999999998</v>
+        <v>0.60163848656146757</v>
       </c>
     </row>
     <row r="16" spans="2:28">
@@ -18299,7 +18299,7 @@
         <v>2.9373730440432126</v>
       </c>
       <c r="N16">
-        <v>0.34599999999999997</v>
+        <v>0.27555787919636771</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -18337,7 +18337,7 @@
         <v>2.2909825950121596</v>
       </c>
       <c r="N17">
-        <v>0.35499999999999998</v>
+        <v>0.1806749074504779</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -18375,7 +18375,7 @@
         <v>0.50346061469511671</v>
       </c>
       <c r="N18">
-        <v>0.34499999999999997</v>
+        <v>0.16575353549747379</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -18413,7 +18413,7 @@
         <v>4.6736011131187617E-2</v>
       </c>
       <c r="N19">
-        <v>0.247</v>
+        <v>0.23146508047071901</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -18451,7 +18451,7 @@
         <v>3.2713256277014229</v>
       </c>
       <c r="N20">
-        <v>0.436</v>
+        <v>0.47272629859141818</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -18489,7 +18489,7 @@
         <v>7.1636306481630978</v>
       </c>
       <c r="N21">
-        <v>0.38800000000000001</v>
+        <v>0.29996245810983668</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -18527,7 +18527,7 @@
         <v>5.0292835622927523</v>
       </c>
       <c r="N22">
-        <v>0.35099999999999998</v>
+        <v>0.19778952387708471</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -18565,7 +18565,7 @@
         <v>1.2630972533442733</v>
       </c>
       <c r="N23">
-        <v>0.33600000000000002</v>
+        <v>9.1515511879042902E-2</v>
       </c>
     </row>
     <row r="24" spans="2:14">
@@ -18603,7 +18603,7 @@
         <v>0.61407741935483873</v>
       </c>
       <c r="N24">
-        <v>0.28999999999999998</v>
+        <v>4.4846596641398999E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14">
@@ -18641,7 +18641,7 @@
         <v>0.32915614713038505</v>
       </c>
       <c r="N25">
-        <v>0.27200000000000002</v>
+        <v>0.14036910787945889</v>
       </c>
     </row>
     <row r="26" spans="2:14">
@@ -18679,7 +18679,7 @@
         <v>2.8281593330904302</v>
       </c>
       <c r="N26">
-        <v>0.42799999999999999</v>
+        <v>0.43764790254914299</v>
       </c>
     </row>
     <row r="27" spans="2:14">
@@ -18717,7 +18717,7 @@
         <v>7.1955351335795479</v>
       </c>
       <c r="N27">
-        <v>0.38500000000000001</v>
+        <v>0.27321129547657219</v>
       </c>
     </row>
     <row r="28" spans="2:14">
@@ -18755,7 +18755,7 @@
         <v>6.2791378627252978</v>
       </c>
       <c r="N28">
-        <v>0.35</v>
+        <v>0.1424264847625058</v>
       </c>
     </row>
     <row r="29" spans="2:14">
@@ -18793,7 +18793,7 @@
         <v>5.225973673342315</v>
       </c>
       <c r="N29">
-        <v>0.32900000000000001</v>
+        <v>6.1241439911996598E-2</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -18831,7 +18831,7 @@
         <v>3.0036495791900775</v>
       </c>
       <c r="N30">
-        <v>0.314</v>
+        <v>3.6938619415704803E-2</v>
       </c>
     </row>
     <row r="31" spans="2:14">
@@ -18869,7 +18869,7 @@
         <v>0.28229021331136134</v>
       </c>
       <c r="N31">
-        <v>0.35599999999999998</v>
+        <v>4.2827392461605801E-2</v>
       </c>
     </row>
     <row r="32" spans="2:14">
@@ -18907,7 +18907,7 @@
         <v>0.14953202746110725</v>
       </c>
       <c r="N32">
-        <v>0.17399999999999999</v>
+        <v>0.1243856175852211</v>
       </c>
     </row>
     <row r="33" spans="2:14">
@@ -18945,7 +18945,7 @@
         <v>4.1297760104255925</v>
       </c>
       <c r="N33">
-        <v>0.35199999999999998</v>
+        <v>0.30750940156351991</v>
       </c>
     </row>
     <row r="34" spans="2:14">
@@ -18983,7 +18983,7 @@
         <v>7.0071176710508372</v>
       </c>
       <c r="N34">
-        <v>0.36799999999999999</v>
+        <v>0.18008776035108889</v>
       </c>
     </row>
     <row r="35" spans="2:14">
@@ -19021,7 +19021,7 @@
         <v>6.0734879597057638</v>
       </c>
       <c r="N35">
-        <v>0.26600000000000001</v>
+        <v>0.1066232689284307</v>
       </c>
     </row>
     <row r="36" spans="2:14">
@@ -19059,7 +19059,7 @@
         <v>4.8470369741425436</v>
       </c>
       <c r="N36">
-        <v>0.30399999999999999</v>
+        <v>6.24575653340931E-2</v>
       </c>
     </row>
     <row r="37" spans="2:14">
@@ -19097,7 +19097,7 @@
         <v>2.1179039326537943</v>
       </c>
       <c r="N37">
-        <v>0.27100000000000002</v>
+        <v>4.3436431935682099E-2</v>
       </c>
     </row>
     <row r="38" spans="2:14">
@@ -19135,7 +19135,7 @@
         <v>0.82911999599837305</v>
       </c>
       <c r="N38">
-        <v>0.313</v>
+        <v>5.7464980163372599E-2</v>
       </c>
     </row>
     <row r="39" spans="2:14">
@@ -19173,7 +19173,7 @@
         <v>0.4428774743172138</v>
       </c>
       <c r="N39">
-        <v>0.187</v>
+        <v>0.12801907091054901</v>
       </c>
     </row>
     <row r="40" spans="2:14">
@@ -19211,7 +19211,7 @@
         <v>2.8599768220009341</v>
       </c>
       <c r="N40">
-        <v>0.34599999999999997</v>
+        <v>0.31067405332712078</v>
       </c>
     </row>
     <row r="41" spans="2:14">
@@ -19249,7 +19249,7 @@
         <v>4.6435315630834797</v>
       </c>
       <c r="N41">
-        <v>0.316</v>
+        <v>0.19897621008103311</v>
       </c>
     </row>
     <row r="42" spans="2:14">
@@ -19287,7 +19287,7 @@
         <v>4.7938972204844053</v>
       </c>
       <c r="N42">
-        <v>0.28499999999999998</v>
+        <v>0.1151133702039025</v>
       </c>
     </row>
     <row r="43" spans="2:14">
@@ -19325,7 +19325,7 @@
         <v>4.4633448443579766</v>
       </c>
       <c r="N43">
-        <v>0.23300000000000001</v>
+        <v>5.9736148589859699E-2</v>
       </c>
     </row>
     <row r="44" spans="2:14">
@@ -19363,7 +19363,7 @@
         <v>3.0872082101916476</v>
       </c>
       <c r="N44">
-        <v>0.23300000000000001</v>
+        <v>5.3471671276954597E-2</v>
       </c>
     </row>
     <row r="45" spans="2:14">
@@ -19401,7 +19401,7 @@
         <v>0.79714758259933072</v>
       </c>
       <c r="N45">
-        <v>0.27700000000000002</v>
+        <v>8.6680763980981193E-2</v>
       </c>
     </row>
     <row r="46" spans="2:14">
@@ -19439,7 +19439,7 @@
         <v>0.32843929476989125</v>
       </c>
       <c r="N46">
-        <v>9.9000000000000005E-2</v>
+        <v>0.12727513724635781</v>
       </c>
     </row>
     <row r="47" spans="2:14">
@@ -19477,7 +19477,7 @@
         <v>2.1205434554973821</v>
       </c>
       <c r="N47">
-        <v>0.191</v>
+        <v>0.18570419883910519</v>
       </c>
     </row>
     <row r="48" spans="2:14">
@@ -19515,7 +19515,7 @@
         <v>4.508805970149254</v>
       </c>
       <c r="N48">
-        <v>0.251</v>
+        <v>0.1172527709898569</v>
       </c>
     </row>
     <row r="49" spans="2:14">
@@ -19553,7 +19553,7 @@
         <v>2.4670264236493424</v>
       </c>
       <c r="N49">
-        <v>0.31</v>
+        <v>0.1144056257666751</v>
       </c>
     </row>
     <row r="50" spans="2:14">
@@ -19591,7 +19591,7 @@
         <v>0.41032383063900418</v>
       </c>
       <c r="N50">
-        <v>0.25700000000000001</v>
+        <v>9.5041770239789894E-2</v>
       </c>
     </row>
     <row r="51" spans="2:14">
@@ -19629,7 +19629,7 @@
         <v>0.5079559043966082</v>
       </c>
       <c r="N51">
-        <v>0.11600000000000001</v>
+        <v>0.1104054533022131</v>
       </c>
     </row>
     <row r="52" spans="2:14">
@@ -19667,7 +19667,7 @@
         <v>0.20287755838923621</v>
       </c>
       <c r="N52">
-        <v>0.154</v>
+        <v>0.2435903152094821</v>
       </c>
     </row>
     <row r="53" spans="2:14">
@@ -19705,7 +19705,7 @@
         <v>2.8129755184473675</v>
       </c>
       <c r="N53">
-        <v>0.33900000000000002</v>
+        <v>0.30437942267587992</v>
       </c>
     </row>
     <row r="54" spans="2:14">
@@ -19743,7 +19743,7 @@
         <v>4.2710558923834778</v>
       </c>
       <c r="N54">
-        <v>0.313</v>
+        <v>0.1943666490936227</v>
       </c>
     </row>
     <row r="55" spans="2:14">
@@ -19781,7 +19781,7 @@
         <v>1.859117014057198</v>
       </c>
       <c r="N55">
-        <v>0.34799999999999998</v>
+        <v>0.1938280085742497</v>
       </c>
     </row>
     <row r="56" spans="2:14">
@@ -19819,7 +19819,7 @@
         <v>0.33541610302977803</v>
       </c>
       <c r="N56">
-        <v>0.318</v>
+        <v>0.1260937523867762</v>
       </c>
     </row>
     <row r="57" spans="2:14">
@@ -19857,7 +19857,7 @@
         <v>0.27885813425864142</v>
       </c>
       <c r="N57">
-        <v>0.14899999999999999</v>
+        <v>5.7604509160064002E-2</v>
       </c>
     </row>
     <row r="58" spans="2:14">
@@ -19895,7 +19895,7 @@
         <v>0.24119264078991506</v>
       </c>
       <c r="N58">
-        <v>0.16600000000000001</v>
+        <v>0.1022244947192848</v>
       </c>
     </row>
     <row r="59" spans="2:14">
@@ -19933,7 +19933,7 @@
         <v>6.9648999730340111E-2</v>
       </c>
       <c r="N59">
-        <v>0.17799999999999999</v>
+        <v>0.22863728737567171</v>
       </c>
     </row>
     <row r="60" spans="2:14">
@@ -19971,7 +19971,7 @@
         <v>8.8831231131880406E-2</v>
       </c>
       <c r="N60">
-        <v>0.26200000000000001</v>
+        <v>0.44535113475269339</v>
       </c>
     </row>
     <row r="61" spans="2:14">
@@ -20009,7 +20009,7 @@
         <v>1.0523359289160656</v>
       </c>
       <c r="N61">
-        <v>0.33500000000000002</v>
+        <v>0.38715746986910149</v>
       </c>
     </row>
     <row r="62" spans="2:14">
@@ -20047,7 +20047,7 @@
         <v>3.6160962725489258</v>
       </c>
       <c r="N62">
-        <v>0.32</v>
+        <v>0.26936297265374748</v>
       </c>
     </row>
     <row r="63" spans="2:14">
@@ -20085,7 +20085,7 @@
         <v>2.4263253254172734</v>
       </c>
       <c r="N63">
-        <v>0.30199999999999999</v>
+        <v>0.16041435094803921</v>
       </c>
     </row>
     <row r="64" spans="2:14">
@@ -20123,7 +20123,7 @@
         <v>1.7664731879502924</v>
       </c>
       <c r="N64">
-        <v>0.318</v>
+        <v>9.9794566737195597E-2</v>
       </c>
     </row>
     <row r="65" spans="2:14">
@@ -20161,7 +20161,7 @@
         <v>0.70629656361120174</v>
       </c>
       <c r="N65">
-        <v>0.2</v>
+        <v>9.0248299595347303E-2</v>
       </c>
     </row>
     <row r="66" spans="2:14">
@@ -20199,7 +20199,7 @@
         <v>0.39825251270751338</v>
       </c>
       <c r="N66">
-        <v>0.17</v>
+        <v>0.12612291503486611</v>
       </c>
     </row>
     <row r="67" spans="2:14">
@@ -20237,7 +20237,7 @@
         <v>0.34705106931740048</v>
       </c>
       <c r="N67">
-        <v>0.221</v>
+        <v>0.40657872468184758</v>
       </c>
     </row>
     <row r="68" spans="2:14">
@@ -20275,7 +20275,7 @@
         <v>0.48938499767044574</v>
       </c>
       <c r="N68">
-        <v>0.36499999999999999</v>
+        <v>0.47745552511226541</v>
       </c>
     </row>
     <row r="69" spans="2:14">
@@ -20313,7 +20313,7 @@
         <v>0.56367622562465713</v>
       </c>
       <c r="N69">
-        <v>0.36</v>
+        <v>0.51866838636324875</v>
       </c>
     </row>
     <row r="70" spans="2:14">
@@ -20351,7 +20351,7 @@
         <v>0.65004775348964428</v>
       </c>
       <c r="N70">
-        <v>0.25700000000000001</v>
+        <v>0.20153257870765759</v>
       </c>
     </row>
     <row r="71" spans="2:14">
@@ -20389,7 +20389,7 @@
         <v>2.1056705431537677</v>
       </c>
       <c r="N71">
-        <v>0.27400000000000002</v>
+        <v>0.1076195758078838</v>
       </c>
     </row>
     <row r="72" spans="2:14">
@@ -20427,7 +20427,7 @@
         <v>1.4876715234148732</v>
       </c>
       <c r="N72">
-        <v>0.27400000000000002</v>
+        <v>0.17130953000979379</v>
       </c>
     </row>
     <row r="73" spans="2:14">
@@ -20465,7 +20465,7 @@
         <v>0.34982731097376635</v>
       </c>
       <c r="N73">
-        <v>0.22900000000000001</v>
+        <v>0.33919584896240818</v>
       </c>
     </row>
     <row r="74" spans="2:14">
@@ -20503,7 +20503,7 @@
         <v>1.7829638920253619</v>
       </c>
       <c r="N74">
-        <v>0.36899999999999999</v>
+        <v>0.52536145962063019</v>
       </c>
     </row>
     <row r="75" spans="2:14">
@@ -20541,7 +20541,7 @@
         <v>2.288754760009537</v>
       </c>
       <c r="N75">
-        <v>0.34499999999999997</v>
+        <v>0.3512594183025694</v>
       </c>
     </row>
     <row r="76" spans="2:14">
@@ -20579,7 +20579,7 @@
         <v>2.5783792200289359</v>
       </c>
       <c r="N76">
-        <v>0.33200000000000002</v>
+        <v>0.34757142611819231</v>
       </c>
     </row>
     <row r="77" spans="2:14">
@@ -20617,7 +20617,7 @@
         <v>0.65905018708197771</v>
       </c>
       <c r="N77">
-        <v>0.36299999999999999</v>
+        <v>0.4284604781699709</v>
       </c>
     </row>
     <row r="78" spans="2:14">
@@ -20655,7 +20655,7 @@
         <v>0.24854835963097086</v>
       </c>
       <c r="N78">
-        <v>0.45700000000000002</v>
+        <v>0.56652477085458819</v>
       </c>
     </row>
     <row r="79" spans="2:14">
@@ -20693,7 +20693,7 @@
         <v>1.6005608422358149</v>
       </c>
       <c r="N79">
-        <v>0.44600000000000001</v>
+        <v>0.51800914816419918</v>
       </c>
     </row>
     <row r="80" spans="2:14">
@@ -20731,7 +20731,7 @@
         <v>4.6476459016393443</v>
       </c>
       <c r="N80">
-        <v>0.35399999999999998</v>
+        <v>0.39205066542589151</v>
       </c>
     </row>
     <row r="81" spans="2:14">
@@ -20769,7 +20769,7 @@
         <v>1.2407169756378273</v>
       </c>
       <c r="N81">
-        <v>0.33100000000000002</v>
+        <v>0.36641536018315229</v>
       </c>
     </row>
     <row r="82" spans="2:14">
@@ -20807,7 +20807,7 @@
         <v>0.89357999700209167</v>
       </c>
       <c r="N82">
-        <v>0.34899999999999998</v>
+        <v>0.39136159967488759</v>
       </c>
     </row>
     <row r="83" spans="2:14">
@@ -20845,7 +20845,7 @@
         <v>1.8738155661067897</v>
       </c>
       <c r="N83">
-        <v>0.35199999999999998</v>
+        <v>0.38633201591702238</v>
       </c>
     </row>
     <row r="84" spans="2:14">
@@ -20883,7 +20883,7 @@
         <v>3.5540873544173417</v>
       </c>
       <c r="N84">
-        <v>0.371</v>
+        <v>0.37686527872616998</v>
       </c>
     </row>
     <row r="85" spans="2:14">
@@ -20921,7 +20921,7 @@
         <v>2.9635943019943021</v>
       </c>
       <c r="N85">
-        <v>0.36</v>
+        <v>0.3725870329193654</v>
       </c>
     </row>
     <row r="86" spans="2:14">
@@ -20959,7 +20959,7 @@
         <v>0.54475968540869324</v>
       </c>
       <c r="N86">
-        <v>0.34</v>
+        <v>0.4089911198432562</v>
       </c>
     </row>
     <row r="87" spans="2:14">
@@ -20997,7 +20997,7 @@
         <v>0.54959134176067381</v>
       </c>
       <c r="N87">
-        <v>0.42899999999999999</v>
+        <v>0.54844648380350902</v>
       </c>
     </row>
     <row r="88" spans="2:14">
@@ -21035,7 +21035,7 @@
         <v>2.3132948414576431</v>
       </c>
       <c r="N88">
-        <v>0.34399999999999997</v>
+        <v>0.44241830129931159</v>
       </c>
     </row>
     <row r="89" spans="2:14">
@@ -21073,7 +21073,7 @@
         <v>1.3500740367665576</v>
       </c>
       <c r="N89">
-        <v>0.255</v>
+        <v>0.4074757910432435</v>
       </c>
     </row>
     <row r="90" spans="2:14">
@@ -21111,7 +21111,7 @@
         <v>2.8285770493485174</v>
       </c>
       <c r="N90">
-        <v>0.38900000000000001</v>
+        <v>0.42476329992823081</v>
       </c>
     </row>
     <row r="91" spans="2:14">
@@ -21149,7 +21149,7 @@
         <v>3.9331941685296883</v>
       </c>
       <c r="N91">
-        <v>0.35899999999999999</v>
+        <v>0.38698110170663969</v>
       </c>
     </row>
     <row r="92" spans="2:14">
@@ -21187,7 +21187,7 @@
         <v>2.0373948516366096</v>
       </c>
       <c r="N92">
-        <v>0.318</v>
+        <v>0.2747032211297431</v>
       </c>
     </row>
     <row r="93" spans="2:14">
@@ -21225,7 +21225,7 @@
         <v>3.3686478028061324</v>
       </c>
       <c r="N93">
-        <v>0.245</v>
+        <v>0.21187662628108719</v>
       </c>
     </row>
     <row r="94" spans="2:14">
@@ -21263,7 +21263,7 @@
         <v>4.6859338713876584</v>
       </c>
       <c r="N94">
-        <v>0.28799999999999998</v>
+        <v>0.2554253826993938</v>
       </c>
     </row>
     <row r="95" spans="2:14">
@@ -21301,7 +21301,7 @@
         <v>5.376832754311005</v>
       </c>
       <c r="N95">
-        <v>0.29599999999999999</v>
+        <v>0.25123330268387167</v>
       </c>
     </row>
     <row r="96" spans="2:14">
@@ -21339,7 +21339,7 @@
         <v>5.9911336345612778</v>
       </c>
       <c r="N96">
-        <v>0.33400000000000002</v>
+        <v>0.30197167758679211</v>
       </c>
     </row>
     <row r="97" spans="2:14">
@@ -21377,7 +21377,7 @@
         <v>3.2648661387432321</v>
       </c>
       <c r="N97">
-        <v>0.312</v>
+        <v>0.3067013233943906</v>
       </c>
     </row>
     <row r="98" spans="2:14">
@@ -21415,7 +21415,7 @@
         <v>0.33396660026927044</v>
       </c>
       <c r="N98">
-        <v>0.36499999999999999</v>
+        <v>0.37204485256898823</v>
       </c>
     </row>
     <row r="99" spans="2:14">
@@ -21453,7 +21453,7 @@
         <v>0.33970058939096265</v>
       </c>
       <c r="N99">
-        <v>0.38200000000000001</v>
+        <v>0.42920450573368629</v>
       </c>
     </row>
     <row r="100" spans="2:14">
@@ -21491,7 +21491,7 @@
         <v>3.4238728424826683</v>
       </c>
       <c r="N100">
-        <v>0.36399999999999999</v>
+        <v>0.45839075169321591</v>
       </c>
     </row>
     <row r="101" spans="2:14">
@@ -21529,7 +21529,7 @@
         <v>6.2021360841816646</v>
       </c>
       <c r="N101">
-        <v>0.443</v>
+        <v>0.403954100653313</v>
       </c>
     </row>
     <row r="102" spans="2:14">
@@ -21567,7 +21567,7 @@
         <v>7.3334443355546846</v>
       </c>
       <c r="N102">
-        <v>0.41699999999999998</v>
+        <v>0.34685195673070141</v>
       </c>
     </row>
     <row r="103" spans="2:14">
@@ -21605,7 +21605,7 @@
         <v>5.2704530374170666</v>
       </c>
       <c r="N103">
-        <v>0.32200000000000001</v>
+        <v>0.28417330611491431</v>
       </c>
     </row>
     <row r="104" spans="2:14">
@@ -21643,7 +21643,7 @@
         <v>3.8681922051456099</v>
       </c>
       <c r="N104">
-        <v>0.35799999999999998</v>
+        <v>0.23335752384388239</v>
       </c>
     </row>
     <row r="105" spans="2:14">
@@ -21681,7 +21681,7 @@
         <v>1.4020326275598749</v>
       </c>
       <c r="N105">
-        <v>0.27900000000000003</v>
+        <v>0.19697977326471161</v>
       </c>
     </row>
     <row r="106" spans="2:14">
@@ -21719,7 +21719,7 @@
         <v>3.6831445671951224</v>
       </c>
       <c r="N106">
-        <v>0.28399999999999997</v>
+        <v>0.2331342112578032</v>
       </c>
     </row>
     <row r="107" spans="2:14">
@@ -21757,7 +21757,7 @@
         <v>4.1714814528854331</v>
       </c>
       <c r="N107">
-        <v>0.29199999999999998</v>
+        <v>0.23958051626697799</v>
       </c>
     </row>
     <row r="108" spans="2:14">
@@ -21795,7 +21795,7 @@
         <v>3.0158280939116593</v>
       </c>
       <c r="N108">
-        <v>0.28499999999999998</v>
+        <v>0.31162873786088868</v>
       </c>
     </row>
     <row r="109" spans="2:14">
@@ -21833,7 +21833,7 @@
         <v>0.76509444735768806</v>
       </c>
       <c r="N109">
-        <v>0.28000000000000003</v>
+        <v>0.3334929915462419</v>
       </c>
     </row>
     <row r="110" spans="2:14">
@@ -21871,7 +21871,7 @@
         <v>0.15164035492048855</v>
       </c>
       <c r="N110">
-        <v>0.313</v>
+        <v>0.42301241586484312</v>
       </c>
     </row>
     <row r="111" spans="2:14">
@@ -21909,7 +21909,7 @@
         <v>4.5440964262637316</v>
       </c>
       <c r="N111">
-        <v>0.38300000000000001</v>
+        <v>0.3954858917459193</v>
       </c>
     </row>
     <row r="112" spans="2:14">
@@ -21947,7 +21947,7 @@
         <v>4.9141725152274693</v>
       </c>
       <c r="N112">
-        <v>0.27600000000000002</v>
+        <v>0.2749006517307867</v>
       </c>
     </row>
     <row r="113" spans="2:14">
@@ -21985,7 +21985,7 @@
         <v>3.1300587651295588</v>
       </c>
       <c r="N113">
-        <v>0.30399999999999999</v>
+        <v>0.24048028758268791</v>
       </c>
     </row>
     <row r="114" spans="2:14">
@@ -22023,7 +22023,7 @@
         <v>1.479833857084301</v>
       </c>
       <c r="N114">
-        <v>0.315</v>
+        <v>0.28243194936428551</v>
       </c>
     </row>
     <row r="115" spans="2:14">
@@ -22061,7 +22061,7 @@
         <v>1.7756208436214307</v>
       </c>
       <c r="N115">
-        <v>0.223</v>
+        <v>0.2292006568823429</v>
       </c>
     </row>
     <row r="116" spans="2:14">
@@ -22099,7 +22099,7 @@
         <v>1.9293026253733689</v>
       </c>
       <c r="N116">
-        <v>0.222</v>
+        <v>0.23058422174983781</v>
       </c>
     </row>
     <row r="117" spans="2:14">
@@ -22137,7 +22137,7 @@
         <v>3.3486497793841368</v>
       </c>
       <c r="N117">
-        <v>0.317</v>
+        <v>0.27907626285456211</v>
       </c>
     </row>
     <row r="118" spans="2:14">
@@ -22175,7 +22175,7 @@
         <v>3.0940009448839487</v>
       </c>
       <c r="N118">
-        <v>0.38</v>
+        <v>0.2586740621409146</v>
       </c>
     </row>
     <row r="119" spans="2:14">
@@ -22213,7 +22213,7 @@
         <v>0.53437336567043681</v>
       </c>
       <c r="N119">
-        <v>0.19</v>
+        <v>0.2236988252917039</v>
       </c>
     </row>
     <row r="120" spans="2:14">
@@ -22251,7 +22251,7 @@
         <v>2.5443258073735353</v>
       </c>
       <c r="N120">
-        <v>0.33500000000000002</v>
+        <v>0.3350431389510522</v>
       </c>
     </row>
     <row r="121" spans="2:14">
@@ -22289,7 +22289,7 @@
         <v>1.2811096663358594</v>
       </c>
       <c r="N121">
-        <v>0.32600000000000001</v>
+        <v>0.28936654710598481</v>
       </c>
     </row>
     <row r="122" spans="2:14">
@@ -22327,7 +22327,7 @@
         <v>0.54460916589924957</v>
       </c>
       <c r="N122">
-        <v>0.32</v>
+        <v>0.50446877497201248</v>
       </c>
     </row>
     <row r="123" spans="2:14">
@@ -22365,7 +22365,7 @@
         <v>0.70682617906050216</v>
       </c>
       <c r="N123">
-        <v>0.48299999999999998</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -22374,7 +22374,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C91F65-A6DF-452A-8ADA-99EC9FEC5FB1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE395907-4633-4ADC-AC96-97A6BB4E275D}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02C6E5BE-5467-4B6A-B49C-7510E7B99833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA438199-708E-4F07-BC4D-82ADA6D37F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12682" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -862,24 +862,66 @@
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_016</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_008</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_015</t>
   </si>
   <si>
@@ -898,54 +940,12 @@
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_011</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -958,15 +958,36 @@
     <t>e_r17609399-220,e_w95344674-220,e_w191346761-220,e_w167572576-220,e_NZ23-220,e_NZ21-220</t>
   </si>
   <si>
+    <t>e_NZ41-220</t>
+  </si>
+  <si>
+    <t>e_w26671244-220,e_w61853727-220,e_w167293888-220,e_NZ3-220,e_w82881422-220,e_w270022030-220,e_w119877500-220,e_NZ5-220</t>
+  </si>
+  <si>
     <t>e_NZ31-220,e_NZ30-220,e_w1099619174-220,e_w95048289-220</t>
   </si>
   <si>
+    <t>e_w412589726-220,e_w180519027-220</t>
+  </si>
+  <si>
+    <t>e_NZ40-220,e_w180519027-220,e_w414953388-220,e_NZ38-220,e_w89636510-220</t>
+  </si>
+  <si>
+    <t>e_w1099619174-220,e_w93827784-220,e_w100957314-220,e_w95046918-220</t>
+  </si>
+  <si>
+    <t>e_w89637277-220,e_w94840399-220,e_NZ32-220,e_w167286837-220,e_w268826084-220</t>
+  </si>
+  <si>
+    <t>e_w93419960-220,e_w409049317-220,e_w95512216-220,e_w270556206-220,e_w148300699-220,e_NZ13-220,e_w167283894-220</t>
+  </si>
+  <si>
+    <t>e_w167427251-220,e_w94053861-220,e_w89411122-220,e_NZ14-220</t>
+  </si>
+  <si>
     <t>e_w268841395-220,e_w90092620-220,e_w180514007-220,e_w270521928-220</t>
   </si>
   <si>
-    <t>e_w93419960-220,e_w409049317-220,e_w95512216-220,e_w270556206-220,e_w148300699-220,e_NZ13-220,e_w167283894-220</t>
-  </si>
-  <si>
     <t>e_w180519027-220,e_w89636510-220,e_NZ30-220</t>
   </si>
   <si>
@@ -976,28 +997,43 @@
     <t>e_w95046918-220,e_NZ27-220,e_w167705537-220,e_w95343089-220,e_w93713118-220,e_NZ26-220,e_w95344674-220,e_w1026587442-220</t>
   </si>
   <si>
-    <t>e_w167427251-220,e_w94053861-220,e_w89411122-220,e_NZ14-220</t>
-  </si>
-  <si>
     <t>e_w412588974-220,e_NZ41-220,e_w268841395-220,e_w180519027-220,e_NZ42-220</t>
   </si>
   <si>
-    <t>e_w412589726-220,e_w180519027-220</t>
-  </si>
-  <si>
-    <t>e_NZ40-220,e_w180519027-220,e_w414953388-220,e_NZ38-220,e_w89636510-220</t>
-  </si>
-  <si>
-    <t>e_w1099619174-220,e_w93827784-220,e_w100957314-220,e_w95046918-220</t>
-  </si>
-  <si>
-    <t>e_NZ41-220</t>
-  </si>
-  <si>
-    <t>e_w26671244-220,e_w61853727-220,e_w167293888-220,e_NZ3-220,e_w82881422-220,e_w270022030-220,e_w119877500-220,e_NZ5-220</t>
-  </si>
-  <si>
-    <t>e_w89637277-220,e_w94840399-220,e_NZ32-220,e_w167286837-220,e_w268826084-220</t>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_008</t>
@@ -1006,273 +1042,327 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_014</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_015</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_004</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_NZ41-220,e_w412588974-220,e_w268841395-220,e_NZ42-220</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w414953388-220,e_w94840399-220</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_NZ31-220,e_w268826084-220,e_w1099619174-220,e_w93827784-220,e_w95046918-220</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w167705537-220,e_w95343089-220,e_w93713118-220,e_w1026587442-220</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w90092620-220,e_w180514007-220,e_w270521928-220,e_w89637277-220,e_w94840399-220</t>
+  </si>
+  <si>
     <t>elc_won_008</t>
   </si>
   <si>
     <t>e_NZ41-220,e_w412589726-220,e_w268841395-220,e_w180519027-220</t>
   </si>
   <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w95048289-220,e_w167705537-220,e_r17609399-220,e_NZ26-220,e_w95344674-220,e_w191346761-220,e_w1026587442-220,e_w167572576-220,e_NZ23-220,e_NZ21-220</t>
+  </si>
+  <si>
     <t>elc_won_014</t>
   </si>
   <si>
     <t>e_NZ30-220,e_w1099619174-220</t>
   </si>
   <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w89943957-220,e_w232382576-220,e_w26671244-220,e_w61853727-220,e_w167293888-220,e_NZ3-220,e_w82881422-220,e_w119877500-220,e_NZ5-220</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_NZ41-220,e_w412589726-220,e_w180519027-220,e_w89636510-220</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w167286837-220,e_w268826084-220,e_w1099619174-220,e_w100957314-220,e_w93827784-220</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w95048289-220,e_w95046918-220,e_NZ27-220</t>
+  </si>
+  <si>
     <t>elc_won_015</t>
   </si>
   <si>
     <t>e_w95048289-220,e_NZ27-220</t>
   </si>
   <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w167705537-220,e_w95343089-220,e_w93713118-220,e_w1026587442-220</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_NZ41-220,e_w412588974-220,e_w268841395-220,e_NZ42-220</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w414953388-220,e_w94840399-220</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_NZ31-220,e_w268826084-220,e_w1099619174-220,e_w93827784-220,e_w95046918-220</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w90092620-220,e_w180514007-220,e_w270521928-220,e_w89637277-220,e_w94840399-220</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w95048289-220,e_w167705537-220,e_r17609399-220,e_NZ26-220,e_w95344674-220,e_w191346761-220,e_w1026587442-220,e_w167572576-220,e_NZ23-220,e_NZ21-220</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w89943957-220,e_w232382576-220,e_w26671244-220,e_w61853727-220,e_w167293888-220,e_NZ3-220,e_w82881422-220,e_w119877500-220,e_NZ5-220</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_NZ41-220,e_w412589726-220,e_w180519027-220,e_w89636510-220</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w167286837-220,e_w268826084-220,e_w1099619174-220,e_w100957314-220,e_w93827784-220</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w95048289-220,e_w95046918-220,e_NZ27-220</t>
-  </si>
-  <si>
     <t>elc_won_004</t>
   </si>
   <si>
     <t>e_w167427251-220,e_w94053861-220,e_w89411122-220,e_NZ14-220,e_w270022030-220</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_017</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_019</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_027</t>
   </si>
   <si>
@@ -1285,184 +1375,181 @@
     <t>connecting wind offshore to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_w167286837-220,e_w268826084-220,e_NZ29-220,e_w100957314-220</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_w412588974-220</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_w412589726-220</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w188180344-220,e_w61853727-220</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_NZ30-220,e_w95048289-220</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_w268841395-220,e_w412588974-220,e_NZ42-220</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_w95512216-220,e_NZ13-220</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_NZ41-220,e_w412588974-220,e_w270521928-220</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_r17609399-220</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_w100957314-220,e_w93827784-220,e_w95046918-220</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_w100957314-220,e_w95343089-220,e_w93713118-220,e_w1026587442-220</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w232382576-220,e_w89943957-220,e_w1363994055-220,e_w82881422-220,e_NZ3-220</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w167427251-220,e_NZ9-220,e_w167293888-220,e_NZ8-220,e_NZ5-220</t>
   </si>
   <si>
     <t>elc_wof_017</t>
   </si>
   <si>
-    <t>e_NZ41-220,e_w412588974-220,e_w270521928-220</t>
+    <t>e_w89637277-220,e_w100957314-220,e_w93713118-220</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_NZ41-220,e_w412589726-220,e_w412588974-220</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_w270521928-220,e_w89637277-220,e_w94840399-220,e_w167286837-220</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_w167705537-220,e_w95343089-220,e_r17609399-220,e_NZ26-220,e_w95344674-220</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_w89943957-220,e_w119877500-220,e_NZ3-220,e_w167283894-220</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_w89943957-220</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_w93713118-220,e_w1167708390-220,e_w1026587442-220,e_w167572576-220,e_w93419960-220</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_w412588974-220,e_NZ41-220</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>e_w95046918-220,e_w95343089-220,e_w93713118-220</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w412588974-220,e_w89637277-220</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_w119877500-220,e_w167283894-220</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_w95512216-220,e_NZ13-220,e_w167283894-220</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>e_w100957314-220,e_w95343089-220</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_w93419960-220,e_w95512216-220</t>
   </si>
   <si>
     <t>elc_wof_019</t>
   </si>
   <si>
-    <t>e_w412588974-220</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_r17609399-220</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_w100957314-220,e_w93827784-220,e_w95046918-220,e_w95343089-220,e_w93713118-220</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_w232382576-220,e_w1363994055-220,e_w82881422-220</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_NZ30-220,e_w95048289-220</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>e_w100957314-220,e_w95343089-220</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_w93419960-220,e_w95512216-220</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_NZ41-220,e_w412589726-220,e_w412588974-220</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w89943957-220</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_w95512216-220,e_NZ13-220,e_w167283894-220</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_w270521928-220,e_w89637277-220</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>e_w167705537-220,e_w95343089-220,e_r17609399-220,e_NZ26-220,e_w95344674-220</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_w93713118-220,e_w1026587442-220</t>
+    <t>e_w412588974-220,e_NZ42-220,e_w270521928-220</t>
   </si>
   <si>
     <t>elc_wof_027</t>
@@ -1472,93 +1559,6 @@
   </si>
   <si>
     <t>e_w95048289-220,e_NZ27-220,e_r17609399-220,e_w167705537-220</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w268841395-220,e_w412588974-220,e_NZ42-220</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_w412588974-220,e_NZ42-220,e_w270521928-220</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_w89637277-220,e_w94840399-220,e_w167286837-220,e_w268826084-220</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_NZ3-220,e_w89943957-220,e_w119877500-220,e_w167283894-220</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_w89637277-220,e_w100957314-220,e_w93713118-220</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w119877500-220,e_w167283894-220</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_w93713118-220,e_w1167708390-220,e_w1026587442-220,e_w167572576-220,e_w93419960-220</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_NZ29-220,e_w100957314-220,e_w93827784-220,e_w95046918-220</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w188180344-220,e_w61853727-220</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w167427251-220,e_NZ9-220,e_w167293888-220,e_NZ8-220,e_NZ5-220</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_w95343089-220,e_w93713118-220</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_w412588974-220,e_NZ41-220,e_w89637277-220</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_w412589726-220</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_w95512216-220,e_NZ13-220</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6777,7 +6777,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F1BFEA8-8B6F-4503-A8EC-9BE118D3E881}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3F7E0EE-A8C0-4D08-90A3-D373DDDDB3E3}">
   <dimension ref="B9:BD43"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7057,10 +7057,10 @@
         <v>321</v>
       </c>
       <c r="AO11">
-        <v>0.99590345602074126</v>
+        <v>0.9975157188831717</v>
       </c>
       <c r="AP11">
-        <v>75.103306286410302</v>
+        <v>45.545153808519316</v>
       </c>
       <c r="AR11" t="s">
         <v>237</v>
@@ -7093,10 +7093,10 @@
         <v>416</v>
       </c>
       <c r="BC11">
-        <v>0.98596601099553871</v>
+        <v>0.99402092584318991</v>
       </c>
       <c r="BD11">
-        <v>257.2897984151241</v>
+        <v>109.61635954151812</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7200,13 +7200,13 @@
         <v>322</v>
       </c>
       <c r="AN12" t="s">
-        <v>323</v>
+        <v>283</v>
       </c>
       <c r="AO12">
-        <v>0.99239099026325794</v>
+        <v>0.99595483459575906</v>
       </c>
       <c r="AP12">
-        <v>139.49851184027145</v>
+        <v>74.161365744417125</v>
       </c>
       <c r="AR12" t="s">
         <v>237</v>
@@ -7239,10 +7239,10 @@
         <v>418</v>
       </c>
       <c r="BC12">
-        <v>0.97496359905143026</v>
+        <v>0.97533397850909798</v>
       </c>
       <c r="BD12">
-        <v>459.00068405711187</v>
+        <v>452.21039399987052</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7307,16 +7307,16 @@
         <v>244</v>
       </c>
       <c r="Y13" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="Z13" t="s">
         <v>276</v>
       </c>
       <c r="AA13">
-        <v>0.99164479201276912</v>
+        <v>0.9958319028842455</v>
       </c>
       <c r="AB13">
-        <v>153.17881309923388</v>
+        <v>76.415113788833068</v>
       </c>
       <c r="AD13" t="s">
         <v>237</v>
@@ -7343,16 +7343,16 @@
         <v>294</v>
       </c>
       <c r="AM13" t="s">
+        <v>323</v>
+      </c>
+      <c r="AN13" t="s">
         <v>324</v>
       </c>
-      <c r="AN13" t="s">
-        <v>325</v>
-      </c>
       <c r="AO13">
-        <v>0.99692224665834439</v>
+        <v>0.99857516825685033</v>
       </c>
       <c r="AP13">
-        <v>56.425477930352955</v>
+        <v>26.121915291078167</v>
       </c>
       <c r="AR13" t="s">
         <v>237</v>
@@ -7385,10 +7385,10 @@
         <v>420</v>
       </c>
       <c r="BC13">
-        <v>0.992142345264865</v>
+        <v>0.99511226039729839</v>
       </c>
       <c r="BD13">
-        <v>144.05700347747464</v>
+        <v>89.608559382863291</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7453,16 +7453,16 @@
         <v>246</v>
       </c>
       <c r="Y14" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Z14" t="s">
         <v>277</v>
       </c>
       <c r="AA14">
-        <v>0.99757939258365447</v>
+        <v>0.9986195737404916</v>
       </c>
       <c r="AB14">
-        <v>44.377802633000776</v>
+        <v>25.307814757654675</v>
       </c>
       <c r="AD14" t="s">
         <v>237</v>
@@ -7489,16 +7489,16 @@
         <v>296</v>
       </c>
       <c r="AM14" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN14" t="s">
         <v>326</v>
       </c>
-      <c r="AN14" t="s">
-        <v>327</v>
-      </c>
       <c r="AO14">
-        <v>0.99665105279570931</v>
+        <v>0.99624198670989172</v>
       </c>
       <c r="AP14">
-        <v>61.397365411996212</v>
+        <v>68.896910318651507</v>
       </c>
       <c r="AR14" t="s">
         <v>237</v>
@@ -7528,13 +7528,13 @@
         <v>421</v>
       </c>
       <c r="BB14" t="s">
-        <v>422</v>
+        <v>274</v>
       </c>
       <c r="BC14">
-        <v>0.98827127202061349</v>
+        <v>0.98183461816751461</v>
       </c>
       <c r="BD14">
-        <v>215.02667962208514</v>
+        <v>333.03200026223124</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7599,16 +7599,16 @@
         <v>248</v>
       </c>
       <c r="Y15" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="Z15" t="s">
         <v>278</v>
       </c>
       <c r="AA15">
-        <v>0.99649838493007836</v>
+        <v>0.99164479201276912</v>
       </c>
       <c r="AB15">
-        <v>64.196276281897482</v>
+        <v>153.17881309923388</v>
       </c>
       <c r="AD15" t="s">
         <v>237</v>
@@ -7635,16 +7635,16 @@
         <v>298</v>
       </c>
       <c r="AM15" t="s">
+        <v>327</v>
+      </c>
+      <c r="AN15" t="s">
         <v>328</v>
       </c>
-      <c r="AN15" t="s">
-        <v>329</v>
-      </c>
       <c r="AO15">
-        <v>0.9975157188831717</v>
+        <v>0.99665105279570931</v>
       </c>
       <c r="AP15">
-        <v>45.545153808519316</v>
+        <v>61.397365411996212</v>
       </c>
       <c r="AR15" t="s">
         <v>237</v>
@@ -7671,16 +7671,16 @@
         <v>357</v>
       </c>
       <c r="BA15" t="s">
+        <v>422</v>
+      </c>
+      <c r="BB15" t="s">
         <v>423</v>
       </c>
-      <c r="BB15" t="s">
-        <v>274</v>
-      </c>
       <c r="BC15">
-        <v>0.98248517632197996</v>
+        <v>0.99490522012066784</v>
       </c>
       <c r="BD15">
-        <v>321.10510076370025</v>
+        <v>93.404297787756065</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7745,16 +7745,16 @@
         <v>250</v>
       </c>
       <c r="Y16" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="Z16" t="s">
         <v>279</v>
       </c>
       <c r="AA16">
-        <v>0.99568371668484024</v>
+        <v>0.99552574319771747</v>
       </c>
       <c r="AB16">
-        <v>79.131860777928608</v>
+        <v>82.028041375179441</v>
       </c>
       <c r="AD16" t="s">
         <v>237</v>
@@ -7781,16 +7781,16 @@
         <v>300</v>
       </c>
       <c r="AM16" t="s">
+        <v>329</v>
+      </c>
+      <c r="AN16" t="s">
         <v>330</v>
       </c>
-      <c r="AN16" t="s">
-        <v>278</v>
-      </c>
       <c r="AO16">
-        <v>0.99595483459575906</v>
+        <v>0.99761292756299069</v>
       </c>
       <c r="AP16">
-        <v>74.161365744417125</v>
+        <v>43.762994678503716</v>
       </c>
       <c r="AR16" t="s">
         <v>237</v>
@@ -7823,10 +7823,10 @@
         <v>425</v>
       </c>
       <c r="BC16">
-        <v>0.99241288386292881</v>
+        <v>0.9878288138539939</v>
       </c>
       <c r="BD16">
-        <v>139.09712917963907</v>
+        <v>223.13841267677765</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7891,16 +7891,16 @@
         <v>252</v>
       </c>
       <c r="Y17" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="Z17" t="s">
         <v>280</v>
       </c>
       <c r="AA17">
-        <v>0.99673728461460676</v>
+        <v>0.99856414548474748</v>
       </c>
       <c r="AB17">
-        <v>59.816448732209111</v>
+        <v>26.323999446296273</v>
       </c>
       <c r="AD17" t="s">
         <v>237</v>
@@ -7933,10 +7933,10 @@
         <v>332</v>
       </c>
       <c r="AO17">
-        <v>0.99857516825685033</v>
+        <v>0.99590345602074126</v>
       </c>
       <c r="AP17">
-        <v>26.121915291078167</v>
+        <v>75.103306286410302</v>
       </c>
       <c r="AR17" t="s">
         <v>237</v>
@@ -7969,10 +7969,10 @@
         <v>427</v>
       </c>
       <c r="BC17">
-        <v>0.9878288138539939</v>
+        <v>0.99503867375582744</v>
       </c>
       <c r="BD17">
-        <v>223.13841267677765</v>
+        <v>90.957647809829638</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8037,16 +8037,16 @@
         <v>254</v>
       </c>
       <c r="Y18" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z18" t="s">
         <v>281</v>
       </c>
       <c r="AA18">
-        <v>0.99709164861435029</v>
+        <v>0.99837169372341228</v>
       </c>
       <c r="AB18">
-        <v>53.319775403577559</v>
+        <v>29.852281737441412</v>
       </c>
       <c r="AD18" t="s">
         <v>237</v>
@@ -8079,10 +8079,10 @@
         <v>334</v>
       </c>
       <c r="AO18">
-        <v>0.99624198670989172</v>
+        <v>0.99807547980555666</v>
       </c>
       <c r="AP18">
-        <v>68.896910318651507</v>
+        <v>35.282870231460656</v>
       </c>
       <c r="AR18" t="s">
         <v>237</v>
@@ -8115,10 +8115,10 @@
         <v>429</v>
       </c>
       <c r="BC18">
-        <v>0.98395883577792953</v>
+        <v>0.9960370911532308</v>
       </c>
       <c r="BD18">
-        <v>294.08801073795939</v>
+        <v>72.653328857434573</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8183,16 +8183,16 @@
         <v>256</v>
       </c>
       <c r="Y19" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="Z19" t="s">
         <v>282</v>
       </c>
       <c r="AA19">
-        <v>0.9982917156958806</v>
+        <v>0.99781284363204548</v>
       </c>
       <c r="AB19">
-        <v>31.318545575522229</v>
+        <v>40.097866745833329</v>
       </c>
       <c r="AD19" t="s">
         <v>237</v>
@@ -8225,10 +8225,10 @@
         <v>336</v>
       </c>
       <c r="AO19">
-        <v>0.99761292756299069</v>
+        <v>0.99239099026325794</v>
       </c>
       <c r="AP19">
-        <v>43.762994678503716</v>
+        <v>139.49851184027145</v>
       </c>
       <c r="AR19" t="s">
         <v>237</v>
@@ -8261,10 +8261,10 @@
         <v>431</v>
       </c>
       <c r="BC19">
-        <v>0.99439449087123744</v>
+        <v>0.98596601099553871</v>
       </c>
       <c r="BD19">
-        <v>102.76766736064755</v>
+        <v>257.2897984151241</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8329,16 +8329,16 @@
         <v>258</v>
       </c>
       <c r="Y20" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="Z20" t="s">
         <v>283</v>
       </c>
       <c r="AA20">
-        <v>0.99656426482871763</v>
+        <v>0.99649838493007836</v>
       </c>
       <c r="AB20">
-        <v>62.988478140176163</v>
+        <v>64.196276281897482</v>
       </c>
       <c r="AD20" t="s">
         <v>237</v>
@@ -8371,10 +8371,10 @@
         <v>338</v>
       </c>
       <c r="AO20">
-        <v>0.99807547980555666</v>
+        <v>0.99725701149052537</v>
       </c>
       <c r="AP20">
-        <v>35.282870231460656</v>
+        <v>50.288122673700855</v>
       </c>
       <c r="AR20" t="s">
         <v>237</v>
@@ -8404,13 +8404,13 @@
         <v>432</v>
       </c>
       <c r="BB20" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="BC20">
-        <v>0.98039565814133589</v>
+        <v>0.992142345264865</v>
       </c>
       <c r="BD20">
-        <v>359.41293407550836</v>
+        <v>144.05700347747464</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8475,16 +8475,16 @@
         <v>260</v>
       </c>
       <c r="Y21" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Z21" t="s">
         <v>284</v>
       </c>
       <c r="AA21">
-        <v>0.99552574319771747</v>
+        <v>0.9982917156958806</v>
       </c>
       <c r="AB21">
-        <v>82.028041375179441</v>
+        <v>31.318545575522229</v>
       </c>
       <c r="AD21" t="s">
         <v>237</v>
@@ -8517,10 +8517,10 @@
         <v>340</v>
       </c>
       <c r="AO21">
-        <v>0.99725701149052537</v>
+        <v>0.99446613913875159</v>
       </c>
       <c r="AP21">
-        <v>50.288122673700855</v>
+        <v>101.45411578955439</v>
       </c>
       <c r="AR21" t="s">
         <v>237</v>
@@ -8547,16 +8547,16 @@
         <v>369</v>
       </c>
       <c r="BA21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="BB21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="BC21">
-        <v>0.99048115912556611</v>
+        <v>0.99199988291996133</v>
       </c>
       <c r="BD21">
-        <v>174.51208269795416</v>
+        <v>146.66881313404267</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8621,16 +8621,16 @@
         <v>262</v>
       </c>
       <c r="Y22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Z22" t="s">
         <v>285</v>
       </c>
       <c r="AA22">
-        <v>0.99856414548474748</v>
+        <v>0.99757939258365447</v>
       </c>
       <c r="AB22">
-        <v>26.323999446296273</v>
+        <v>44.377802633000776</v>
       </c>
       <c r="AD22" t="s">
         <v>237</v>
@@ -8663,10 +8663,10 @@
         <v>342</v>
       </c>
       <c r="AO22">
-        <v>0.99446613913875159</v>
+        <v>0.99821201020674788</v>
       </c>
       <c r="AP22">
-        <v>101.45411578955439</v>
+        <v>32.77981287628851</v>
       </c>
       <c r="AR22" t="s">
         <v>237</v>
@@ -8693,16 +8693,16 @@
         <v>371</v>
       </c>
       <c r="BA22" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="BB22" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="BC22">
-        <v>0.99441710380733805</v>
+        <v>0.98560960960201449</v>
       </c>
       <c r="BD22">
-        <v>102.3530968654682</v>
+        <v>263.82382396306684</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8767,16 +8767,16 @@
         <v>264</v>
       </c>
       <c r="Y23" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Z23" t="s">
         <v>286</v>
       </c>
       <c r="AA23">
-        <v>0.99837169372341228</v>
+        <v>0.99568371668484024</v>
       </c>
       <c r="AB23">
-        <v>29.852281737441412</v>
+        <v>79.131860777928608</v>
       </c>
       <c r="AD23" t="s">
         <v>237</v>
@@ -8809,10 +8809,10 @@
         <v>344</v>
       </c>
       <c r="AO23">
-        <v>0.99821201020674788</v>
+        <v>0.99562511313409086</v>
       </c>
       <c r="AP23">
-        <v>32.77981287628851</v>
+        <v>80.206259208334231</v>
       </c>
       <c r="AR23" t="s">
         <v>237</v>
@@ -8839,16 +8839,16 @@
         <v>373</v>
       </c>
       <c r="BA23" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="BB23" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="BC23">
-        <v>0.9871879084242271</v>
+        <v>0.99342656473398216</v>
       </c>
       <c r="BD23">
-        <v>234.88834555583597</v>
+        <v>120.51297987699346</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8913,16 +8913,16 @@
         <v>266</v>
       </c>
       <c r="Y24" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Z24" t="s">
         <v>287</v>
       </c>
       <c r="AA24">
-        <v>0.9958319028842455</v>
+        <v>0.99673728461460676</v>
       </c>
       <c r="AB24">
-        <v>76.415113788833068</v>
+        <v>59.816448732209111</v>
       </c>
       <c r="AD24" t="s">
         <v>237</v>
@@ -8955,10 +8955,10 @@
         <v>346</v>
       </c>
       <c r="AO24">
-        <v>0.99562511313409086</v>
+        <v>0.99692224665834439</v>
       </c>
       <c r="AP24">
-        <v>80.206259208334231</v>
+        <v>56.425477930352955</v>
       </c>
       <c r="AR24" t="s">
         <v>237</v>
@@ -8985,16 +8985,16 @@
         <v>375</v>
       </c>
       <c r="BA24" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="BB24" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="BC24">
-        <v>0.99605126302771252</v>
+        <v>0.99728827252195684</v>
       </c>
       <c r="BD24">
-        <v>72.393511158603474</v>
+        <v>49.715003764125143</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9059,16 +9059,16 @@
         <v>268</v>
       </c>
       <c r="Y25" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Z25" t="s">
         <v>288</v>
       </c>
       <c r="AA25">
-        <v>0.9986195737404916</v>
+        <v>0.99709164861435029</v>
       </c>
       <c r="AB25">
-        <v>25.307814757654675</v>
+        <v>53.319775403577559</v>
       </c>
       <c r="AD25" t="s">
         <v>237</v>
@@ -9131,16 +9131,16 @@
         <v>377</v>
       </c>
       <c r="BA25" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="BB25" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="BC25">
-        <v>0.99514843803074871</v>
+        <v>0.94957327345368925</v>
       </c>
       <c r="BD25">
-        <v>88.945302769606073</v>
+        <v>924.48998668236334</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9205,16 +9205,16 @@
         <v>270</v>
       </c>
       <c r="Y26" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Z26" t="s">
         <v>289</v>
       </c>
       <c r="AA26">
-        <v>0.99781284363204548</v>
+        <v>0.99656426482871763</v>
       </c>
       <c r="AB26">
-        <v>40.097866745833329</v>
+        <v>62.988478140176163</v>
       </c>
       <c r="AR26" t="s">
         <v>237</v>
@@ -9241,16 +9241,16 @@
         <v>379</v>
       </c>
       <c r="BA26" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="BB26" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="BC26">
-        <v>0.98382606125833871</v>
+        <v>0.99048115912556611</v>
       </c>
       <c r="BD26">
-        <v>296.52221026378965</v>
+        <v>174.51208269795416</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9279,16 +9279,16 @@
         <v>381</v>
       </c>
       <c r="BA27" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="BB27" t="s">
-        <v>279</v>
+        <v>447</v>
       </c>
       <c r="BC27">
-        <v>0.98974923036021278</v>
+        <v>0.9955021345306051</v>
       </c>
       <c r="BD27">
-        <v>187.93077672943278</v>
+        <v>82.460866938907401</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9317,16 +9317,16 @@
         <v>383</v>
       </c>
       <c r="BA28" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="BB28" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="BC28">
-        <v>0.9877150845460122</v>
+        <v>0.99514843803074871</v>
       </c>
       <c r="BD28">
-        <v>225.22344998977596</v>
+        <v>88.945302769606073</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9355,16 +9355,16 @@
         <v>385</v>
       </c>
       <c r="BA29" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="BB29" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="BC29">
-        <v>0.99503867375582744</v>
+        <v>0.99052756852009682</v>
       </c>
       <c r="BD29">
-        <v>90.957647809829638</v>
+        <v>173.66124379822571</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9393,16 +9393,16 @@
         <v>387</v>
       </c>
       <c r="BA30" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BB30" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BC30">
-        <v>0.99053075643264799</v>
+        <v>0.95113733831453195</v>
       </c>
       <c r="BD30">
-        <v>173.60279873478748</v>
+        <v>895.81546423358179</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9431,16 +9431,16 @@
         <v>389</v>
       </c>
       <c r="BA31" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BB31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="BC31">
-        <v>0.99516210931521021</v>
+        <v>0.99402264995370893</v>
       </c>
       <c r="BD31">
-        <v>88.694662554479393</v>
+        <v>109.58475084866993</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9469,16 +9469,16 @@
         <v>391</v>
       </c>
       <c r="BA32" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BB32" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="BC32">
-        <v>0.99162758874212198</v>
+        <v>0.96374055461874508</v>
       </c>
       <c r="BD32">
-        <v>153.49420639442948</v>
+        <v>664.7564986563408</v>
       </c>
     </row>
     <row r="33" spans="44:56">
@@ -9507,16 +9507,16 @@
         <v>393</v>
       </c>
       <c r="BA33" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="BB33" t="s">
-        <v>457</v>
+        <v>286</v>
       </c>
       <c r="BC33">
-        <v>0.94957327345368925</v>
+        <v>0.98974923036021278</v>
       </c>
       <c r="BD33">
-        <v>924.48998668236334</v>
+        <v>187.93077672943278</v>
       </c>
     </row>
     <row r="34" spans="44:56">
@@ -9545,16 +9545,16 @@
         <v>395</v>
       </c>
       <c r="BA34" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="BB34" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="BC34">
-        <v>0.99508487560623826</v>
+        <v>0.99579892549254256</v>
       </c>
       <c r="BD34">
-        <v>90.110613885632716</v>
+        <v>77.019699303385977</v>
       </c>
     </row>
     <row r="35" spans="44:56">
@@ -9583,16 +9583,16 @@
         <v>397</v>
       </c>
       <c r="BA35" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="BB35" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="BC35">
-        <v>0.99402264995370893</v>
+        <v>0.99338832047077197</v>
       </c>
       <c r="BD35">
-        <v>109.58475084866993</v>
+        <v>121.21412470251306</v>
       </c>
     </row>
     <row r="36" spans="44:56">
@@ -9627,10 +9627,10 @@
         <v>463</v>
       </c>
       <c r="BC36">
-        <v>0.99407026930811881</v>
+        <v>0.96365973275398331</v>
       </c>
       <c r="BD36">
-        <v>108.71172935115584</v>
+        <v>666.23823284363971</v>
       </c>
     </row>
     <row r="37" spans="44:56">
@@ -9665,10 +9665,10 @@
         <v>465</v>
       </c>
       <c r="BC37">
-        <v>0.99490522012066784</v>
+        <v>0.99508487560623826</v>
       </c>
       <c r="BD37">
-        <v>93.404297787756065</v>
+        <v>90.110613885632716</v>
       </c>
     </row>
     <row r="38" spans="44:56">
@@ -9703,10 +9703,10 @@
         <v>467</v>
       </c>
       <c r="BC38">
-        <v>0.99728827252195684</v>
+        <v>0.9871879084242271</v>
       </c>
       <c r="BD38">
-        <v>49.715003764125143</v>
+        <v>234.88834555583597</v>
       </c>
     </row>
     <row r="39" spans="44:56">
@@ -9738,13 +9738,13 @@
         <v>468</v>
       </c>
       <c r="BB39" t="s">
-        <v>436</v>
+        <v>469</v>
       </c>
       <c r="BC39">
-        <v>0.95113733831453195</v>
+        <v>0.98395883577792953</v>
       </c>
       <c r="BD39">
-        <v>895.81546423358179</v>
+        <v>294.08801073795939</v>
       </c>
     </row>
     <row r="40" spans="44:56">
@@ -9773,16 +9773,16 @@
         <v>407</v>
       </c>
       <c r="BA40" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="BB40" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="BC40">
-        <v>0.99691534062855203</v>
+        <v>0.99439449087123744</v>
       </c>
       <c r="BD40">
-        <v>56.552088476546054</v>
+        <v>102.76766736064755</v>
       </c>
     </row>
     <row r="41" spans="44:56">
@@ -9811,16 +9811,16 @@
         <v>409</v>
       </c>
       <c r="BA41" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="BB41" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="BC41">
-        <v>0.96341374264179058</v>
+        <v>0.99053075643264799</v>
       </c>
       <c r="BD41">
-        <v>670.74805156717241</v>
+        <v>173.60279873478748</v>
       </c>
     </row>
     <row r="42" spans="44:56">
@@ -9849,16 +9849,16 @@
         <v>411</v>
       </c>
       <c r="BA42" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="BB42" t="s">
-        <v>474</v>
+        <v>425</v>
       </c>
       <c r="BC42">
-        <v>0.99511226039729839</v>
+        <v>0.98039565814133589</v>
       </c>
       <c r="BD42">
-        <v>89.608559382863291</v>
+        <v>359.41293407550836</v>
       </c>
     </row>
     <row r="43" spans="44:56">
@@ -9893,10 +9893,10 @@
         <v>476</v>
       </c>
       <c r="BC43">
-        <v>0.9960370911532308</v>
+        <v>0.9877150845460122</v>
       </c>
       <c r="BD43">
-        <v>72.653328857434573</v>
+        <v>225.22344998977596</v>
       </c>
     </row>
   </sheetData>
@@ -9905,7 +9905,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2755721A-ED27-445B-8407-4C497A8C40DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D0FA5E4-FEB2-4568-953C-8C71975D872C}">
   <dimension ref="B9:Z43"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10017,7 +10017,7 @@
         <v>477</v>
       </c>
       <c r="K11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L11">
         <v>8.3728062197205944</v>
@@ -10050,7 +10050,7 @@
         <v>507</v>
       </c>
       <c r="X11" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="Y11">
         <v>2.177</v>
@@ -10085,7 +10085,7 @@
         <v>479</v>
       </c>
       <c r="K12" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L12">
         <v>42.531235680568031</v>
@@ -10118,13 +10118,13 @@
         <v>509</v>
       </c>
       <c r="X12" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="Y12">
-        <v>47.905999999999999</v>
+        <v>32.750999999999998</v>
       </c>
       <c r="Z12">
-        <v>0.39630773122137791</v>
+        <v>0.4149952637595713</v>
       </c>
     </row>
     <row r="13" spans="2:26">
@@ -10153,7 +10153,7 @@
         <v>481</v>
       </c>
       <c r="K13" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L13">
         <v>30.271312154499352</v>
@@ -10186,13 +10186,13 @@
         <v>511</v>
       </c>
       <c r="X13" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Y13">
-        <v>91.13</v>
+        <v>84.296000000000006</v>
       </c>
       <c r="Z13">
-        <v>0.44286743234979481</v>
+        <v>0.45002333050960358</v>
       </c>
     </row>
     <row r="14" spans="2:26">
@@ -10254,7 +10254,7 @@
         <v>513</v>
       </c>
       <c r="X14" t="s">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="Y14">
         <v>30.484999999999999</v>
@@ -10289,7 +10289,7 @@
         <v>485</v>
       </c>
       <c r="K15" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="L15">
         <v>29.120153762247021</v>
@@ -10322,7 +10322,7 @@
         <v>515</v>
       </c>
       <c r="X15" t="s">
-        <v>475</v>
+        <v>428</v>
       </c>
       <c r="Y15">
         <v>6.726</v>
@@ -10357,7 +10357,7 @@
         <v>487</v>
       </c>
       <c r="K16" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="L16">
         <v>10.867385180190169</v>
@@ -10390,7 +10390,7 @@
         <v>517</v>
       </c>
       <c r="X16" t="s">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="Y16">
         <v>33.183</v>
@@ -10425,7 +10425,7 @@
         <v>489</v>
       </c>
       <c r="K17" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="L17">
         <v>32.115075062865692</v>
@@ -10458,13 +10458,13 @@
         <v>519</v>
       </c>
       <c r="X17" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="Y17">
-        <v>40.698999999999998</v>
+        <v>3.617</v>
       </c>
       <c r="Z17">
-        <v>0.37792367562576878</v>
+        <v>0.24168407961239979</v>
       </c>
     </row>
     <row r="18" spans="2:26">
@@ -10493,7 +10493,7 @@
         <v>491</v>
       </c>
       <c r="K18" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="L18">
         <v>9.0868240253443027</v>
@@ -10526,13 +10526,13 @@
         <v>521</v>
       </c>
       <c r="X18" t="s">
-        <v>454</v>
+        <v>422</v>
       </c>
       <c r="Y18">
-        <v>43.79</v>
+        <v>45.468000000000004</v>
       </c>
       <c r="Z18">
-        <v>0.42069502992921548</v>
+        <v>0.37157095621951258</v>
       </c>
     </row>
     <row r="19" spans="2:26">
@@ -10561,7 +10561,7 @@
         <v>493</v>
       </c>
       <c r="K19" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="L19">
         <v>18.016423245563796</v>
@@ -10594,13 +10594,13 @@
         <v>523</v>
       </c>
       <c r="X19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="Y19">
-        <v>3.617</v>
+        <v>60.06</v>
       </c>
       <c r="Z19">
-        <v>0.24168407961239979</v>
+        <v>0.43959926703691221</v>
       </c>
     </row>
     <row r="20" spans="2:26">
@@ -10629,7 +10629,7 @@
         <v>495</v>
       </c>
       <c r="K20" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L20">
         <v>0.75250112047637663</v>
@@ -10662,13 +10662,13 @@
         <v>525</v>
       </c>
       <c r="X20" t="s">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="Y20">
-        <v>45.468000000000004</v>
+        <v>70.188999999999993</v>
       </c>
       <c r="Z20">
-        <v>0.37157095621951258</v>
+        <v>0.36475020734260799</v>
       </c>
     </row>
     <row r="21" spans="2:26">
@@ -10697,7 +10697,7 @@
         <v>497</v>
       </c>
       <c r="K21" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="L21">
         <v>18.381813037942475</v>
@@ -10730,13 +10730,13 @@
         <v>527</v>
       </c>
       <c r="X21" t="s">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="Y21">
-        <v>33.305</v>
+        <v>40.698999999999998</v>
       </c>
       <c r="Z21">
-        <v>0.3615930122116382</v>
+        <v>0.37792367562576878</v>
       </c>
     </row>
     <row r="22" spans="2:26">
@@ -10765,7 +10765,7 @@
         <v>499</v>
       </c>
       <c r="K22" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="L22">
         <v>4.5221914845937041</v>
@@ -10798,13 +10798,13 @@
         <v>529</v>
       </c>
       <c r="X22" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="Y22">
-        <v>26.634</v>
+        <v>28.895</v>
       </c>
       <c r="Z22">
-        <v>0.4581408616860102</v>
+        <v>0.4388644768658766</v>
       </c>
     </row>
     <row r="23" spans="2:26">
@@ -10833,7 +10833,7 @@
         <v>501</v>
       </c>
       <c r="K23" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="L23">
         <v>8.2953562793919264</v>
@@ -10866,13 +10866,13 @@
         <v>531</v>
       </c>
       <c r="X23" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="Y23">
-        <v>32.006</v>
+        <v>259.62099999999998</v>
       </c>
       <c r="Z23">
-        <v>0.4896460680814318</v>
+        <v>0.80103658565450375</v>
       </c>
     </row>
     <row r="24" spans="2:26">
@@ -10901,7 +10901,7 @@
         <v>503</v>
       </c>
       <c r="K24" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="L24">
         <v>1.2792726734837132</v>
@@ -10934,13 +10934,13 @@
         <v>533</v>
       </c>
       <c r="X24" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="Y24">
-        <v>92.117999999999995</v>
+        <v>96.406999999999996</v>
       </c>
       <c r="Z24">
-        <v>0.62860555778735661</v>
+        <v>0.79274433267354172</v>
       </c>
     </row>
     <row r="25" spans="2:26">
@@ -10969,7 +10969,7 @@
         <v>505</v>
       </c>
       <c r="K25" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="L25">
         <v>1.6182682752282065</v>
@@ -11002,13 +11002,13 @@
         <v>535</v>
       </c>
       <c r="X25" t="s">
-        <v>473</v>
+        <v>417</v>
       </c>
       <c r="Y25">
-        <v>6.194</v>
+        <v>218.93100000000001</v>
       </c>
       <c r="Z25">
-        <v>0.38156880578624569</v>
+        <v>0.77232429046058915</v>
       </c>
     </row>
     <row r="26" spans="2:26">
@@ -11037,13 +11037,13 @@
         <v>537</v>
       </c>
       <c r="X26" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="Y26">
-        <v>55.912999999999997</v>
+        <v>164.86799999999999</v>
       </c>
       <c r="Z26">
-        <v>0.65599145251831115</v>
+        <v>0.72650931190792389</v>
       </c>
     </row>
     <row r="27" spans="2:26">
@@ -11072,13 +11072,13 @@
         <v>539</v>
       </c>
       <c r="X27" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="Y27">
-        <v>164.86799999999999</v>
+        <v>177.54</v>
       </c>
       <c r="Z27">
-        <v>0.72650931190792389</v>
+        <v>0.68803916449510105</v>
       </c>
     </row>
     <row r="28" spans="2:26">
@@ -11107,13 +11107,13 @@
         <v>541</v>
       </c>
       <c r="X28" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="Y28">
-        <v>177.54</v>
+        <v>32.006</v>
       </c>
       <c r="Z28">
-        <v>0.68803916449510105</v>
+        <v>0.4896460680814318</v>
       </c>
     </row>
     <row r="29" spans="2:26">
@@ -11142,13 +11142,13 @@
         <v>543</v>
       </c>
       <c r="X29" t="s">
-        <v>417</v>
+        <v>472</v>
       </c>
       <c r="Y29">
-        <v>234.209</v>
+        <v>92.117999999999995</v>
       </c>
       <c r="Z29">
-        <v>0.77345015707305564</v>
+        <v>0.62860555778735661</v>
       </c>
     </row>
     <row r="30" spans="2:26">
@@ -11177,13 +11177,13 @@
         <v>545</v>
       </c>
       <c r="X30" t="s">
-        <v>471</v>
+        <v>419</v>
       </c>
       <c r="Y30">
-        <v>340.75</v>
+        <v>6.194</v>
       </c>
       <c r="Z30">
-        <v>0.79920400199903174</v>
+        <v>0.38156880578624569</v>
       </c>
     </row>
     <row r="31" spans="2:26">
@@ -11212,13 +11212,13 @@
         <v>547</v>
       </c>
       <c r="X31" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Y31">
-        <v>20.597000000000001</v>
+        <v>55.912999999999997</v>
       </c>
       <c r="Z31">
-        <v>0.56041320139424933</v>
+        <v>0.65599145251831115</v>
       </c>
     </row>
     <row r="32" spans="2:26">
@@ -11247,7 +11247,7 @@
         <v>549</v>
       </c>
       <c r="X32" t="s">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="Y32">
         <v>45.517000000000003</v>
@@ -11282,13 +11282,13 @@
         <v>551</v>
       </c>
       <c r="X33" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="Y33">
-        <v>106.795</v>
+        <v>76.210999999999999</v>
       </c>
       <c r="Z33">
-        <v>0.49924622041540068</v>
+        <v>0.5468169336461739</v>
       </c>
     </row>
     <row r="34" spans="15:26">
@@ -11317,13 +11317,13 @@
         <v>553</v>
       </c>
       <c r="X34" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="Y34">
-        <v>36.399000000000001</v>
+        <v>44.996000000000002</v>
       </c>
       <c r="Z34">
-        <v>0.3471342957137602</v>
+        <v>0.42188049242982117</v>
       </c>
     </row>
     <row r="35" spans="15:26">
@@ -11352,13 +11352,13 @@
         <v>555</v>
       </c>
       <c r="X35" t="s">
-        <v>462</v>
+        <v>434</v>
       </c>
       <c r="Y35">
-        <v>70.254000000000005</v>
+        <v>69.513999999999996</v>
       </c>
       <c r="Z35">
-        <v>0.39409725839336718</v>
+        <v>0.43127662972358699</v>
       </c>
     </row>
     <row r="36" spans="15:26">
@@ -11387,13 +11387,13 @@
         <v>557</v>
       </c>
       <c r="X36" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="Y36">
-        <v>72.956000000000003</v>
+        <v>60.743000000000002</v>
       </c>
       <c r="Z36">
-        <v>0.44425172502430138</v>
+        <v>0.39077255435176689</v>
       </c>
     </row>
     <row r="37" spans="15:26">
@@ -11422,13 +11422,13 @@
         <v>559</v>
       </c>
       <c r="X37" t="s">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="Y37">
-        <v>19.841000000000001</v>
+        <v>72.956000000000003</v>
       </c>
       <c r="Z37">
-        <v>0.37558571129148788</v>
+        <v>0.44425172502430138</v>
       </c>
     </row>
     <row r="38" spans="15:26">
@@ -11457,13 +11457,13 @@
         <v>561</v>
       </c>
       <c r="X38" t="s">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="Y38">
-        <v>138.42500000000001</v>
+        <v>19.841000000000001</v>
       </c>
       <c r="Z38">
-        <v>0.3667297322843705</v>
+        <v>0.37558571129148788</v>
       </c>
     </row>
     <row r="39" spans="15:26">
@@ -11492,13 +11492,13 @@
         <v>563</v>
       </c>
       <c r="X39" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="Y39">
-        <v>60.06</v>
+        <v>138.42500000000001</v>
       </c>
       <c r="Z39">
-        <v>0.43959926703691221</v>
+        <v>0.3667297322843705</v>
       </c>
     </row>
     <row r="40" spans="15:26">
@@ -11527,7 +11527,7 @@
         <v>565</v>
       </c>
       <c r="X40" t="s">
-        <v>446</v>
+        <v>475</v>
       </c>
       <c r="Y40">
         <v>142.483</v>
@@ -11562,7 +11562,7 @@
         <v>567</v>
       </c>
       <c r="X41" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="Y41">
         <v>20.327999999999999</v>
@@ -11597,13 +11597,13 @@
         <v>569</v>
       </c>
       <c r="X42" t="s">
-        <v>469</v>
+        <v>448</v>
       </c>
       <c r="Y42">
-        <v>23.687000000000001</v>
+        <v>65.320999999999998</v>
       </c>
       <c r="Z42">
-        <v>0.47565669805874711</v>
+        <v>0.4965068538533049</v>
       </c>
     </row>
     <row r="43" spans="15:26">
@@ -11632,13 +11632,13 @@
         <v>571</v>
       </c>
       <c r="X43" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="Y43">
-        <v>65.320999999999998</v>
+        <v>32.902000000000001</v>
       </c>
       <c r="Z43">
-        <v>0.4965068538533049</v>
+        <v>0.43396218713816731</v>
       </c>
     </row>
   </sheetData>
@@ -11647,7 +11647,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{824049A4-6246-4688-80B1-D6F8647243B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C167C9A6-CF52-4DA2-8528-B84871055501}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA438199-708E-4F07-BC4D-82ADA6D37F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{82188418-9902-42D3-8EBC-145AE3158EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -844,24 +844,96 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_002</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_010</t>
   </si>
   <si>
@@ -874,130 +946,106 @@
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w93419960-220,e_w409049317-220,e_w95512216-220,e_w270556206-220,e_w148300699-220,e_NZ13-220,e_w167283894-220</t>
+  </si>
+  <si>
+    <t>e_w180519027-220,e_w89636510-220,e_NZ30-220</t>
+  </si>
+  <si>
+    <t>e_w95046918-220,e_w95048289-220,e_NZ27-220,e_w167705537-220</t>
+  </si>
+  <si>
+    <t>e_w95046918-220,e_NZ27-220,e_w167705537-220,e_w95343089-220,e_w93713118-220,e_NZ26-220,e_w95344674-220,e_w1026587442-220</t>
+  </si>
+  <si>
     <t>e_w89943957-220,e_w232382576-220</t>
   </si>
   <si>
     <t>e_r17609399-220,e_w95344674-220,e_w191346761-220,e_w167572576-220,e_NZ23-220,e_NZ21-220</t>
   </si>
   <si>
+    <t>e_NZ31-220,e_NZ30-220,e_w1099619174-220,e_w95048289-220</t>
+  </si>
+  <si>
+    <t>e_w412588974-220,e_NZ41-220,e_w268841395-220,e_w180519027-220,e_NZ42-220</t>
+  </si>
+  <si>
+    <t>e_w167427251-220,e_w94053861-220,e_w89411122-220,e_NZ14-220</t>
+  </si>
+  <si>
+    <t>e_w89637277-220,e_w94840399-220,e_NZ32-220,e_w167286837-220,e_w268826084-220</t>
+  </si>
+  <si>
+    <t>e_w268841395-220,e_w90092620-220,e_w180514007-220,e_w270521928-220</t>
+  </si>
+  <si>
+    <t>e_w412589726-220,e_w180519027-220</t>
+  </si>
+  <si>
+    <t>e_NZ40-220,e_w180519027-220,e_w414953388-220,e_NZ38-220,e_w89636510-220</t>
+  </si>
+  <si>
+    <t>e_w1099619174-220,e_w93827784-220,e_w100957314-220,e_w95046918-220</t>
+  </si>
+  <si>
     <t>e_NZ41-220</t>
   </si>
   <si>
     <t>e_w26671244-220,e_w61853727-220,e_w167293888-220,e_NZ3-220,e_w82881422-220,e_w270022030-220,e_w119877500-220,e_NZ5-220</t>
   </si>
   <si>
-    <t>e_NZ31-220,e_NZ30-220,e_w1099619174-220,e_w95048289-220</t>
-  </si>
-  <si>
-    <t>e_w412589726-220,e_w180519027-220</t>
-  </si>
-  <si>
-    <t>e_NZ40-220,e_w180519027-220,e_w414953388-220,e_NZ38-220,e_w89636510-220</t>
-  </si>
-  <si>
-    <t>e_w1099619174-220,e_w93827784-220,e_w100957314-220,e_w95046918-220</t>
-  </si>
-  <si>
-    <t>e_w89637277-220,e_w94840399-220,e_NZ32-220,e_w167286837-220,e_w268826084-220</t>
-  </si>
-  <si>
-    <t>e_w93419960-220,e_w409049317-220,e_w95512216-220,e_w270556206-220,e_w148300699-220,e_NZ13-220,e_w167283894-220</t>
-  </si>
-  <si>
-    <t>e_w167427251-220,e_w94053861-220,e_w89411122-220,e_NZ14-220</t>
-  </si>
-  <si>
-    <t>e_w268841395-220,e_w90092620-220,e_w180514007-220,e_w270521928-220</t>
-  </si>
-  <si>
-    <t>e_w180519027-220,e_w89636510-220,e_NZ30-220</t>
-  </si>
-  <si>
-    <t>e_w95046918-220,e_w95048289-220,e_NZ27-220,e_w167705537-220</t>
-  </si>
-  <si>
-    <t>e_w95046918-220,e_NZ27-220,e_w167705537-220,e_w95343089-220,e_w93713118-220,e_NZ26-220,e_w95344674-220,e_w1026587442-220</t>
-  </si>
-  <si>
-    <t>e_w412588974-220,e_NZ41-220,e_w268841395-220,e_w180519027-220,e_NZ42-220</t>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
     <t>distr_wonelc_won_009</t>
@@ -1006,6 +1054,24 @@
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_005</t>
   </si>
   <si>
@@ -1024,70 +1090,52 @@
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w95048289-220,e_NZ27-220</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w89943957-220,e_w232382576-220,e_w26671244-220,e_w61853727-220,e_w167293888-220,e_NZ3-220,e_w82881422-220,e_w119877500-220,e_NZ5-220</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w95048289-220,e_w167705537-220,e_r17609399-220,e_NZ26-220,e_w95344674-220,e_w191346761-220,e_w1026587442-220,e_w167572576-220,e_NZ23-220,e_NZ21-220</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w167705537-220,e_w95343089-220,e_w93713118-220,e_w1026587442-220</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_NZ41-220,e_w412589726-220,e_w268841395-220,e_w180519027-220</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_NZ41-220,e_w412589726-220,e_w180519027-220,e_w89636510-220</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w167286837-220,e_w268826084-220,e_w1099619174-220,e_w100957314-220,e_w93827784-220</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w95048289-220,e_w95046918-220,e_NZ27-220</t>
   </si>
   <si>
     <t>elc_won_009</t>
@@ -1096,6 +1144,24 @@
     <t>e_NZ41-220,e_w412588974-220,e_w268841395-220,e_NZ42-220</t>
   </si>
   <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w167427251-220,e_w94053861-220,e_w89411122-220,e_NZ14-220,e_w270022030-220</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w90092620-220,e_w180514007-220,e_w270521928-220,e_w89637277-220,e_w94840399-220</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_NZ30-220,e_w1099619174-220</t>
+  </si>
+  <si>
     <t>elc_won_005</t>
   </si>
   <si>
@@ -1111,70 +1177,130 @@
     <t>e_NZ31-220,e_w268826084-220,e_w1099619174-220,e_w93827784-220,e_w95046918-220</t>
   </si>
   <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w167705537-220,e_w95343089-220,e_w93713118-220,e_w1026587442-220</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w90092620-220,e_w180514007-220,e_w270521928-220,e_w89637277-220,e_w94840399-220</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_NZ41-220,e_w412589726-220,e_w268841395-220,e_w180519027-220</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w95048289-220,e_w167705537-220,e_r17609399-220,e_NZ26-220,e_w95344674-220,e_w191346761-220,e_w1026587442-220,e_w167572576-220,e_NZ23-220,e_NZ21-220</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_NZ30-220,e_w1099619174-220</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w89943957-220,e_w232382576-220,e_w26671244-220,e_w61853727-220,e_w167293888-220,e_NZ3-220,e_w82881422-220,e_w119877500-220,e_NZ5-220</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_NZ41-220,e_w412589726-220,e_w180519027-220,e_w89636510-220</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w167286837-220,e_w268826084-220,e_w1099619174-220,e_w100957314-220,e_w93827784-220</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w95048289-220,e_w95046918-220,e_NZ27-220</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w95048289-220,e_NZ27-220</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w167427251-220,e_w94053861-220,e_w89411122-220,e_NZ14-220,e_w270022030-220</t>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_wofelc_wof_026</t>
@@ -1183,36 +1309,6 @@
     <t>connecting wind offshore to buses in cluster 26</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_018</t>
   </si>
   <si>
@@ -1225,52 +1321,16 @@
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wofelc_wof_024</t>
@@ -1297,36 +1357,6 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_013</t>
   </si>
   <si>
@@ -1345,34 +1375,121 @@
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_w412588974-220,e_NZ42-220,e_w270521928-220</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_NZ30-220,e_w95048289-220</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_w412589726-220</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w188180344-220,e_w61853727-220</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_NZ41-220,e_w412588974-220,e_w270521928-220</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_r17609399-220</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_w100957314-220,e_w93827784-220,e_w95046918-220</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_w100957314-220,e_w95343089-220,e_w93713118-220,e_w1026587442-220</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_w412588974-220</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_NZ41-220,e_w412589726-220,e_w412588974-220</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_w93713118-220,e_w1167708390-220,e_w1026587442-220,e_w167572576-220,e_w93419960-220</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_w95048289-220,e_NZ27-220,e_r17609399-220,e_w167705537-220</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_w412588974-220,e_NZ41-220</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>e_w95046918-220,e_w95343089-220,e_w93713118-220</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w89943957-220</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w232382576-220,e_w89943957-220,e_w1363994055-220,e_w82881422-220,e_NZ3-220</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w167427251-220,e_NZ9-220,e_w167293888-220,e_NZ8-220,e_NZ5-220</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_w89637277-220,e_w100957314-220,e_w93713118-220</t>
   </si>
   <si>
     <t>elc_wof_026</t>
@@ -1381,33 +1498,6 @@
     <t>e_w167286837-220,e_w268826084-220,e_NZ29-220,e_w100957314-220</t>
   </si>
   <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_w412588974-220</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_w412589726-220</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w188180344-220,e_w61853727-220</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_NZ30-220,e_w95048289-220</t>
-  </si>
-  <si>
     <t>elc_wof_018</t>
   </si>
   <si>
@@ -1420,52 +1510,16 @@
     <t>e_w95512216-220,e_NZ13-220</t>
   </si>
   <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_NZ41-220,e_w412588974-220,e_w270521928-220</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_r17609399-220</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_w100957314-220,e_w93827784-220,e_w95046918-220</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_w100957314-220,e_w95343089-220,e_w93713118-220,e_w1026587442-220</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w232382576-220,e_w89943957-220,e_w1363994055-220,e_w82881422-220,e_NZ3-220</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w167427251-220,e_NZ9-220,e_w167293888-220,e_NZ8-220,e_NZ5-220</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_w89637277-220,e_w100957314-220,e_w93713118-220</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_NZ41-220,e_w412589726-220,e_w412588974-220</t>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>e_w100957314-220,e_w95343089-220</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_w93419960-220,e_w95512216-220</t>
   </si>
   <si>
     <t>elc_wof_024</t>
@@ -1489,33 +1543,6 @@
     <t>elc_wof_001</t>
   </si>
   <si>
-    <t>e_w89943957-220</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_w93713118-220,e_w1167708390-220,e_w1026587442-220,e_w167572576-220,e_w93419960-220</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_w412588974-220,e_NZ41-220</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>e_w95046918-220,e_w95343089-220,e_w93713118-220</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
     <t>elc_wof_013</t>
   </si>
   <si>
@@ -1532,33 +1559,6 @@
   </si>
   <si>
     <t>e_w95512216-220,e_NZ13-220,e_w167283894-220</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>e_w100957314-220,e_w95343089-220</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_w93419960-220,e_w95512216-220</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_w412588974-220,e_NZ42-220,e_w270521928-220</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_w95048289-220,e_NZ27-220,e_r17609399-220,e_w167705537-220</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6777,7 +6777,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3F7E0EE-A8C0-4D08-90A3-D373DDDDB3E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C11669-6791-4422-8D49-365020E06D77}">
   <dimension ref="B9:BD43"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7015,16 +7015,16 @@
         <v>238</v>
       </c>
       <c r="Y11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Z11" t="s">
         <v>274</v>
       </c>
       <c r="AA11">
-        <v>0.99541580702824473</v>
+        <v>0.99649838493007836</v>
       </c>
       <c r="AB11">
-        <v>84.0435378155141</v>
+        <v>64.196276281897482</v>
       </c>
       <c r="AD11" t="s">
         <v>237</v>
@@ -7057,10 +7057,10 @@
         <v>321</v>
       </c>
       <c r="AO11">
-        <v>0.9975157188831717</v>
+        <v>0.99692224665834439</v>
       </c>
       <c r="AP11">
-        <v>45.545153808519316</v>
+        <v>56.425477930352955</v>
       </c>
       <c r="AR11" t="s">
         <v>237</v>
@@ -7093,10 +7093,10 @@
         <v>416</v>
       </c>
       <c r="BC11">
-        <v>0.99402092584318991</v>
+        <v>0.99053075643264799</v>
       </c>
       <c r="BD11">
-        <v>109.61635954151812</v>
+        <v>173.60279873478748</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7161,16 +7161,16 @@
         <v>242</v>
       </c>
       <c r="Y12" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="Z12" t="s">
         <v>275</v>
       </c>
       <c r="AA12">
-        <v>0.9981722170039925</v>
+        <v>0.99568371668484024</v>
       </c>
       <c r="AB12">
-        <v>33.509354926805031</v>
+        <v>79.131860777928608</v>
       </c>
       <c r="AD12" t="s">
         <v>237</v>
@@ -7200,13 +7200,13 @@
         <v>322</v>
       </c>
       <c r="AN12" t="s">
-        <v>283</v>
+        <v>323</v>
       </c>
       <c r="AO12">
-        <v>0.99595483459575906</v>
+        <v>0.99725701149052537</v>
       </c>
       <c r="AP12">
-        <v>74.161365744417125</v>
+        <v>50.288122673700855</v>
       </c>
       <c r="AR12" t="s">
         <v>237</v>
@@ -7239,10 +7239,10 @@
         <v>418</v>
       </c>
       <c r="BC12">
-        <v>0.97533397850909798</v>
+        <v>0.98039565814133589</v>
       </c>
       <c r="BD12">
-        <v>452.21039399987052</v>
+        <v>359.41293407550836</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7307,16 +7307,16 @@
         <v>244</v>
       </c>
       <c r="Y13" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Z13" t="s">
         <v>276</v>
       </c>
       <c r="AA13">
-        <v>0.9958319028842455</v>
+        <v>0.99673728461460676</v>
       </c>
       <c r="AB13">
-        <v>76.415113788833068</v>
+        <v>59.816448732209111</v>
       </c>
       <c r="AD13" t="s">
         <v>237</v>
@@ -7343,16 +7343,16 @@
         <v>294</v>
       </c>
       <c r="AM13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO13">
-        <v>0.99857516825685033</v>
+        <v>0.99807547980555666</v>
       </c>
       <c r="AP13">
-        <v>26.121915291078167</v>
+        <v>35.282870231460656</v>
       </c>
       <c r="AR13" t="s">
         <v>237</v>
@@ -7453,16 +7453,16 @@
         <v>246</v>
       </c>
       <c r="Y14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Z14" t="s">
         <v>277</v>
       </c>
       <c r="AA14">
-        <v>0.9986195737404916</v>
+        <v>0.99709164861435029</v>
       </c>
       <c r="AB14">
-        <v>25.307814757654675</v>
+        <v>53.319775403577559</v>
       </c>
       <c r="AD14" t="s">
         <v>237</v>
@@ -7489,16 +7489,16 @@
         <v>296</v>
       </c>
       <c r="AM14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO14">
-        <v>0.99624198670989172</v>
+        <v>0.99665105279570931</v>
       </c>
       <c r="AP14">
-        <v>68.896910318651507</v>
+        <v>61.397365411996212</v>
       </c>
       <c r="AR14" t="s">
         <v>237</v>
@@ -7528,7 +7528,7 @@
         <v>421</v>
       </c>
       <c r="BB14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="BC14">
         <v>0.98183461816751461</v>
@@ -7599,16 +7599,16 @@
         <v>248</v>
       </c>
       <c r="Y15" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="Z15" t="s">
         <v>278</v>
       </c>
       <c r="AA15">
-        <v>0.99164479201276912</v>
+        <v>0.99541580702824473</v>
       </c>
       <c r="AB15">
-        <v>153.17881309923388</v>
+        <v>84.0435378155141</v>
       </c>
       <c r="AD15" t="s">
         <v>237</v>
@@ -7635,16 +7635,16 @@
         <v>298</v>
       </c>
       <c r="AM15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO15">
-        <v>0.99665105279570931</v>
+        <v>0.99590345602074126</v>
       </c>
       <c r="AP15">
-        <v>61.397365411996212</v>
+        <v>75.103306286410302</v>
       </c>
       <c r="AR15" t="s">
         <v>237</v>
@@ -7745,16 +7745,16 @@
         <v>250</v>
       </c>
       <c r="Y16" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Z16" t="s">
         <v>279</v>
       </c>
       <c r="AA16">
-        <v>0.99552574319771747</v>
+        <v>0.9981722170039925</v>
       </c>
       <c r="AB16">
-        <v>82.028041375179441</v>
+        <v>33.509354926805031</v>
       </c>
       <c r="AD16" t="s">
         <v>237</v>
@@ -7781,16 +7781,16 @@
         <v>300</v>
       </c>
       <c r="AM16" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO16">
-        <v>0.99761292756299069</v>
+        <v>0.99446613913875159</v>
       </c>
       <c r="AP16">
-        <v>43.762994678503716</v>
+        <v>101.45411578955439</v>
       </c>
       <c r="AR16" t="s">
         <v>237</v>
@@ -7823,10 +7823,10 @@
         <v>425</v>
       </c>
       <c r="BC16">
-        <v>0.9878288138539939</v>
+        <v>0.98596601099553871</v>
       </c>
       <c r="BD16">
-        <v>223.13841267677765</v>
+        <v>257.2897984151241</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7891,16 +7891,16 @@
         <v>252</v>
       </c>
       <c r="Y17" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="Z17" t="s">
         <v>280</v>
       </c>
       <c r="AA17">
-        <v>0.99856414548474748</v>
+        <v>0.99164479201276912</v>
       </c>
       <c r="AB17">
-        <v>26.323999446296273</v>
+        <v>153.17881309923388</v>
       </c>
       <c r="AD17" t="s">
         <v>237</v>
@@ -7927,16 +7927,16 @@
         <v>302</v>
       </c>
       <c r="AM17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO17">
-        <v>0.99590345602074126</v>
+        <v>0.99821201020674788</v>
       </c>
       <c r="AP17">
-        <v>75.103306286410302</v>
+        <v>32.77981287628851</v>
       </c>
       <c r="AR17" t="s">
         <v>237</v>
@@ -7969,10 +7969,10 @@
         <v>427</v>
       </c>
       <c r="BC17">
-        <v>0.99503867375582744</v>
+        <v>0.992142345264865</v>
       </c>
       <c r="BD17">
-        <v>90.957647809829638</v>
+        <v>144.05700347747464</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8037,16 +8037,16 @@
         <v>254</v>
       </c>
       <c r="Y18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Z18" t="s">
         <v>281</v>
       </c>
       <c r="AA18">
-        <v>0.99837169372341228</v>
+        <v>0.99656426482871763</v>
       </c>
       <c r="AB18">
-        <v>29.852281737441412</v>
+        <v>62.988478140176163</v>
       </c>
       <c r="AD18" t="s">
         <v>237</v>
@@ -8073,16 +8073,16 @@
         <v>304</v>
       </c>
       <c r="AM18" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN18" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO18">
-        <v>0.99807547980555666</v>
+        <v>0.99562511313409086</v>
       </c>
       <c r="AP18">
-        <v>35.282870231460656</v>
+        <v>80.206259208334231</v>
       </c>
       <c r="AR18" t="s">
         <v>237</v>
@@ -8115,10 +8115,10 @@
         <v>429</v>
       </c>
       <c r="BC18">
-        <v>0.9960370911532308</v>
+        <v>0.99199988291996133</v>
       </c>
       <c r="BD18">
-        <v>72.653328857434573</v>
+        <v>146.66881313404267</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8183,16 +8183,16 @@
         <v>256</v>
       </c>
       <c r="Y19" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="Z19" t="s">
         <v>282</v>
       </c>
       <c r="AA19">
-        <v>0.99781284363204548</v>
+        <v>0.9982917156958806</v>
       </c>
       <c r="AB19">
-        <v>40.097866745833329</v>
+        <v>31.318545575522229</v>
       </c>
       <c r="AD19" t="s">
         <v>237</v>
@@ -8219,16 +8219,16 @@
         <v>306</v>
       </c>
       <c r="AM19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO19">
-        <v>0.99239099026325794</v>
+        <v>0.9975157188831717</v>
       </c>
       <c r="AP19">
-        <v>139.49851184027145</v>
+        <v>45.545153808519316</v>
       </c>
       <c r="AR19" t="s">
         <v>237</v>
@@ -8261,10 +8261,10 @@
         <v>431</v>
       </c>
       <c r="BC19">
-        <v>0.98596601099553871</v>
+        <v>0.98560960960201449</v>
       </c>
       <c r="BD19">
-        <v>257.2897984151241</v>
+        <v>263.82382396306684</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8329,16 +8329,16 @@
         <v>258</v>
       </c>
       <c r="Y20" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="Z20" t="s">
         <v>283</v>
       </c>
       <c r="AA20">
-        <v>0.99649838493007836</v>
+        <v>0.99781284363204548</v>
       </c>
       <c r="AB20">
-        <v>64.196276281897482</v>
+        <v>40.097866745833329</v>
       </c>
       <c r="AD20" t="s">
         <v>237</v>
@@ -8365,16 +8365,16 @@
         <v>308</v>
       </c>
       <c r="AM20" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN20" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO20">
-        <v>0.99725701149052537</v>
+        <v>0.99826030196534266</v>
       </c>
       <c r="AP20">
-        <v>50.288122673700855</v>
+        <v>31.894463968718917</v>
       </c>
       <c r="AR20" t="s">
         <v>237</v>
@@ -8404,13 +8404,13 @@
         <v>432</v>
       </c>
       <c r="BB20" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="BC20">
-        <v>0.992142345264865</v>
+        <v>0.9878288138539939</v>
       </c>
       <c r="BD20">
-        <v>144.05700347747464</v>
+        <v>223.13841267677765</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8475,16 +8475,16 @@
         <v>260</v>
       </c>
       <c r="Y21" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z21" t="s">
         <v>284</v>
       </c>
       <c r="AA21">
-        <v>0.9982917156958806</v>
+        <v>0.99757939258365447</v>
       </c>
       <c r="AB21">
-        <v>31.318545575522229</v>
+        <v>44.377802633000776</v>
       </c>
       <c r="AD21" t="s">
         <v>237</v>
@@ -8511,16 +8511,16 @@
         <v>310</v>
       </c>
       <c r="AM21" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN21" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO21">
-        <v>0.99446613913875159</v>
+        <v>0.99761292756299069</v>
       </c>
       <c r="AP21">
-        <v>101.45411578955439</v>
+        <v>43.762994678503716</v>
       </c>
       <c r="AR21" t="s">
         <v>237</v>
@@ -8547,16 +8547,16 @@
         <v>369</v>
       </c>
       <c r="BA21" t="s">
+        <v>433</v>
+      </c>
+      <c r="BB21" t="s">
         <v>434</v>
       </c>
-      <c r="BB21" t="s">
-        <v>435</v>
-      </c>
       <c r="BC21">
-        <v>0.99199988291996133</v>
+        <v>0.97533397850909798</v>
       </c>
       <c r="BD21">
-        <v>146.66881313404267</v>
+        <v>452.21039399987052</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8621,16 +8621,16 @@
         <v>262</v>
       </c>
       <c r="Y22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Z22" t="s">
         <v>285</v>
       </c>
       <c r="AA22">
-        <v>0.99757939258365447</v>
+        <v>0.99552574319771747</v>
       </c>
       <c r="AB22">
-        <v>44.377802633000776</v>
+        <v>82.028041375179441</v>
       </c>
       <c r="AD22" t="s">
         <v>237</v>
@@ -8657,16 +8657,16 @@
         <v>312</v>
       </c>
       <c r="AM22" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN22" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO22">
-        <v>0.99821201020674788</v>
+        <v>0.99239099026325794</v>
       </c>
       <c r="AP22">
-        <v>32.77981287628851</v>
+        <v>139.49851184027145</v>
       </c>
       <c r="AR22" t="s">
         <v>237</v>
@@ -8693,16 +8693,16 @@
         <v>371</v>
       </c>
       <c r="BA22" t="s">
+        <v>435</v>
+      </c>
+      <c r="BB22" t="s">
         <v>436</v>
       </c>
-      <c r="BB22" t="s">
-        <v>437</v>
-      </c>
       <c r="BC22">
-        <v>0.98560960960201449</v>
+        <v>0.99048115912556611</v>
       </c>
       <c r="BD22">
-        <v>263.82382396306684</v>
+        <v>174.51208269795416</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8767,16 +8767,16 @@
         <v>264</v>
       </c>
       <c r="Y23" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Z23" t="s">
         <v>286</v>
       </c>
       <c r="AA23">
-        <v>0.99568371668484024</v>
+        <v>0.99856414548474748</v>
       </c>
       <c r="AB23">
-        <v>79.131860777928608</v>
+        <v>26.323999446296273</v>
       </c>
       <c r="AD23" t="s">
         <v>237</v>
@@ -8803,16 +8803,16 @@
         <v>314</v>
       </c>
       <c r="AM23" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN23" t="s">
-        <v>344</v>
+        <v>274</v>
       </c>
       <c r="AO23">
-        <v>0.99562511313409086</v>
+        <v>0.99595483459575906</v>
       </c>
       <c r="AP23">
-        <v>80.206259208334231</v>
+        <v>74.161365744417125</v>
       </c>
       <c r="AR23" t="s">
         <v>237</v>
@@ -8839,16 +8839,16 @@
         <v>373</v>
       </c>
       <c r="BA23" t="s">
+        <v>437</v>
+      </c>
+      <c r="BB23" t="s">
         <v>438</v>
       </c>
-      <c r="BB23" t="s">
-        <v>439</v>
-      </c>
       <c r="BC23">
-        <v>0.99342656473398216</v>
+        <v>0.99402264995370893</v>
       </c>
       <c r="BD23">
-        <v>120.51297987699346</v>
+        <v>109.58475084866993</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8913,16 +8913,16 @@
         <v>266</v>
       </c>
       <c r="Y24" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Z24" t="s">
         <v>287</v>
       </c>
       <c r="AA24">
-        <v>0.99673728461460676</v>
+        <v>0.99837169372341228</v>
       </c>
       <c r="AB24">
-        <v>59.816448732209111</v>
+        <v>29.852281737441412</v>
       </c>
       <c r="AD24" t="s">
         <v>237</v>
@@ -8955,10 +8955,10 @@
         <v>346</v>
       </c>
       <c r="AO24">
-        <v>0.99692224665834439</v>
+        <v>0.99857516825685033</v>
       </c>
       <c r="AP24">
-        <v>56.425477930352955</v>
+        <v>26.121915291078167</v>
       </c>
       <c r="AR24" t="s">
         <v>237</v>
@@ -8985,16 +8985,16 @@
         <v>375</v>
       </c>
       <c r="BA24" t="s">
+        <v>439</v>
+      </c>
+      <c r="BB24" t="s">
         <v>440</v>
       </c>
-      <c r="BB24" t="s">
-        <v>441</v>
-      </c>
       <c r="BC24">
-        <v>0.99728827252195684</v>
+        <v>0.9877150845460122</v>
       </c>
       <c r="BD24">
-        <v>49.715003764125143</v>
+        <v>225.22344998977596</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9059,16 +9059,16 @@
         <v>268</v>
       </c>
       <c r="Y25" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="Z25" t="s">
         <v>288</v>
       </c>
       <c r="AA25">
-        <v>0.99709164861435029</v>
+        <v>0.9958319028842455</v>
       </c>
       <c r="AB25">
-        <v>53.319775403577559</v>
+        <v>76.415113788833068</v>
       </c>
       <c r="AD25" t="s">
         <v>237</v>
@@ -9101,10 +9101,10 @@
         <v>348</v>
       </c>
       <c r="AO25">
-        <v>0.99826030196534266</v>
+        <v>0.99624198670989172</v>
       </c>
       <c r="AP25">
-        <v>31.894463968718917</v>
+        <v>68.896910318651507</v>
       </c>
       <c r="AR25" t="s">
         <v>237</v>
@@ -9131,16 +9131,16 @@
         <v>377</v>
       </c>
       <c r="BA25" t="s">
+        <v>441</v>
+      </c>
+      <c r="BB25" t="s">
         <v>442</v>
       </c>
-      <c r="BB25" t="s">
-        <v>443</v>
-      </c>
       <c r="BC25">
-        <v>0.94957327345368925</v>
+        <v>0.96374055461874508</v>
       </c>
       <c r="BD25">
-        <v>924.48998668236334</v>
+        <v>664.7564986563408</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9205,16 +9205,16 @@
         <v>270</v>
       </c>
       <c r="Y26" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="Z26" t="s">
         <v>289</v>
       </c>
       <c r="AA26">
-        <v>0.99656426482871763</v>
+        <v>0.9986195737404916</v>
       </c>
       <c r="AB26">
-        <v>62.988478140176163</v>
+        <v>25.307814757654675</v>
       </c>
       <c r="AR26" t="s">
         <v>237</v>
@@ -9241,16 +9241,16 @@
         <v>379</v>
       </c>
       <c r="BA26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="BB26" t="s">
-        <v>445</v>
+        <v>275</v>
       </c>
       <c r="BC26">
-        <v>0.99048115912556611</v>
+        <v>0.98974923036021278</v>
       </c>
       <c r="BD26">
-        <v>174.51208269795416</v>
+        <v>187.93077672943278</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9279,16 +9279,16 @@
         <v>381</v>
       </c>
       <c r="BA27" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="BB27" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="BC27">
-        <v>0.9955021345306051</v>
+        <v>0.99579892549254256</v>
       </c>
       <c r="BD27">
-        <v>82.460866938907401</v>
+        <v>77.019699303385977</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9317,16 +9317,16 @@
         <v>383</v>
       </c>
       <c r="BA28" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="BB28" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="BC28">
-        <v>0.99514843803074871</v>
+        <v>0.99338832047077197</v>
       </c>
       <c r="BD28">
-        <v>88.945302769606073</v>
+        <v>121.21412470251306</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9355,16 +9355,16 @@
         <v>385</v>
       </c>
       <c r="BA29" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="BB29" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="BC29">
-        <v>0.99052756852009682</v>
+        <v>0.99342656473398216</v>
       </c>
       <c r="BD29">
-        <v>173.66124379822571</v>
+        <v>120.51297987699346</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9393,16 +9393,16 @@
         <v>387</v>
       </c>
       <c r="BA30" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="BB30" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="BC30">
-        <v>0.95113733831453195</v>
+        <v>0.99728827252195684</v>
       </c>
       <c r="BD30">
-        <v>895.81546423358179</v>
+        <v>49.715003764125143</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9431,16 +9431,16 @@
         <v>389</v>
       </c>
       <c r="BA31" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="BB31" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="BC31">
-        <v>0.99402264995370893</v>
+        <v>0.94957327345368925</v>
       </c>
       <c r="BD31">
-        <v>109.58475084866993</v>
+        <v>924.48998668236334</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9469,16 +9469,16 @@
         <v>391</v>
       </c>
       <c r="BA32" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="BB32" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="BC32">
-        <v>0.96374055461874508</v>
+        <v>0.99402092584318991</v>
       </c>
       <c r="BD32">
-        <v>664.7564986563408</v>
+        <v>109.61635954151812</v>
       </c>
     </row>
     <row r="33" spans="44:56">
@@ -9507,16 +9507,16 @@
         <v>393</v>
       </c>
       <c r="BA33" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="BB33" t="s">
-        <v>286</v>
+        <v>457</v>
       </c>
       <c r="BC33">
-        <v>0.98974923036021278</v>
+        <v>0.99503867375582744</v>
       </c>
       <c r="BD33">
-        <v>187.93077672943278</v>
+        <v>90.957647809829638</v>
       </c>
     </row>
     <row r="34" spans="44:56">
@@ -9545,16 +9545,16 @@
         <v>395</v>
       </c>
       <c r="BA34" t="s">
+        <v>458</v>
+      </c>
+      <c r="BB34" t="s">
         <v>459</v>
       </c>
-      <c r="BB34" t="s">
-        <v>460</v>
-      </c>
       <c r="BC34">
-        <v>0.99579892549254256</v>
+        <v>0.9960370911532308</v>
       </c>
       <c r="BD34">
-        <v>77.019699303385977</v>
+        <v>72.653328857434573</v>
       </c>
     </row>
     <row r="35" spans="44:56">
@@ -9583,16 +9583,16 @@
         <v>397</v>
       </c>
       <c r="BA35" t="s">
+        <v>460</v>
+      </c>
+      <c r="BB35" t="s">
         <v>461</v>
       </c>
-      <c r="BB35" t="s">
-        <v>453</v>
-      </c>
       <c r="BC35">
-        <v>0.99338832047077197</v>
+        <v>0.98395883577792953</v>
       </c>
       <c r="BD35">
-        <v>121.21412470251306</v>
+        <v>294.08801073795939</v>
       </c>
     </row>
     <row r="36" spans="44:56">
@@ -9627,10 +9627,10 @@
         <v>463</v>
       </c>
       <c r="BC36">
-        <v>0.96365973275398331</v>
+        <v>0.99439449087123744</v>
       </c>
       <c r="BD36">
-        <v>666.23823284363971</v>
+        <v>102.76766736064755</v>
       </c>
     </row>
     <row r="37" spans="44:56">
@@ -9665,10 +9665,10 @@
         <v>465</v>
       </c>
       <c r="BC37">
-        <v>0.99508487560623826</v>
+        <v>0.9955021345306051</v>
       </c>
       <c r="BD37">
-        <v>90.110613885632716</v>
+        <v>82.460866938907401</v>
       </c>
     </row>
     <row r="38" spans="44:56">
@@ -9703,10 +9703,10 @@
         <v>467</v>
       </c>
       <c r="BC38">
-        <v>0.9871879084242271</v>
+        <v>0.99514843803074871</v>
       </c>
       <c r="BD38">
-        <v>234.88834555583597</v>
+        <v>88.945302769606073</v>
       </c>
     </row>
     <row r="39" spans="44:56">
@@ -9741,10 +9741,10 @@
         <v>469</v>
       </c>
       <c r="BC39">
-        <v>0.98395883577792953</v>
+        <v>0.99052756852009682</v>
       </c>
       <c r="BD39">
-        <v>294.08801073795939</v>
+        <v>173.66124379822571</v>
       </c>
     </row>
     <row r="40" spans="44:56">
@@ -9776,13 +9776,13 @@
         <v>470</v>
       </c>
       <c r="BB40" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="BC40">
-        <v>0.99439449087123744</v>
+        <v>0.95113733831453195</v>
       </c>
       <c r="BD40">
-        <v>102.76766736064755</v>
+        <v>895.81546423358179</v>
       </c>
     </row>
     <row r="41" spans="44:56">
@@ -9811,16 +9811,16 @@
         <v>409</v>
       </c>
       <c r="BA41" t="s">
+        <v>471</v>
+      </c>
+      <c r="BB41" t="s">
         <v>472</v>
       </c>
-      <c r="BB41" t="s">
-        <v>473</v>
-      </c>
       <c r="BC41">
-        <v>0.99053075643264799</v>
+        <v>0.96365973275398331</v>
       </c>
       <c r="BD41">
-        <v>173.60279873478748</v>
+        <v>666.23823284363971</v>
       </c>
     </row>
     <row r="42" spans="44:56">
@@ -9849,16 +9849,16 @@
         <v>411</v>
       </c>
       <c r="BA42" t="s">
+        <v>473</v>
+      </c>
+      <c r="BB42" t="s">
         <v>474</v>
       </c>
-      <c r="BB42" t="s">
-        <v>425</v>
-      </c>
       <c r="BC42">
-        <v>0.98039565814133589</v>
+        <v>0.99508487560623826</v>
       </c>
       <c r="BD42">
-        <v>359.41293407550836</v>
+        <v>90.110613885632716</v>
       </c>
     </row>
     <row r="43" spans="44:56">
@@ -9893,10 +9893,10 @@
         <v>476</v>
       </c>
       <c r="BC43">
-        <v>0.9877150845460122</v>
+        <v>0.9871879084242271</v>
       </c>
       <c r="BD43">
-        <v>225.22344998977596</v>
+        <v>234.88834555583597</v>
       </c>
     </row>
   </sheetData>
@@ -9905,7 +9905,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D0FA5E4-FEB2-4568-953C-8C71975D872C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E962DB0-E706-486A-83AC-B9BB9D5CA035}">
   <dimension ref="B9:Z43"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10017,7 +10017,7 @@
         <v>477</v>
       </c>
       <c r="K11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L11">
         <v>8.3728062197205944</v>
@@ -10050,7 +10050,7 @@
         <v>507</v>
       </c>
       <c r="X11" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="Y11">
         <v>2.177</v>
@@ -10085,7 +10085,7 @@
         <v>479</v>
       </c>
       <c r="K12" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="L12">
         <v>42.531235680568031</v>
@@ -10118,7 +10118,7 @@
         <v>509</v>
       </c>
       <c r="X12" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="Y12">
         <v>32.750999999999998</v>
@@ -10153,7 +10153,7 @@
         <v>481</v>
       </c>
       <c r="K13" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="L13">
         <v>30.271312154499352</v>
@@ -10221,7 +10221,7 @@
         <v>483</v>
       </c>
       <c r="K14" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="L14">
         <v>22.688073076145226</v>
@@ -10254,7 +10254,7 @@
         <v>513</v>
       </c>
       <c r="X14" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="Y14">
         <v>30.484999999999999</v>
@@ -10289,7 +10289,7 @@
         <v>485</v>
       </c>
       <c r="K15" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="L15">
         <v>29.120153762247021</v>
@@ -10322,7 +10322,7 @@
         <v>515</v>
       </c>
       <c r="X15" t="s">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="Y15">
         <v>6.726</v>
@@ -10357,7 +10357,7 @@
         <v>487</v>
       </c>
       <c r="K16" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="L16">
         <v>10.867385180190169</v>
@@ -10390,7 +10390,7 @@
         <v>517</v>
       </c>
       <c r="X16" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="Y16">
         <v>33.183</v>
@@ -10425,7 +10425,7 @@
         <v>489</v>
       </c>
       <c r="K17" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="L17">
         <v>32.115075062865692</v>
@@ -10458,7 +10458,7 @@
         <v>519</v>
       </c>
       <c r="X17" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="Y17">
         <v>3.617</v>
@@ -10493,7 +10493,7 @@
         <v>491</v>
       </c>
       <c r="K18" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="L18">
         <v>9.0868240253443027</v>
@@ -10561,7 +10561,7 @@
         <v>493</v>
       </c>
       <c r="K19" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="L19">
         <v>18.016423245563796</v>
@@ -10594,7 +10594,7 @@
         <v>523</v>
       </c>
       <c r="X19" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="Y19">
         <v>60.06</v>
@@ -10629,7 +10629,7 @@
         <v>495</v>
       </c>
       <c r="K20" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="L20">
         <v>0.75250112047637663</v>
@@ -10662,7 +10662,7 @@
         <v>525</v>
       </c>
       <c r="X20" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="Y20">
         <v>70.188999999999993</v>
@@ -10697,7 +10697,7 @@
         <v>497</v>
       </c>
       <c r="K21" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="L21">
         <v>18.381813037942475</v>
@@ -10730,7 +10730,7 @@
         <v>527</v>
       </c>
       <c r="X21" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="Y21">
         <v>40.698999999999998</v>
@@ -10765,7 +10765,7 @@
         <v>499</v>
       </c>
       <c r="K22" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="L22">
         <v>4.5221914845937041</v>
@@ -10798,7 +10798,7 @@
         <v>529</v>
       </c>
       <c r="X22" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="Y22">
         <v>28.895</v>
@@ -10833,7 +10833,7 @@
         <v>501</v>
       </c>
       <c r="K23" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="L23">
         <v>8.2953562793919264</v>
@@ -10866,7 +10866,7 @@
         <v>531</v>
       </c>
       <c r="X23" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="Y23">
         <v>259.62099999999998</v>
@@ -10901,7 +10901,7 @@
         <v>503</v>
       </c>
       <c r="K24" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="L24">
         <v>1.2792726734837132</v>
@@ -10934,7 +10934,7 @@
         <v>533</v>
       </c>
       <c r="X24" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="Y24">
         <v>96.406999999999996</v>
@@ -10969,7 +10969,7 @@
         <v>505</v>
       </c>
       <c r="K25" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="L25">
         <v>1.6182682752282065</v>
@@ -11002,7 +11002,7 @@
         <v>535</v>
       </c>
       <c r="X25" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="Y25">
         <v>218.93100000000001</v>
@@ -11037,7 +11037,7 @@
         <v>537</v>
       </c>
       <c r="X26" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="Y26">
         <v>164.86799999999999</v>
@@ -11072,7 +11072,7 @@
         <v>539</v>
       </c>
       <c r="X27" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="Y27">
         <v>177.54</v>
@@ -11107,7 +11107,7 @@
         <v>541</v>
       </c>
       <c r="X28" t="s">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="Y28">
         <v>32.006</v>
@@ -11142,7 +11142,7 @@
         <v>543</v>
       </c>
       <c r="X29" t="s">
-        <v>472</v>
+        <v>415</v>
       </c>
       <c r="Y29">
         <v>92.117999999999995</v>
@@ -11212,7 +11212,7 @@
         <v>547</v>
       </c>
       <c r="X31" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="Y31">
         <v>55.912999999999997</v>
@@ -11247,7 +11247,7 @@
         <v>549</v>
       </c>
       <c r="X32" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="Y32">
         <v>45.517000000000003</v>
@@ -11282,7 +11282,7 @@
         <v>551</v>
       </c>
       <c r="X33" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="Y33">
         <v>76.210999999999999</v>
@@ -11317,7 +11317,7 @@
         <v>553</v>
       </c>
       <c r="X34" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="Y34">
         <v>44.996000000000002</v>
@@ -11352,7 +11352,7 @@
         <v>555</v>
       </c>
       <c r="X35" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="Y35">
         <v>69.513999999999996</v>
@@ -11387,7 +11387,7 @@
         <v>557</v>
       </c>
       <c r="X36" t="s">
-        <v>415</v>
+        <v>454</v>
       </c>
       <c r="Y36">
         <v>60.743000000000002</v>
@@ -11422,7 +11422,7 @@
         <v>559</v>
       </c>
       <c r="X37" t="s">
-        <v>474</v>
+        <v>417</v>
       </c>
       <c r="Y37">
         <v>72.956000000000003</v>
@@ -11457,7 +11457,7 @@
         <v>561</v>
       </c>
       <c r="X38" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="Y38">
         <v>19.841000000000001</v>
@@ -11492,7 +11492,7 @@
         <v>563</v>
       </c>
       <c r="X39" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="Y39">
         <v>138.42500000000001</v>
@@ -11527,7 +11527,7 @@
         <v>565</v>
       </c>
       <c r="X40" t="s">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="Y40">
         <v>142.483</v>
@@ -11562,7 +11562,7 @@
         <v>567</v>
       </c>
       <c r="X41" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="Y41">
         <v>20.327999999999999</v>
@@ -11597,7 +11597,7 @@
         <v>569</v>
       </c>
       <c r="X42" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="Y42">
         <v>65.320999999999998</v>
@@ -11632,7 +11632,7 @@
         <v>571</v>
       </c>
       <c r="X43" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="Y43">
         <v>32.902000000000001</v>
@@ -11647,7 +11647,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C167C9A6-CF52-4DA2-8528-B84871055501}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB7543C-A9AC-463B-A3D3-9B62CD70D42F}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AAC3151-6BDE-4EEA-A62F-77726B7CB359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD20C665-346F-4587-9981-8007C14FE6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -813,52 +813,100 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_solelc_spv_011</t>
@@ -867,106 +915,82 @@
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w89637277-220,e_w94840399-220,e_NZ32-220,e_w167286837-220,e_w268826084-220</t>
+  </si>
+  <si>
+    <t>e_NZ31-220,e_NZ30-220,e_w1099619174-220,e_w95048289-220</t>
+  </si>
+  <si>
+    <t>e_w180519027-220,e_w89636510-220,e_NZ30-220</t>
+  </si>
+  <si>
+    <t>e_w95046918-220,e_w95048289-220,e_NZ27-220,e_w167705537-220</t>
+  </si>
+  <si>
+    <t>e_w95046918-220,e_NZ27-220,e_w167705537-220,e_w95343089-220,e_w93713118-220,e_NZ26-220,e_w95344674-220,e_w1026587442-220</t>
+  </si>
+  <si>
+    <t>e_w412589726-220,e_w180519027-220</t>
+  </si>
+  <si>
+    <t>e_NZ40-220,e_w180519027-220,e_w414953388-220,e_NZ38-220,e_w89636510-220</t>
+  </si>
+  <si>
+    <t>e_w1099619174-220,e_w93827784-220,e_w100957314-220,e_w95046918-220</t>
+  </si>
+  <si>
+    <t>e_w89943957-220,e_w232382576-220</t>
+  </si>
+  <si>
+    <t>e_r17609399-220,e_w95344674-220,e_w191346761-220,e_w167572576-220,e_NZ23-220,e_NZ21-220</t>
+  </si>
+  <si>
+    <t>e_w268841395-220,e_w90092620-220,e_w180514007-220,e_w270521928-220</t>
+  </si>
+  <si>
+    <t>e_w167427251-220,e_w94053861-220,e_w89411122-220,e_NZ14-220</t>
+  </si>
+  <si>
     <t>e_w93419960-220,e_w409049317-220,e_w95512216-220,e_w270556206-220,e_w148300699-220,e_NZ13-220,e_w167283894-220</t>
   </si>
   <si>
-    <t>e_w180519027-220,e_w89636510-220,e_NZ30-220</t>
-  </si>
-  <si>
-    <t>e_w95046918-220,e_w95048289-220,e_NZ27-220,e_w167705537-220</t>
-  </si>
-  <si>
-    <t>e_w95046918-220,e_NZ27-220,e_w167705537-220,e_w95343089-220,e_w93713118-220,e_NZ26-220,e_w95344674-220,e_w1026587442-220</t>
-  </si>
-  <si>
-    <t>e_NZ31-220,e_NZ30-220,e_w1099619174-220,e_w95048289-220</t>
-  </si>
-  <si>
-    <t>e_w89943957-220,e_w232382576-220</t>
-  </si>
-  <si>
-    <t>e_r17609399-220,e_w95344674-220,e_w191346761-220,e_w167572576-220,e_NZ23-220,e_NZ21-220</t>
+    <t>e_NZ41-220</t>
+  </si>
+  <si>
+    <t>e_w26671244-220,e_w61853727-220,e_w167293888-220,e_NZ3-220,e_w82881422-220,e_w270022030-220,e_w119877500-220,e_NZ5-220</t>
   </si>
   <si>
     <t>e_w412588974-220,e_NZ41-220,e_w268841395-220,e_w180519027-220,e_NZ42-220</t>
   </si>
   <si>
-    <t>e_w89637277-220,e_w94840399-220,e_NZ32-220,e_w167286837-220,e_w268826084-220</t>
-  </si>
-  <si>
-    <t>e_w268841395-220,e_w90092620-220,e_w180514007-220,e_w270521928-220</t>
-  </si>
-  <si>
-    <t>e_w167427251-220,e_w94053861-220,e_w89411122-220,e_NZ14-220</t>
-  </si>
-  <si>
-    <t>e_w412589726-220,e_w180519027-220</t>
-  </si>
-  <si>
-    <t>e_NZ40-220,e_w180519027-220,e_w414953388-220,e_NZ38-220,e_w89636510-220</t>
-  </si>
-  <si>
-    <t>e_w1099619174-220,e_w93827784-220,e_w100957314-220,e_w95046918-220</t>
-  </si>
-  <si>
-    <t>e_NZ41-220</t>
-  </si>
-  <si>
-    <t>e_w26671244-220,e_w61853727-220,e_w167293888-220,e_NZ3-220,e_w82881422-220,e_w270022030-220,e_w119877500-220,e_NZ5-220</t>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wonelc_won_005</t>
@@ -975,6 +999,12 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_010</t>
   </si>
   <si>
@@ -993,10 +1023,22 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wonelc_won_002</t>
@@ -1005,63 +1047,51 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_001</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_004</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w95048289-220,e_NZ27-220</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_NZ41-220,e_w412589726-220,e_w268841395-220,e_w180519027-220</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_NZ41-220,e_w412588974-220,e_w268841395-220,e_NZ42-220</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w89943957-220,e_w232382576-220,e_w26671244-220,e_w61853727-220,e_w167293888-220,e_NZ3-220,e_w82881422-220,e_w119877500-220,e_NZ5-220</t>
   </si>
   <si>
     <t>elc_won_005</t>
   </si>
   <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w90092620-220,e_w180514007-220,e_w270521928-220,e_w89637277-220,e_w94840399-220</t>
+  </si>
+  <si>
     <t>elc_won_010</t>
   </si>
   <si>
@@ -1080,10 +1110,22 @@
     <t>e_w95048289-220,e_w95046918-220,e_NZ27-220</t>
   </si>
   <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w89943957-220,e_w232382576-220,e_w26671244-220,e_w61853727-220,e_w167293888-220,e_NZ3-220,e_w82881422-220,e_w119877500-220,e_NZ5-220</t>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w414953388-220,e_w94840399-220</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_NZ31-220,e_w268826084-220,e_w1099619174-220,e_w93827784-220,e_w95046918-220</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_NZ30-220,e_w1099619174-220</t>
   </si>
   <si>
     <t>elc_won_002</t>
@@ -1092,58 +1134,178 @@
     <t>e_w95048289-220,e_w167705537-220,e_r17609399-220,e_NZ26-220,e_w95344674-220,e_w191346761-220,e_w1026587442-220,e_w167572576-220,e_NZ23-220,e_NZ21-220</t>
   </si>
   <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_NZ41-220,e_w412589726-220,e_w268841395-220,e_w180519027-220</t>
-  </si>
-  <si>
     <t>elc_won_001</t>
   </si>
   <si>
     <t>e_w167705537-220,e_w95343089-220,e_w93713118-220,e_w1026587442-220</t>
   </si>
   <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w90092620-220,e_w180514007-220,e_w270521928-220,e_w89637277-220,e_w94840399-220</t>
-  </si>
-  <si>
     <t>elc_won_004</t>
   </si>
   <si>
     <t>e_w167427251-220,e_w94053861-220,e_w89411122-220,e_NZ14-220,e_w270022030-220</t>
   </si>
   <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w414953388-220,e_w94840399-220</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_NZ31-220,e_w268826084-220,e_w1099619174-220,e_w93827784-220,e_w95046918-220</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w95048289-220,e_NZ27-220</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_NZ30-220,e_w1099619174-220</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_NZ41-220,e_w412588974-220,e_w268841395-220,e_NZ42-220</t>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
   </si>
   <si>
     <t>distr_wofelc_wof_010</t>
@@ -1164,64 +1326,10 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
   </si>
   <si>
     <t>distr_wofelc_wof_033</t>
@@ -1230,118 +1338,163 @@
     <t>connecting wind offshore to buses in cluster 33</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_021</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_NZ30-220,e_w95048289-220</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w100957314-220,e_w95343089-220</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w89637277-220,e_w100957314-220,e_w93713118-220</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_w100957314-220,e_w95343089-220,e_w93713118-220,e_w1026587442-220</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w412588974-220,e_NZ42-220,e_w270521928-220</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_w93419960-220,e_w95512216-220</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_w95512216-220,e_NZ13-220</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_NZ41-220,e_w412588974-220,e_w270521928-220</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_w412588974-220,e_w89637277-220</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_r17609399-220</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_w232382576-220,e_w1363994055-220,e_w82881422-220</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_w268841395-220,e_w412588974-220,e_NZ42-220</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_NZ3-220,e_w89943957-220,e_w119877500-220,e_w167283894-220</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w119877500-220,e_w167283894-220</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_w412588974-220</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_w167705537-220,e_w95343089-220,e_r17609399-220,e_NZ26-220,e_w95344674-220</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_w100957314-220,e_w93827784-220,e_w95046918-220</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_w412588974-220,e_NZ41-220</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_NZ41-220,e_w412589726-220,e_w412588974-220</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w89943957-220</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_w95512216-220,e_NZ13-220,e_w167283894-220</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_w412589726-220</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_w167286837-220,e_w268826084-220,e_NZ29-220,e_w100957314-220</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_w93713118-220,e_w1167708390-220,e_w1026587442-220,e_w167572576-220,e_w93419960-220</t>
   </si>
   <si>
     <t>elc_wof_010</t>
@@ -1359,175 +1512,22 @@
     <t>elc_wof_001</t>
   </si>
   <si>
-    <t>e_w89943957-220</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_NZ30-220,e_w95048289-220</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_w89637277-220,e_w100957314-220,e_w93713118-220</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
+    <t>elc_wof_028</t>
   </si>
   <si>
     <t>e_w270521928-220,e_w89637277-220,e_w94840399-220,e_w167286837-220</t>
   </si>
   <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_w167286837-220,e_w268826084-220,e_NZ29-220,e_w100957314-220,e_w93827784-220,e_w95046918-220</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_r17609399-220</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_w268841395-220,e_w412588974-220,e_NZ42-220</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_NZ3-220,e_w89943957-220,e_w119877500-220,e_w167283894-220</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w119877500-220,e_w167283894-220</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_w412588974-220,e_NZ41-220</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_w167705537-220,e_w95343089-220,e_r17609399-220,e_NZ26-220,e_w95344674-220</t>
-  </si>
-  <si>
     <t>elc_wof_033</t>
   </si>
   <si>
-    <t>e_w95343089-220,e_w93713118-220</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_NZ41-220,e_w412588974-220,e_w270521928-220</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_w412588974-220,e_w89637277-220</t>
+    <t>e_w95046918-220,e_w95343089-220,e_w93713118-220</t>
   </si>
   <si>
     <t>elc_wof_021</t>
   </si>
   <si>
-    <t>e_w100957314-220,e_w95343089-220</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_NZ41-220,e_w412589726-220,e_w412588974-220</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_w93713118-220,e_w1167708390-220,e_w1026587442-220,e_w167572576-220,e_w93419960-220</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_w95512216-220,e_NZ13-220</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_w95512216-220,e_NZ13-220,e_w167283894-220</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_w412588974-220</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_w232382576-220,e_w1363994055-220,e_w82881422-220</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w412588974-220,e_NZ42-220,e_w270521928-220</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
     <t>e_w95048289-220,e_NZ27-220,e_r17609399-220,e_w167705537-220</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_w412589726-220</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_w93827784-220,e_w95046918-220,e_w100957314-220,e_w95343089-220,e_w93713118-220</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>e_w93713118-220,e_w1026587442-220</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_w93419960-220,e_w95512216-220</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6594,7 +6594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5F9B1-2AD3-4AC6-9FFE-C93291553BEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B32BA658-D5F4-4EAC-B02C-EFD79AC04820}">
   <dimension ref="B9:BD43"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6832,16 +6832,16 @@
         <v>228</v>
       </c>
       <c r="Y11" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="Z11" t="s">
         <v>264</v>
       </c>
       <c r="AA11">
-        <v>0.99649838493007836</v>
+        <v>0.99781284363204548</v>
       </c>
       <c r="AB11">
-        <v>64.196276281897482</v>
+        <v>40.097866745833329</v>
       </c>
       <c r="AD11" t="s">
         <v>227</v>
@@ -6871,13 +6871,13 @@
         <v>310</v>
       </c>
       <c r="AN11" t="s">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="AO11">
-        <v>0.99595483459575906</v>
+        <v>0.99692224665834439</v>
       </c>
       <c r="AP11">
-        <v>74.161365744417125</v>
+        <v>56.425477930352955</v>
       </c>
       <c r="AR11" t="s">
         <v>227</v>
@@ -6910,10 +6910,10 @@
         <v>406</v>
       </c>
       <c r="BC11">
-        <v>0.99490522012066784</v>
+        <v>0.9878288138539939</v>
       </c>
       <c r="BD11">
-        <v>93.404297787756065</v>
+        <v>223.13841267677765</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6978,16 +6978,16 @@
         <v>232</v>
       </c>
       <c r="Y12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Z12" t="s">
         <v>265</v>
       </c>
       <c r="AA12">
-        <v>0.99568371668484024</v>
+        <v>0.99164479201276912</v>
       </c>
       <c r="AB12">
-        <v>79.131860777928608</v>
+        <v>153.17881309923388</v>
       </c>
       <c r="AD12" t="s">
         <v>227</v>
@@ -7014,16 +7014,16 @@
         <v>282</v>
       </c>
       <c r="AM12" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO12">
-        <v>0.99446613913875159</v>
+        <v>0.99590345602074126</v>
       </c>
       <c r="AP12">
-        <v>101.45411578955439</v>
+        <v>75.103306286410302</v>
       </c>
       <c r="AR12" t="s">
         <v>227</v>
@@ -7056,10 +7056,10 @@
         <v>408</v>
       </c>
       <c r="BC12">
-        <v>0.99728827252195684</v>
+        <v>0.98395883577792953</v>
       </c>
       <c r="BD12">
-        <v>49.715003764125143</v>
+        <v>294.08801073795939</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7124,16 +7124,16 @@
         <v>234</v>
       </c>
       <c r="Y13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z13" t="s">
         <v>266</v>
       </c>
       <c r="AA13">
-        <v>0.99673728461460676</v>
+        <v>0.99568371668484024</v>
       </c>
       <c r="AB13">
-        <v>59.816448732209111</v>
+        <v>79.131860777928608</v>
       </c>
       <c r="AD13" t="s">
         <v>227</v>
@@ -7160,16 +7160,16 @@
         <v>284</v>
       </c>
       <c r="AM13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AN13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO13">
-        <v>0.99821201020674788</v>
+        <v>0.9975157188831717</v>
       </c>
       <c r="AP13">
-        <v>32.77981287628851</v>
+        <v>45.545153808519316</v>
       </c>
       <c r="AR13" t="s">
         <v>227</v>
@@ -7202,10 +7202,10 @@
         <v>410</v>
       </c>
       <c r="BC13">
-        <v>0.95113733831453195</v>
+        <v>0.94957327345368925</v>
       </c>
       <c r="BD13">
-        <v>895.81546423358179</v>
+        <v>924.48998668236334</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7270,16 +7270,16 @@
         <v>236</v>
       </c>
       <c r="Y14" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="Z14" t="s">
         <v>267</v>
       </c>
       <c r="AA14">
-        <v>0.99709164861435029</v>
+        <v>0.99673728461460676</v>
       </c>
       <c r="AB14">
-        <v>53.319775403577559</v>
+        <v>59.816448732209111</v>
       </c>
       <c r="AD14" t="s">
         <v>227</v>
@@ -7306,16 +7306,16 @@
         <v>286</v>
       </c>
       <c r="AM14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO14">
-        <v>0.99562511313409086</v>
+        <v>0.99725701149052537</v>
       </c>
       <c r="AP14">
-        <v>80.206259208334231</v>
+        <v>50.288122673700855</v>
       </c>
       <c r="AR14" t="s">
         <v>227</v>
@@ -7348,10 +7348,10 @@
         <v>412</v>
       </c>
       <c r="BC14">
-        <v>0.98039565814133589</v>
+        <v>0.98560960960201449</v>
       </c>
       <c r="BD14">
-        <v>359.41293407550836</v>
+        <v>263.82382396306684</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7416,16 +7416,16 @@
         <v>238</v>
       </c>
       <c r="Y15" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="Z15" t="s">
         <v>268</v>
       </c>
       <c r="AA15">
-        <v>0.99164479201276912</v>
+        <v>0.99709164861435029</v>
       </c>
       <c r="AB15">
-        <v>153.17881309923388</v>
+        <v>53.319775403577559</v>
       </c>
       <c r="AD15" t="s">
         <v>227</v>
@@ -7452,16 +7452,16 @@
         <v>288</v>
       </c>
       <c r="AM15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN15" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="AO15">
-        <v>0.99725701149052537</v>
+        <v>0.99595483459575906</v>
       </c>
       <c r="AP15">
-        <v>50.288122673700855</v>
+        <v>74.161365744417125</v>
       </c>
       <c r="AR15" t="s">
         <v>227</v>
@@ -7494,10 +7494,10 @@
         <v>414</v>
       </c>
       <c r="BC15">
-        <v>0.94957327345368925</v>
+        <v>0.99053075643264799</v>
       </c>
       <c r="BD15">
-        <v>924.48998668236334</v>
+        <v>173.60279873478748</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7562,16 +7562,16 @@
         <v>240</v>
       </c>
       <c r="Y16" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="Z16" t="s">
         <v>269</v>
       </c>
       <c r="AA16">
-        <v>0.99541580702824473</v>
+        <v>0.99552574319771747</v>
       </c>
       <c r="AB16">
-        <v>84.0435378155141</v>
+        <v>82.028041375179441</v>
       </c>
       <c r="AD16" t="s">
         <v>227</v>
@@ -7604,10 +7604,10 @@
         <v>320</v>
       </c>
       <c r="AO16">
-        <v>0.99807547980555666</v>
+        <v>0.99761292756299069</v>
       </c>
       <c r="AP16">
-        <v>35.282870231460656</v>
+        <v>43.762994678503716</v>
       </c>
       <c r="AR16" t="s">
         <v>227</v>
@@ -7637,13 +7637,13 @@
         <v>415</v>
       </c>
       <c r="BB16" t="s">
-        <v>416</v>
+        <v>266</v>
       </c>
       <c r="BC16">
-        <v>0.9955021345306051</v>
+        <v>0.98974923036021278</v>
       </c>
       <c r="BD16">
-        <v>82.460866938907401</v>
+        <v>187.93077672943278</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7708,16 +7708,16 @@
         <v>242</v>
       </c>
       <c r="Y17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Z17" t="s">
         <v>270</v>
       </c>
       <c r="AA17">
-        <v>0.9981722170039925</v>
+        <v>0.99856414548474748</v>
       </c>
       <c r="AB17">
-        <v>33.509354926805031</v>
+        <v>26.323999446296273</v>
       </c>
       <c r="AD17" t="s">
         <v>227</v>
@@ -7750,10 +7750,10 @@
         <v>322</v>
       </c>
       <c r="AO17">
-        <v>0.99590345602074126</v>
+        <v>0.99446613913875159</v>
       </c>
       <c r="AP17">
-        <v>75.103306286410302</v>
+        <v>101.45411578955439</v>
       </c>
       <c r="AR17" t="s">
         <v>227</v>
@@ -7780,16 +7780,16 @@
         <v>351</v>
       </c>
       <c r="BA17" t="s">
+        <v>416</v>
+      </c>
+      <c r="BB17" t="s">
         <v>417</v>
       </c>
-      <c r="BB17" t="s">
-        <v>418</v>
-      </c>
       <c r="BC17">
-        <v>0.99438825713920898</v>
+        <v>0.99439449087123744</v>
       </c>
       <c r="BD17">
-        <v>102.88195244783461</v>
+        <v>102.76766736064755</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7854,16 +7854,16 @@
         <v>244</v>
       </c>
       <c r="Y18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Z18" t="s">
         <v>271</v>
       </c>
       <c r="AA18">
-        <v>0.99656426482871763</v>
+        <v>0.99837169372341228</v>
       </c>
       <c r="AB18">
-        <v>62.988478140176163</v>
+        <v>29.852281737441412</v>
       </c>
       <c r="AD18" t="s">
         <v>227</v>
@@ -7896,10 +7896,10 @@
         <v>324</v>
       </c>
       <c r="AO18">
-        <v>0.99665105279570931</v>
+        <v>0.99821201020674788</v>
       </c>
       <c r="AP18">
-        <v>61.397365411996212</v>
+        <v>32.77981287628851</v>
       </c>
       <c r="AR18" t="s">
         <v>227</v>
@@ -7926,16 +7926,16 @@
         <v>353</v>
       </c>
       <c r="BA18" t="s">
+        <v>418</v>
+      </c>
+      <c r="BB18" t="s">
         <v>419</v>
       </c>
-      <c r="BB18" t="s">
-        <v>420</v>
-      </c>
       <c r="BC18">
-        <v>0.992142345264865</v>
+        <v>0.9960370911532308</v>
       </c>
       <c r="BD18">
-        <v>144.05700347747464</v>
+        <v>72.653328857434573</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8000,16 +8000,16 @@
         <v>246</v>
       </c>
       <c r="Y19" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="Z19" t="s">
         <v>272</v>
       </c>
       <c r="AA19">
-        <v>0.99781284363204548</v>
+        <v>0.99541580702824473</v>
       </c>
       <c r="AB19">
-        <v>40.097866745833329</v>
+        <v>84.0435378155141</v>
       </c>
       <c r="AD19" t="s">
         <v>227</v>
@@ -8042,10 +8042,10 @@
         <v>326</v>
       </c>
       <c r="AO19">
-        <v>0.99761292756299069</v>
+        <v>0.99562511313409086</v>
       </c>
       <c r="AP19">
-        <v>43.762994678503716</v>
+        <v>80.206259208334231</v>
       </c>
       <c r="AR19" t="s">
         <v>227</v>
@@ -8072,16 +8072,16 @@
         <v>355</v>
       </c>
       <c r="BA19" t="s">
+        <v>420</v>
+      </c>
+      <c r="BB19" t="s">
         <v>421</v>
       </c>
-      <c r="BB19" t="s">
-        <v>422</v>
-      </c>
       <c r="BC19">
-        <v>0.99503867375582744</v>
+        <v>0.98596601099553871</v>
       </c>
       <c r="BD19">
-        <v>90.957647809829638</v>
+        <v>257.2897984151241</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8146,16 +8146,16 @@
         <v>248</v>
       </c>
       <c r="Y20" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Z20" t="s">
         <v>273</v>
       </c>
       <c r="AA20">
-        <v>0.99757939258365447</v>
+        <v>0.9981722170039925</v>
       </c>
       <c r="AB20">
-        <v>44.377802633000776</v>
+        <v>33.509354926805031</v>
       </c>
       <c r="AD20" t="s">
         <v>227</v>
@@ -8188,10 +8188,10 @@
         <v>328</v>
       </c>
       <c r="AO20">
-        <v>0.99826030196534266</v>
+        <v>0.99857516825685033</v>
       </c>
       <c r="AP20">
-        <v>31.894463968718917</v>
+        <v>26.121915291078167</v>
       </c>
       <c r="AR20" t="s">
         <v>227</v>
@@ -8218,16 +8218,16 @@
         <v>357</v>
       </c>
       <c r="BA20" t="s">
+        <v>422</v>
+      </c>
+      <c r="BB20" t="s">
         <v>423</v>
       </c>
-      <c r="BB20" t="s">
-        <v>424</v>
-      </c>
       <c r="BC20">
-        <v>0.99162758874212198</v>
+        <v>0.96328479701100822</v>
       </c>
       <c r="BD20">
-        <v>153.49420639442948</v>
+        <v>673.11205479818182</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8292,16 +8292,16 @@
         <v>250</v>
       </c>
       <c r="Y21" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Z21" t="s">
         <v>274</v>
       </c>
       <c r="AA21">
-        <v>0.9982917156958806</v>
+        <v>0.99757939258365447</v>
       </c>
       <c r="AB21">
-        <v>31.318545575522229</v>
+        <v>44.377802633000776</v>
       </c>
       <c r="AD21" t="s">
         <v>227</v>
@@ -8334,10 +8334,10 @@
         <v>330</v>
       </c>
       <c r="AO21">
-        <v>0.99857516825685033</v>
+        <v>0.99624198670989172</v>
       </c>
       <c r="AP21">
-        <v>26.121915291078167</v>
+        <v>68.896910318651507</v>
       </c>
       <c r="AR21" t="s">
         <v>227</v>
@@ -8364,16 +8364,16 @@
         <v>359</v>
       </c>
       <c r="BA21" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="BB21" t="s">
-        <v>426</v>
+        <v>272</v>
       </c>
       <c r="BC21">
-        <v>0.99508487560623826</v>
+        <v>0.98248517632197996</v>
       </c>
       <c r="BD21">
-        <v>90.110613885632716</v>
+        <v>321.10510076370025</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8438,16 +8438,16 @@
         <v>252</v>
       </c>
       <c r="Y22" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="Z22" t="s">
         <v>275</v>
       </c>
       <c r="AA22">
-        <v>0.99552574319771747</v>
+        <v>0.9982917156958806</v>
       </c>
       <c r="AB22">
-        <v>82.028041375179441</v>
+        <v>31.318545575522229</v>
       </c>
       <c r="AD22" t="s">
         <v>227</v>
@@ -8480,10 +8480,10 @@
         <v>332</v>
       </c>
       <c r="AO22">
-        <v>0.99624198670989172</v>
+        <v>0.99239099026325794</v>
       </c>
       <c r="AP22">
-        <v>68.896910318651507</v>
+        <v>139.49851184027145</v>
       </c>
       <c r="AR22" t="s">
         <v>227</v>
@@ -8510,16 +8510,16 @@
         <v>361</v>
       </c>
       <c r="BA22" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="BB22" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="BC22">
-        <v>0.96374055461874508</v>
+        <v>0.992142345264865</v>
       </c>
       <c r="BD22">
-        <v>664.7564986563408</v>
+        <v>144.05700347747464</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8584,16 +8584,16 @@
         <v>254</v>
       </c>
       <c r="Y23" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="Z23" t="s">
         <v>276</v>
       </c>
       <c r="AA23">
-        <v>0.99856414548474748</v>
+        <v>0.99649838493007836</v>
       </c>
       <c r="AB23">
-        <v>26.323999446296273</v>
+        <v>64.196276281897482</v>
       </c>
       <c r="AD23" t="s">
         <v>227</v>
@@ -8626,10 +8626,10 @@
         <v>334</v>
       </c>
       <c r="AO23">
-        <v>0.99692224665834439</v>
+        <v>0.99807547980555666</v>
       </c>
       <c r="AP23">
-        <v>56.425477930352955</v>
+        <v>35.282870231460656</v>
       </c>
       <c r="AR23" t="s">
         <v>227</v>
@@ -8656,16 +8656,16 @@
         <v>363</v>
       </c>
       <c r="BA23" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="BB23" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="BC23">
-        <v>0.99514843803074871</v>
+        <v>0.99241288386292881</v>
       </c>
       <c r="BD23">
-        <v>88.945302769606073</v>
+        <v>139.09712917963907</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8730,16 +8730,16 @@
         <v>256</v>
       </c>
       <c r="Y24" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Z24" t="s">
         <v>277</v>
       </c>
       <c r="AA24">
-        <v>0.99837169372341228</v>
+        <v>0.9958319028842455</v>
       </c>
       <c r="AB24">
-        <v>29.852281737441412</v>
+        <v>76.415113788833068</v>
       </c>
       <c r="AD24" t="s">
         <v>227</v>
@@ -8772,10 +8772,10 @@
         <v>336</v>
       </c>
       <c r="AO24">
-        <v>0.99239099026325794</v>
+        <v>0.99665105279570931</v>
       </c>
       <c r="AP24">
-        <v>139.49851184027145</v>
+        <v>61.397365411996212</v>
       </c>
       <c r="AR24" t="s">
         <v>227</v>
@@ -8802,16 +8802,16 @@
         <v>365</v>
       </c>
       <c r="BA24" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="BB24" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="BC24">
-        <v>0.99616514741256923</v>
+        <v>0.99503867375582744</v>
       </c>
       <c r="BD24">
-        <v>70.305630769563152</v>
+        <v>90.957647809829638</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8876,16 +8876,16 @@
         <v>258</v>
       </c>
       <c r="Y25" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="Z25" t="s">
         <v>278</v>
       </c>
       <c r="AA25">
-        <v>0.9958319028842455</v>
+        <v>0.9986195737404916</v>
       </c>
       <c r="AB25">
-        <v>76.415113788833068</v>
+        <v>25.307814757654675</v>
       </c>
       <c r="AD25" t="s">
         <v>227</v>
@@ -8918,10 +8918,10 @@
         <v>338</v>
       </c>
       <c r="AO25">
-        <v>0.9975157188831717</v>
+        <v>0.99826030196534266</v>
       </c>
       <c r="AP25">
-        <v>45.545153808519316</v>
+        <v>31.894463968718917</v>
       </c>
       <c r="AR25" t="s">
         <v>227</v>
@@ -8948,16 +8948,16 @@
         <v>367</v>
       </c>
       <c r="BA25" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="BB25" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="BC25">
-        <v>0.98596601099553871</v>
+        <v>0.99162758874212198</v>
       </c>
       <c r="BD25">
-        <v>257.2897984151241</v>
+        <v>153.49420639442948</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9022,16 +9022,16 @@
         <v>260</v>
       </c>
       <c r="Y26" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="Z26" t="s">
         <v>279</v>
       </c>
       <c r="AA26">
-        <v>0.9986195737404916</v>
+        <v>0.99656426482871763</v>
       </c>
       <c r="AB26">
-        <v>25.307814757654675</v>
+        <v>62.988478140176163</v>
       </c>
       <c r="AR26" t="s">
         <v>227</v>
@@ -9058,16 +9058,16 @@
         <v>369</v>
       </c>
       <c r="BA26" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="BB26" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="BC26">
-        <v>0.96328479701100822</v>
+        <v>0.99508487560623826</v>
       </c>
       <c r="BD26">
-        <v>673.11205479818182</v>
+        <v>90.110613885632716</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9096,16 +9096,16 @@
         <v>371</v>
       </c>
       <c r="BA27" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="BB27" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="BC27">
-        <v>0.98591647432380625</v>
+        <v>0.97496359905143026</v>
       </c>
       <c r="BD27">
-        <v>258.19797073021897</v>
+        <v>459.00068405711187</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9134,16 +9134,16 @@
         <v>373</v>
       </c>
       <c r="BA28" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="BB28" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="BC28">
-        <v>0.99048115912556611</v>
+        <v>0.99514843803074871</v>
       </c>
       <c r="BD28">
-        <v>174.51208269795416</v>
+        <v>88.945302769606073</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9172,16 +9172,16 @@
         <v>375</v>
       </c>
       <c r="BA29" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="BB29" t="s">
-        <v>442</v>
+        <v>406</v>
       </c>
       <c r="BC29">
-        <v>0.99402264995370893</v>
+        <v>0.98039565814133589</v>
       </c>
       <c r="BD29">
-        <v>109.58475084866993</v>
+        <v>359.41293407550836</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9210,16 +9210,16 @@
         <v>377</v>
       </c>
       <c r="BA30" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="BB30" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="BC30">
-        <v>0.9960370911532308</v>
+        <v>0.99199988291996133</v>
       </c>
       <c r="BD30">
-        <v>72.653328857434573</v>
+        <v>146.66881313404267</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9248,16 +9248,16 @@
         <v>379</v>
       </c>
       <c r="BA31" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="BB31" t="s">
-        <v>410</v>
+        <v>443</v>
       </c>
       <c r="BC31">
-        <v>0.99441710380733805</v>
+        <v>0.96374055461874508</v>
       </c>
       <c r="BD31">
-        <v>102.3530968654682</v>
+        <v>664.7564986563408</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9286,16 +9286,16 @@
         <v>381</v>
       </c>
       <c r="BA32" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="BB32" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="BC32">
-        <v>0.9871879084242271</v>
+        <v>0.99048115912556611</v>
       </c>
       <c r="BD32">
-        <v>234.88834555583597</v>
+        <v>174.51208269795416</v>
       </c>
     </row>
     <row r="33" spans="44:56">
@@ -9324,16 +9324,16 @@
         <v>383</v>
       </c>
       <c r="BA33" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="BB33" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="BC33">
-        <v>0.97496359905143026</v>
+        <v>0.99441710380733805</v>
       </c>
       <c r="BD33">
-        <v>459.00068405711187</v>
+        <v>102.3530968654682</v>
       </c>
     </row>
     <row r="34" spans="44:56">
@@ -9362,16 +9362,16 @@
         <v>385</v>
       </c>
       <c r="BA34" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="BB34" t="s">
-        <v>269</v>
+        <v>449</v>
       </c>
       <c r="BC34">
-        <v>0.98248517632197996</v>
+        <v>0.9871879084242271</v>
       </c>
       <c r="BD34">
-        <v>321.10510076370025</v>
+        <v>234.88834555583597</v>
       </c>
     </row>
     <row r="35" spans="44:56">
@@ -9400,16 +9400,16 @@
         <v>387</v>
       </c>
       <c r="BA35" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB35" t="s">
         <v>451</v>
       </c>
-      <c r="BB35" t="s">
-        <v>452</v>
-      </c>
       <c r="BC35">
-        <v>0.99241288386292881</v>
+        <v>0.99511226039729839</v>
       </c>
       <c r="BD35">
-        <v>139.09712917963907</v>
+        <v>89.608559382863291</v>
       </c>
     </row>
     <row r="36" spans="44:56">
@@ -9438,16 +9438,16 @@
         <v>389</v>
       </c>
       <c r="BA36" t="s">
+        <v>452</v>
+      </c>
+      <c r="BB36" t="s">
         <v>453</v>
       </c>
-      <c r="BB36" t="s">
-        <v>454</v>
-      </c>
       <c r="BC36">
-        <v>0.99053075643264799</v>
+        <v>0.99402092584318991</v>
       </c>
       <c r="BD36">
-        <v>173.60279873478748</v>
+        <v>109.61635954151812</v>
       </c>
     </row>
     <row r="37" spans="44:56">
@@ -9476,16 +9476,16 @@
         <v>391</v>
       </c>
       <c r="BA37" t="s">
+        <v>454</v>
+      </c>
+      <c r="BB37" t="s">
         <v>455</v>
       </c>
-      <c r="BB37" t="s">
-        <v>265</v>
-      </c>
       <c r="BC37">
-        <v>0.98974923036021278</v>
+        <v>0.99402264995370893</v>
       </c>
       <c r="BD37">
-        <v>187.93077672943278</v>
+        <v>109.58475084866993</v>
       </c>
     </row>
     <row r="38" spans="44:56">
@@ -9520,10 +9520,10 @@
         <v>457</v>
       </c>
       <c r="BC38">
-        <v>0.9877150845460122</v>
+        <v>0.99490522012066784</v>
       </c>
       <c r="BD38">
-        <v>225.22344998977596</v>
+        <v>93.404297787756065</v>
       </c>
     </row>
     <row r="39" spans="44:56">
@@ -9558,10 +9558,10 @@
         <v>459</v>
       </c>
       <c r="BC39">
-        <v>0.99511226039729839</v>
+        <v>0.99728827252195684</v>
       </c>
       <c r="BD39">
-        <v>89.608559382863291</v>
+        <v>49.715003764125143</v>
       </c>
     </row>
     <row r="40" spans="44:56">
@@ -9593,13 +9593,13 @@
         <v>460</v>
       </c>
       <c r="BB40" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="BC40">
-        <v>0.9878288138539939</v>
+        <v>0.95113733831453195</v>
       </c>
       <c r="BD40">
-        <v>223.13841267677765</v>
+        <v>895.81546423358179</v>
       </c>
     </row>
     <row r="41" spans="44:56">
@@ -9634,10 +9634,10 @@
         <v>462</v>
       </c>
       <c r="BC41">
-        <v>0.98739169991813736</v>
+        <v>0.9955021345306051</v>
       </c>
       <c r="BD41">
-        <v>231.15216816748233</v>
+        <v>82.460866938907401</v>
       </c>
     </row>
     <row r="42" spans="44:56">
@@ -9672,10 +9672,10 @@
         <v>464</v>
       </c>
       <c r="BC42">
-        <v>0.98382606125833871</v>
+        <v>0.99579892549254256</v>
       </c>
       <c r="BD42">
-        <v>296.52221026378965</v>
+        <v>77.019699303385977</v>
       </c>
     </row>
     <row r="43" spans="44:56">
@@ -9710,10 +9710,10 @@
         <v>466</v>
       </c>
       <c r="BC43">
-        <v>0.99439449087123744</v>
+        <v>0.9877150845460122</v>
       </c>
       <c r="BD43">
-        <v>102.76766736064755</v>
+        <v>225.22344998977596</v>
       </c>
     </row>
   </sheetData>
@@ -9722,7 +9722,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A7A9BF-29FB-41F6-A62A-7F7F1C155B73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8066EFCD-2778-49D7-8C00-3FF12B4CE8E9}">
   <dimension ref="B9:Z43"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9834,7 +9834,7 @@
         <v>467</v>
       </c>
       <c r="K11" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="L11">
         <v>8.3728062197205944</v>
@@ -9867,7 +9867,7 @@
         <v>497</v>
       </c>
       <c r="X11" t="s">
-        <v>409</v>
+        <v>460</v>
       </c>
       <c r="Y11">
         <v>2.177</v>
@@ -9902,7 +9902,7 @@
         <v>469</v>
       </c>
       <c r="K12" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="L12">
         <v>42.531235680568031</v>
@@ -9935,7 +9935,7 @@
         <v>499</v>
       </c>
       <c r="X12" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Y12">
         <v>47.905999999999999</v>
@@ -9970,7 +9970,7 @@
         <v>471</v>
       </c>
       <c r="K13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L13">
         <v>30.271312154499352</v>
@@ -10003,7 +10003,7 @@
         <v>501</v>
       </c>
       <c r="X13" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="Y13">
         <v>91.13</v>
@@ -10038,7 +10038,7 @@
         <v>473</v>
       </c>
       <c r="K14" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="L14">
         <v>22.688073076145226</v>
@@ -10071,7 +10071,7 @@
         <v>503</v>
       </c>
       <c r="X14" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Y14">
         <v>30.484999999999999</v>
@@ -10106,7 +10106,7 @@
         <v>475</v>
       </c>
       <c r="K15" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="L15">
         <v>29.120153762247021</v>
@@ -10139,7 +10139,7 @@
         <v>505</v>
       </c>
       <c r="X15" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="Y15">
         <v>6.726</v>
@@ -10174,7 +10174,7 @@
         <v>477</v>
       </c>
       <c r="K16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L16">
         <v>10.867385180190169</v>
@@ -10207,7 +10207,7 @@
         <v>507</v>
       </c>
       <c r="X16" t="s">
-        <v>465</v>
+        <v>416</v>
       </c>
       <c r="Y16">
         <v>33.183</v>
@@ -10242,7 +10242,7 @@
         <v>479</v>
       </c>
       <c r="K17" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="L17">
         <v>32.115075062865692</v>
@@ -10275,7 +10275,7 @@
         <v>509</v>
       </c>
       <c r="X17" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="Y17">
         <v>40.698999999999998</v>
@@ -10310,7 +10310,7 @@
         <v>481</v>
       </c>
       <c r="K18" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="L18">
         <v>9.0868240253443027</v>
@@ -10343,7 +10343,7 @@
         <v>511</v>
       </c>
       <c r="X18" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="Y18">
         <v>43.79</v>
@@ -10378,7 +10378,7 @@
         <v>483</v>
       </c>
       <c r="K19" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="L19">
         <v>18.016423245563796</v>
@@ -10411,7 +10411,7 @@
         <v>513</v>
       </c>
       <c r="X19" t="s">
-        <v>407</v>
+        <v>458</v>
       </c>
       <c r="Y19">
         <v>3.617</v>
@@ -10446,7 +10446,7 @@
         <v>485</v>
       </c>
       <c r="K20" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="L20">
         <v>0.75250112047637663</v>
@@ -10479,7 +10479,7 @@
         <v>515</v>
       </c>
       <c r="X20" t="s">
-        <v>405</v>
+        <v>456</v>
       </c>
       <c r="Y20">
         <v>45.468000000000004</v>
@@ -10514,7 +10514,7 @@
         <v>487</v>
       </c>
       <c r="K21" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="L21">
         <v>18.381813037942475</v>
@@ -10547,7 +10547,7 @@
         <v>517</v>
       </c>
       <c r="X21" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="Y21">
         <v>33.305</v>
@@ -10582,7 +10582,7 @@
         <v>489</v>
       </c>
       <c r="K22" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="L22">
         <v>4.5221914845937041</v>
@@ -10615,7 +10615,7 @@
         <v>519</v>
       </c>
       <c r="X22" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="Y22">
         <v>32.006</v>
@@ -10650,7 +10650,7 @@
         <v>491</v>
       </c>
       <c r="K23" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="L23">
         <v>8.2953562793919264</v>
@@ -10683,7 +10683,7 @@
         <v>521</v>
       </c>
       <c r="X23" t="s">
-        <v>453</v>
+        <v>413</v>
       </c>
       <c r="Y23">
         <v>92.117999999999995</v>
@@ -10718,7 +10718,7 @@
         <v>493</v>
       </c>
       <c r="K24" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="L24">
         <v>1.2792726734837132</v>
@@ -10751,13 +10751,13 @@
         <v>523</v>
       </c>
       <c r="X24" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="Y24">
-        <v>6.194</v>
+        <v>55.912999999999997</v>
       </c>
       <c r="Z24">
-        <v>0.38156880578624569</v>
+        <v>0.65599145251831115</v>
       </c>
     </row>
     <row r="25" spans="2:26">
@@ -10786,7 +10786,7 @@
         <v>495</v>
       </c>
       <c r="K25" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="L25">
         <v>1.6182682752282065</v>
@@ -10819,13 +10819,13 @@
         <v>525</v>
       </c>
       <c r="X25" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="Y25">
-        <v>55.912999999999997</v>
+        <v>164.86799999999999</v>
       </c>
       <c r="Z25">
-        <v>0.65599145251831115</v>
+        <v>0.72650931190792389</v>
       </c>
     </row>
     <row r="26" spans="2:26">
@@ -10854,13 +10854,13 @@
         <v>527</v>
       </c>
       <c r="X26" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="Y26">
-        <v>164.86799999999999</v>
+        <v>177.54</v>
       </c>
       <c r="Z26">
-        <v>0.72650931190792389</v>
+        <v>0.68803916449510105</v>
       </c>
     </row>
     <row r="27" spans="2:26">
@@ -10889,13 +10889,13 @@
         <v>529</v>
       </c>
       <c r="X27" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="Y27">
-        <v>177.54</v>
+        <v>234.209</v>
       </c>
       <c r="Z27">
-        <v>0.68803916449510105</v>
+        <v>0.77345015707305564</v>
       </c>
     </row>
     <row r="28" spans="2:26">
@@ -10924,13 +10924,13 @@
         <v>531</v>
       </c>
       <c r="X28" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="Y28">
-        <v>234.209</v>
+        <v>244.34299999999999</v>
       </c>
       <c r="Z28">
-        <v>0.77345015707305564</v>
+        <v>0.80175270337644977</v>
       </c>
     </row>
     <row r="29" spans="2:26">
@@ -10959,13 +10959,13 @@
         <v>533</v>
       </c>
       <c r="X29" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="Y29">
-        <v>244.34299999999999</v>
+        <v>96.406999999999996</v>
       </c>
       <c r="Z29">
-        <v>0.80175270337644977</v>
+        <v>0.79274433267354172</v>
       </c>
     </row>
     <row r="30" spans="2:26">
@@ -10994,13 +10994,13 @@
         <v>535</v>
       </c>
       <c r="X30" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Y30">
-        <v>96.406999999999996</v>
+        <v>60.06</v>
       </c>
       <c r="Z30">
-        <v>0.79274433267354172</v>
+        <v>0.43959926703691221</v>
       </c>
     </row>
     <row r="31" spans="2:26">
@@ -11029,13 +11029,13 @@
         <v>537</v>
       </c>
       <c r="X31" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="Y31">
-        <v>70.597999999999999</v>
+        <v>142.483</v>
       </c>
       <c r="Z31">
-        <v>0.50775932669613255</v>
+        <v>0.52316710613332129</v>
       </c>
     </row>
     <row r="32" spans="2:26">
@@ -11064,13 +11064,13 @@
         <v>539</v>
       </c>
       <c r="X32" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="Y32">
-        <v>20.597000000000001</v>
+        <v>72.956000000000003</v>
       </c>
       <c r="Z32">
-        <v>0.56041320139424933</v>
+        <v>0.44425172502430138</v>
       </c>
     </row>
     <row r="33" spans="15:26">
@@ -11099,13 +11099,13 @@
         <v>541</v>
       </c>
       <c r="X33" t="s">
-        <v>461</v>
+        <v>415</v>
       </c>
       <c r="Y33">
-        <v>74.921000000000006</v>
+        <v>19.841000000000001</v>
       </c>
       <c r="Z33">
-        <v>0.52029689441762395</v>
+        <v>0.37558571129148788</v>
       </c>
     </row>
     <row r="34" spans="15:26">
@@ -11134,13 +11134,13 @@
         <v>543</v>
       </c>
       <c r="X34" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="Y34">
-        <v>88.290999999999997</v>
+        <v>138.42500000000001</v>
       </c>
       <c r="Z34">
-        <v>0.37989646842402669</v>
+        <v>0.3667297322843705</v>
       </c>
     </row>
     <row r="35" spans="15:26">
@@ -11169,13 +11169,13 @@
         <v>545</v>
       </c>
       <c r="X35" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="Y35">
-        <v>44.996000000000002</v>
+        <v>69.513999999999996</v>
       </c>
       <c r="Z35">
-        <v>0.42188049242982117</v>
+        <v>0.43127662972358699</v>
       </c>
     </row>
     <row r="36" spans="15:26">
@@ -11204,13 +11204,13 @@
         <v>547</v>
       </c>
       <c r="X36" t="s">
-        <v>411</v>
+        <v>452</v>
       </c>
       <c r="Y36">
-        <v>72.956000000000003</v>
+        <v>60.743000000000002</v>
       </c>
       <c r="Z36">
-        <v>0.44425172502430138</v>
+        <v>0.39077255435176689</v>
       </c>
     </row>
     <row r="37" spans="15:26">
@@ -11239,13 +11239,13 @@
         <v>549</v>
       </c>
       <c r="X37" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="Y37">
-        <v>19.841000000000001</v>
+        <v>6.194</v>
       </c>
       <c r="Z37">
-        <v>0.37558571129148788</v>
+        <v>0.38156880578624569</v>
       </c>
     </row>
     <row r="38" spans="15:26">
@@ -11274,13 +11274,13 @@
         <v>551</v>
       </c>
       <c r="X38" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Y38">
-        <v>138.42500000000001</v>
+        <v>44.996000000000002</v>
       </c>
       <c r="Z38">
-        <v>0.3667297322843705</v>
+        <v>0.42188049242982117</v>
       </c>
     </row>
     <row r="39" spans="15:26">
@@ -11309,13 +11309,13 @@
         <v>553</v>
       </c>
       <c r="X39" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="Y39">
-        <v>60.06</v>
+        <v>45.517000000000003</v>
       </c>
       <c r="Z39">
-        <v>0.43959926703691221</v>
+        <v>0.51873296024771309</v>
       </c>
     </row>
     <row r="40" spans="15:26">
@@ -11344,13 +11344,13 @@
         <v>555</v>
       </c>
       <c r="X40" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="Y40">
-        <v>142.483</v>
+        <v>76.210999999999999</v>
       </c>
       <c r="Z40">
-        <v>0.52316710613332129</v>
+        <v>0.5468169336461739</v>
       </c>
     </row>
     <row r="41" spans="15:26">
@@ -11379,7 +11379,7 @@
         <v>557</v>
       </c>
       <c r="X41" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="Y41">
         <v>20.327999999999999</v>
@@ -11414,7 +11414,7 @@
         <v>559</v>
       </c>
       <c r="X42" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="Y42">
         <v>65.320999999999998</v>
@@ -11449,13 +11449,13 @@
         <v>561</v>
       </c>
       <c r="X43" t="s">
-        <v>431</v>
+        <v>463</v>
       </c>
       <c r="Y43">
-        <v>30.48</v>
+        <v>32.902000000000001</v>
       </c>
       <c r="Z43">
-        <v>0.43855288369485051</v>
+        <v>0.43396218713816731</v>
       </c>
     </row>
   </sheetData>
@@ -11464,7 +11464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23948EED-1829-4714-9CED-DBEE22AD6D58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6ACE87-10DB-4D24-9E2C-7F47D0E68560}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
